--- a/要件定義書（採用管理システム）.xlsx
+++ b/要件定義書（採用管理システム）.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\my_application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99E140AB-5B69-4C19-A710-EC479CB7A924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D9DC5D-8B87-4010-9778-55E4143366B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="163">
   <si>
     <t>要件定義</t>
   </si>
@@ -89,42 +89,15 @@
     <t>タイトル</t>
   </si>
   <si>
-    <t>ページ</t>
-  </si>
-  <si>
     <t>第1章</t>
   </si>
   <si>
-    <t>要求概要</t>
-  </si>
-  <si>
     <t>第4章</t>
   </si>
   <si>
-    <t>システムの背景と目的</t>
-  </si>
-  <si>
-    <t>用語の定義</t>
-  </si>
-  <si>
-    <t>業務の概要</t>
-  </si>
-  <si>
-    <t>現状の課題と改善案</t>
-  </si>
-  <si>
-    <t>基本要件と優先順位</t>
-  </si>
-  <si>
     <t>第2章</t>
   </si>
   <si>
-    <t>システムの要件</t>
-  </si>
-  <si>
-    <t>システム機能要件</t>
-  </si>
-  <si>
     <t>第3章</t>
   </si>
   <si>
@@ -176,25 +149,10 @@
     <t>4-1. 性能要件</t>
   </si>
   <si>
-    <t>・  1,000件の見積データに対し検索応答時間 1 秒以内</t>
-  </si>
-  <si>
     <t>4-2. セキュリティ要件</t>
   </si>
   <si>
-    <t>・  権限管理の実装</t>
-  </si>
-  <si>
-    <t>・  通信経路の HTTPS 暗号化</t>
-  </si>
-  <si>
     <t>4-3. 可用性</t>
-  </si>
-  <si>
-    <t>・月間稼働率 99.5%以上</t>
-  </si>
-  <si>
-    <t>・システムメンテナンスは深夜帯に実施</t>
   </si>
   <si>
     <t>データ項目定義</t>
@@ -1345,13 +1303,278 @@
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
+  <si>
+    <t>渡辺のぞみ</t>
+    <rPh sb="0" eb="2">
+      <t>ワタナベ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>業務要件、利用者・権限定義、機能要件（途中）</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>業務要件、利用者・権限定義（修正・追記）、機能要件（作成）</t>
+    <rPh sb="0" eb="1">
+      <t>ギョウ</t>
+    </rPh>
+    <rPh sb="21" eb="25">
+      <t>キノウヨウケン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>データ項目定義、リスク・課題（作成）</t>
+    <rPh sb="3" eb="7">
+      <t>コウモクテイギ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>業務要件：1-3、1-4追記
+利用者・権限：管理者の権限内容変更</t>
+    <rPh sb="0" eb="4">
+      <t>ギョウムヨウケン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ツイキ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>リヨウシャ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ケンゲン</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>カンリシャ</t>
+    </rPh>
+    <rPh sb="26" eb="30">
+      <t>ケンゲンナイヨウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>1-1</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>1-2</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>1-3</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>1-4</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>業務要件</t>
+    <rPh sb="0" eb="4">
+      <t>ギョウムヨウケン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>システム化の目的</t>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>モクテキ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>システム化の背景</t>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>システム化の範囲</t>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>現状の課題</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>改善後の姿</t>
+    <rPh sb="0" eb="3">
+      <t>カイゼンゴ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>スガタ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>利用者区分</t>
+    <rPh sb="0" eb="5">
+      <t>リヨウシャクブン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>利用者・権限</t>
+    <rPh sb="0" eb="3">
+      <t>リヨウシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケンゲン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>2-1</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>機能要件</t>
+    <rPh sb="0" eb="4">
+      <t>キノウヨウケン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>3-1</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>機能一覧</t>
+    <rPh sb="0" eb="4">
+      <t>キノウイチラン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>3-2</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>機能詳細</t>
+    <rPh sb="0" eb="4">
+      <t>キノウショウサイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>第4章</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>非機能要件</t>
+    <rPh sb="0" eb="3">
+      <t>ヒキノウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヨウケン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>4-1</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>性能要件</t>
+    <rPh sb="0" eb="4">
+      <t>セイノウヨウケン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>4-2</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>セキュリティ要件</t>
+    <rPh sb="6" eb="8">
+      <t>ヨウケン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>第5章</t>
+    <rPh sb="0" eb="1">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ショウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>5-1</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>データ項目定義</t>
+    <rPh sb="3" eb="7">
+      <t>コウモクテイギ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>第6章</t>
+    <rPh sb="0" eb="1">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ショウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>6-1</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>リスク・課題</t>
+    <rPh sb="4" eb="6">
+      <t>カダイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>渡辺のぞみ</t>
+    <rPh sb="0" eb="2">
+      <t>ワタナベ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="179" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -1498,7 +1721,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1828,13 +2051,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1940,9 +2185,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2063,18 +2305,174 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2090,117 +2488,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2228,12 +2515,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2243,32 +2524,47 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2678,44 +2974,44 @@
       <c r="P5" s="8"/>
     </row>
     <row r="6" spans="1:16" ht="39" customHeight="1">
-      <c r="A6" s="85"/>
-      <c r="B6" s="86"/>
-      <c r="C6" s="87"/>
-      <c r="D6" s="88" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" s="88"/>
-      <c r="F6" s="88"/>
-      <c r="G6" s="88"/>
-      <c r="H6" s="88"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="88"/>
-      <c r="K6" s="88"/>
-      <c r="L6" s="88"/>
-      <c r="M6" s="88"/>
-      <c r="N6" s="86"/>
-      <c r="O6" s="87"/>
-      <c r="P6" s="85"/>
+      <c r="A6" s="78"/>
+      <c r="B6" s="79"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="81" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="81"/>
+      <c r="K6" s="81"/>
+      <c r="L6" s="81"/>
+      <c r="M6" s="81"/>
+      <c r="N6" s="79"/>
+      <c r="O6" s="80"/>
+      <c r="P6" s="78"/>
     </row>
     <row r="7" spans="1:16" ht="39" customHeight="1">
-      <c r="A7" s="85"/>
-      <c r="B7" s="86"/>
-      <c r="C7" s="87"/>
-      <c r="D7" s="88" t="s">
+      <c r="A7" s="78"/>
+      <c r="B7" s="79"/>
+      <c r="C7" s="80"/>
+      <c r="D7" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="88"/>
-      <c r="F7" s="88"/>
-      <c r="G7" s="88"/>
-      <c r="H7" s="88"/>
-      <c r="I7" s="88"/>
-      <c r="J7" s="88"/>
-      <c r="K7" s="88"/>
-      <c r="L7" s="88"/>
-      <c r="M7" s="88"/>
-      <c r="N7" s="86"/>
-      <c r="O7" s="87"/>
-      <c r="P7" s="85"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="81"/>
+      <c r="K7" s="81"/>
+      <c r="L7" s="81"/>
+      <c r="M7" s="81"/>
+      <c r="N7" s="79"/>
+      <c r="O7" s="80"/>
+      <c r="P7" s="78"/>
     </row>
     <row r="8" spans="1:16" ht="18.5" thickBot="1">
       <c r="A8" s="8"/>
@@ -2777,16 +3073,16 @@
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
-      <c r="F11" s="89" t="s">
+      <c r="F11" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="90"/>
-      <c r="H11" s="91" t="s">
-        <v>74</v>
-      </c>
-      <c r="I11" s="92"/>
-      <c r="J11" s="92"/>
-      <c r="K11" s="92"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="84" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" s="85"/>
+      <c r="J11" s="85"/>
+      <c r="K11" s="85"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -2799,16 +3095,16 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
-      <c r="F12" s="89" t="s">
+      <c r="F12" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="90"/>
-      <c r="H12" s="143">
+      <c r="G12" s="83"/>
+      <c r="H12" s="86">
         <v>46265</v>
       </c>
-      <c r="I12" s="144"/>
-      <c r="J12" s="144"/>
-      <c r="K12" s="144"/>
+      <c r="I12" s="87"/>
+      <c r="J12" s="87"/>
+      <c r="K12" s="87"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
@@ -2821,16 +3117,16 @@
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
-      <c r="F13" s="89" t="s">
+      <c r="F13" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="90"/>
-      <c r="H13" s="143">
-        <v>46268</v>
-      </c>
-      <c r="I13" s="144"/>
-      <c r="J13" s="144"/>
-      <c r="K13" s="144"/>
+      <c r="G13" s="83"/>
+      <c r="H13" s="86">
+        <v>46273</v>
+      </c>
+      <c r="I13" s="87"/>
+      <c r="J13" s="87"/>
+      <c r="K13" s="87"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
@@ -2843,14 +3139,14 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
-      <c r="F14" s="89" t="s">
+      <c r="F14" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="90"/>
-      <c r="H14" s="91"/>
-      <c r="I14" s="92"/>
-      <c r="J14" s="92"/>
-      <c r="K14" s="92"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="84"/>
+      <c r="I14" s="85"/>
+      <c r="J14" s="85"/>
+      <c r="K14" s="85"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
@@ -3015,52 +3311,56 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="95" t="s">
+      <c r="B1" s="89"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="97"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="95"/>
+      <c r="L1" s="95"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="95"/>
+      <c r="O1" s="96"/>
       <c r="P1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="101"/>
-      <c r="R1" s="102"/>
+      <c r="Q1" s="100" t="s">
+        <v>127</v>
+      </c>
+      <c r="R1" s="101"/>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="78"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="100"/>
+      <c r="A2" s="91"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="98"/>
+      <c r="K2" s="98"/>
+      <c r="L2" s="98"/>
+      <c r="M2" s="98"/>
+      <c r="N2" s="98"/>
+      <c r="O2" s="99"/>
       <c r="P2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="101"/>
-      <c r="R2" s="102"/>
+      <c r="Q2" s="102">
+        <v>46273</v>
+      </c>
+      <c r="R2" s="103"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="2"/>
@@ -3086,427 +3386,447 @@
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="103" t="s">
+      <c r="B4" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="104"/>
-      <c r="D4" s="103" t="s">
+      <c r="C4" s="105"/>
+      <c r="D4" s="104" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="104"/>
-      <c r="F4" s="103" t="s">
+      <c r="E4" s="105"/>
+      <c r="F4" s="104" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="105"/>
-      <c r="H4" s="104"/>
-      <c r="I4" s="103" t="s">
+      <c r="G4" s="106"/>
+      <c r="H4" s="105"/>
+      <c r="I4" s="104" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="105"/>
-      <c r="K4" s="105"/>
-      <c r="L4" s="105"/>
-      <c r="M4" s="105"/>
-      <c r="N4" s="105"/>
-      <c r="O4" s="105"/>
-      <c r="P4" s="105"/>
-      <c r="Q4" s="105"/>
-      <c r="R4" s="104"/>
-    </row>
-    <row r="5" spans="1:18">
+      <c r="J4" s="106"/>
+      <c r="K4" s="106"/>
+      <c r="L4" s="106"/>
+      <c r="M4" s="106"/>
+      <c r="N4" s="106"/>
+      <c r="O4" s="106"/>
+      <c r="P4" s="106"/>
+      <c r="Q4" s="106"/>
+      <c r="R4" s="105"/>
+    </row>
+    <row r="5" spans="1:18" ht="36" customHeight="1">
       <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="106"/>
-      <c r="C5" s="107"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="107"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="108"/>
-      <c r="H5" s="107"/>
-      <c r="I5" s="109"/>
-      <c r="J5" s="110"/>
-      <c r="K5" s="110"/>
-      <c r="L5" s="110"/>
-      <c r="M5" s="110"/>
-      <c r="N5" s="110"/>
-      <c r="O5" s="110"/>
-      <c r="P5" s="110"/>
-      <c r="Q5" s="110"/>
-      <c r="R5" s="111"/>
-    </row>
-    <row r="6" spans="1:18">
+      <c r="B5" s="107">
+        <v>46260</v>
+      </c>
+      <c r="C5" s="108"/>
+      <c r="D5" s="109" t="s">
+        <v>127</v>
+      </c>
+      <c r="E5" s="110"/>
+      <c r="F5" s="111" t="s">
+        <v>128</v>
+      </c>
+      <c r="G5" s="112"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="114"/>
+      <c r="J5" s="115"/>
+      <c r="K5" s="115"/>
+      <c r="L5" s="115"/>
+      <c r="M5" s="115"/>
+      <c r="N5" s="115"/>
+      <c r="O5" s="115"/>
+      <c r="P5" s="115"/>
+      <c r="Q5" s="115"/>
+      <c r="R5" s="116"/>
+    </row>
+    <row r="6" spans="1:18" ht="36" customHeight="1">
       <c r="A6" s="6">
         <v>2</v>
       </c>
-      <c r="B6" s="112"/>
-      <c r="C6" s="113"/>
-      <c r="D6" s="112"/>
-      <c r="E6" s="113"/>
-      <c r="F6" s="112"/>
-      <c r="G6" s="114"/>
-      <c r="H6" s="113"/>
-      <c r="I6" s="115"/>
-      <c r="J6" s="116"/>
-      <c r="K6" s="116"/>
-      <c r="L6" s="116"/>
-      <c r="M6" s="116"/>
-      <c r="N6" s="116"/>
-      <c r="O6" s="116"/>
-      <c r="P6" s="116"/>
-      <c r="Q6" s="116"/>
-      <c r="R6" s="117"/>
-    </row>
-    <row r="7" spans="1:18">
+      <c r="B6" s="117">
+        <v>46266</v>
+      </c>
+      <c r="C6" s="118"/>
+      <c r="D6" s="119" t="s">
+        <v>127</v>
+      </c>
+      <c r="E6" s="118"/>
+      <c r="F6" s="120" t="s">
+        <v>129</v>
+      </c>
+      <c r="G6" s="121"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="120" t="s">
+        <v>131</v>
+      </c>
+      <c r="J6" s="123"/>
+      <c r="K6" s="123"/>
+      <c r="L6" s="123"/>
+      <c r="M6" s="123"/>
+      <c r="N6" s="123"/>
+      <c r="O6" s="123"/>
+      <c r="P6" s="123"/>
+      <c r="Q6" s="123"/>
+      <c r="R6" s="124"/>
+    </row>
+    <row r="7" spans="1:18" ht="36" customHeight="1">
       <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="112"/>
-      <c r="C7" s="113"/>
-      <c r="D7" s="112"/>
-      <c r="E7" s="113"/>
-      <c r="F7" s="112"/>
-      <c r="G7" s="114"/>
-      <c r="H7" s="113"/>
-      <c r="I7" s="115"/>
-      <c r="J7" s="116"/>
-      <c r="K7" s="116"/>
-      <c r="L7" s="116"/>
-      <c r="M7" s="116"/>
-      <c r="N7" s="116"/>
-      <c r="O7" s="116"/>
-      <c r="P7" s="116"/>
-      <c r="Q7" s="116"/>
-      <c r="R7" s="117"/>
-    </row>
-    <row r="8" spans="1:18">
+      <c r="B7" s="117">
+        <v>46268</v>
+      </c>
+      <c r="C7" s="118"/>
+      <c r="D7" s="119" t="s">
+        <v>127</v>
+      </c>
+      <c r="E7" s="118"/>
+      <c r="F7" s="120" t="s">
+        <v>130</v>
+      </c>
+      <c r="G7" s="121"/>
+      <c r="H7" s="122"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="123"/>
+      <c r="K7" s="123"/>
+      <c r="L7" s="123"/>
+      <c r="M7" s="123"/>
+      <c r="N7" s="123"/>
+      <c r="O7" s="123"/>
+      <c r="P7" s="123"/>
+      <c r="Q7" s="123"/>
+      <c r="R7" s="124"/>
+    </row>
+    <row r="8" spans="1:18" ht="36" customHeight="1">
       <c r="A8" s="6">
         <v>4</v>
       </c>
-      <c r="B8" s="112"/>
-      <c r="C8" s="113"/>
-      <c r="D8" s="112"/>
-      <c r="E8" s="113"/>
-      <c r="F8" s="112"/>
-      <c r="G8" s="114"/>
-      <c r="H8" s="113"/>
-      <c r="I8" s="115"/>
-      <c r="J8" s="116"/>
-      <c r="K8" s="116"/>
-      <c r="L8" s="116"/>
-      <c r="M8" s="116"/>
-      <c r="N8" s="116"/>
-      <c r="O8" s="116"/>
-      <c r="P8" s="116"/>
-      <c r="Q8" s="116"/>
-      <c r="R8" s="117"/>
+      <c r="B8" s="119"/>
+      <c r="C8" s="118"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="126"/>
+      <c r="H8" s="118"/>
+      <c r="I8" s="125"/>
+      <c r="J8" s="123"/>
+      <c r="K8" s="123"/>
+      <c r="L8" s="123"/>
+      <c r="M8" s="123"/>
+      <c r="N8" s="123"/>
+      <c r="O8" s="123"/>
+      <c r="P8" s="123"/>
+      <c r="Q8" s="123"/>
+      <c r="R8" s="124"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="6">
         <v>5</v>
       </c>
-      <c r="B9" s="112"/>
-      <c r="C9" s="113"/>
-      <c r="D9" s="112"/>
-      <c r="E9" s="113"/>
-      <c r="F9" s="112"/>
-      <c r="G9" s="114"/>
-      <c r="H9" s="113"/>
-      <c r="I9" s="115"/>
-      <c r="J9" s="116"/>
-      <c r="K9" s="116"/>
-      <c r="L9" s="116"/>
-      <c r="M9" s="116"/>
-      <c r="N9" s="116"/>
-      <c r="O9" s="116"/>
-      <c r="P9" s="116"/>
-      <c r="Q9" s="116"/>
-      <c r="R9" s="117"/>
+      <c r="B9" s="119"/>
+      <c r="C9" s="118"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="118"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="126"/>
+      <c r="H9" s="118"/>
+      <c r="I9" s="125"/>
+      <c r="J9" s="123"/>
+      <c r="K9" s="123"/>
+      <c r="L9" s="123"/>
+      <c r="M9" s="123"/>
+      <c r="N9" s="123"/>
+      <c r="O9" s="123"/>
+      <c r="P9" s="123"/>
+      <c r="Q9" s="123"/>
+      <c r="R9" s="124"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="6">
         <v>6</v>
       </c>
-      <c r="B10" s="112"/>
-      <c r="C10" s="113"/>
-      <c r="D10" s="112"/>
-      <c r="E10" s="113"/>
-      <c r="F10" s="112"/>
-      <c r="G10" s="114"/>
-      <c r="H10" s="113"/>
-      <c r="I10" s="115"/>
-      <c r="J10" s="116"/>
-      <c r="K10" s="116"/>
-      <c r="L10" s="116"/>
-      <c r="M10" s="116"/>
-      <c r="N10" s="116"/>
-      <c r="O10" s="116"/>
-      <c r="P10" s="116"/>
-      <c r="Q10" s="116"/>
-      <c r="R10" s="117"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="118"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="118"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="126"/>
+      <c r="H10" s="118"/>
+      <c r="I10" s="125"/>
+      <c r="J10" s="123"/>
+      <c r="K10" s="123"/>
+      <c r="L10" s="123"/>
+      <c r="M10" s="123"/>
+      <c r="N10" s="123"/>
+      <c r="O10" s="123"/>
+      <c r="P10" s="123"/>
+      <c r="Q10" s="123"/>
+      <c r="R10" s="124"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="6">
         <v>7</v>
       </c>
-      <c r="B11" s="112"/>
-      <c r="C11" s="113"/>
-      <c r="D11" s="112"/>
-      <c r="E11" s="113"/>
-      <c r="F11" s="112"/>
-      <c r="G11" s="114"/>
-      <c r="H11" s="113"/>
-      <c r="I11" s="115"/>
-      <c r="J11" s="116"/>
-      <c r="K11" s="116"/>
-      <c r="L11" s="116"/>
-      <c r="M11" s="116"/>
-      <c r="N11" s="116"/>
-      <c r="O11" s="116"/>
-      <c r="P11" s="116"/>
-      <c r="Q11" s="116"/>
-      <c r="R11" s="117"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="118"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="118"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="126"/>
+      <c r="H11" s="118"/>
+      <c r="I11" s="125"/>
+      <c r="J11" s="123"/>
+      <c r="K11" s="123"/>
+      <c r="L11" s="123"/>
+      <c r="M11" s="123"/>
+      <c r="N11" s="123"/>
+      <c r="O11" s="123"/>
+      <c r="P11" s="123"/>
+      <c r="Q11" s="123"/>
+      <c r="R11" s="124"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="6">
         <v>8</v>
       </c>
-      <c r="B12" s="112"/>
-      <c r="C12" s="113"/>
-      <c r="D12" s="112"/>
-      <c r="E12" s="113"/>
-      <c r="F12" s="112"/>
-      <c r="G12" s="114"/>
-      <c r="H12" s="113"/>
-      <c r="I12" s="115"/>
-      <c r="J12" s="116"/>
-      <c r="K12" s="116"/>
-      <c r="L12" s="116"/>
-      <c r="M12" s="116"/>
-      <c r="N12" s="116"/>
-      <c r="O12" s="116"/>
-      <c r="P12" s="116"/>
-      <c r="Q12" s="116"/>
-      <c r="R12" s="117"/>
+      <c r="B12" s="119"/>
+      <c r="C12" s="118"/>
+      <c r="D12" s="119"/>
+      <c r="E12" s="118"/>
+      <c r="F12" s="119"/>
+      <c r="G12" s="126"/>
+      <c r="H12" s="118"/>
+      <c r="I12" s="125"/>
+      <c r="J12" s="123"/>
+      <c r="K12" s="123"/>
+      <c r="L12" s="123"/>
+      <c r="M12" s="123"/>
+      <c r="N12" s="123"/>
+      <c r="O12" s="123"/>
+      <c r="P12" s="123"/>
+      <c r="Q12" s="123"/>
+      <c r="R12" s="124"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="6">
         <v>9</v>
       </c>
-      <c r="B13" s="112"/>
-      <c r="C13" s="113"/>
-      <c r="D13" s="112"/>
-      <c r="E13" s="113"/>
-      <c r="F13" s="112"/>
-      <c r="G13" s="114"/>
-      <c r="H13" s="113"/>
-      <c r="I13" s="115"/>
-      <c r="J13" s="116"/>
-      <c r="K13" s="116"/>
-      <c r="L13" s="116"/>
-      <c r="M13" s="116"/>
-      <c r="N13" s="116"/>
-      <c r="O13" s="116"/>
-      <c r="P13" s="116"/>
-      <c r="Q13" s="116"/>
-      <c r="R13" s="117"/>
+      <c r="B13" s="119"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="119"/>
+      <c r="E13" s="118"/>
+      <c r="F13" s="119"/>
+      <c r="G13" s="126"/>
+      <c r="H13" s="118"/>
+      <c r="I13" s="125"/>
+      <c r="J13" s="123"/>
+      <c r="K13" s="123"/>
+      <c r="L13" s="123"/>
+      <c r="M13" s="123"/>
+      <c r="N13" s="123"/>
+      <c r="O13" s="123"/>
+      <c r="P13" s="123"/>
+      <c r="Q13" s="123"/>
+      <c r="R13" s="124"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="6">
         <v>10</v>
       </c>
-      <c r="B14" s="112"/>
-      <c r="C14" s="113"/>
-      <c r="D14" s="112"/>
-      <c r="E14" s="113"/>
-      <c r="F14" s="112"/>
-      <c r="G14" s="114"/>
-      <c r="H14" s="113"/>
-      <c r="I14" s="115"/>
-      <c r="J14" s="116"/>
-      <c r="K14" s="116"/>
-      <c r="L14" s="116"/>
-      <c r="M14" s="116"/>
-      <c r="N14" s="116"/>
-      <c r="O14" s="116"/>
-      <c r="P14" s="116"/>
-      <c r="Q14" s="116"/>
-      <c r="R14" s="117"/>
+      <c r="B14" s="119"/>
+      <c r="C14" s="118"/>
+      <c r="D14" s="119"/>
+      <c r="E14" s="118"/>
+      <c r="F14" s="119"/>
+      <c r="G14" s="126"/>
+      <c r="H14" s="118"/>
+      <c r="I14" s="125"/>
+      <c r="J14" s="123"/>
+      <c r="K14" s="123"/>
+      <c r="L14" s="123"/>
+      <c r="M14" s="123"/>
+      <c r="N14" s="123"/>
+      <c r="O14" s="123"/>
+      <c r="P14" s="123"/>
+      <c r="Q14" s="123"/>
+      <c r="R14" s="124"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="6">
         <v>11</v>
       </c>
-      <c r="B15" s="112"/>
-      <c r="C15" s="113"/>
-      <c r="D15" s="112"/>
-      <c r="E15" s="113"/>
-      <c r="F15" s="112"/>
-      <c r="G15" s="114"/>
-      <c r="H15" s="113"/>
-      <c r="I15" s="115"/>
-      <c r="J15" s="116"/>
-      <c r="K15" s="116"/>
-      <c r="L15" s="116"/>
-      <c r="M15" s="116"/>
-      <c r="N15" s="116"/>
-      <c r="O15" s="116"/>
-      <c r="P15" s="116"/>
-      <c r="Q15" s="116"/>
-      <c r="R15" s="117"/>
+      <c r="B15" s="119"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="119"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="119"/>
+      <c r="G15" s="126"/>
+      <c r="H15" s="118"/>
+      <c r="I15" s="125"/>
+      <c r="J15" s="123"/>
+      <c r="K15" s="123"/>
+      <c r="L15" s="123"/>
+      <c r="M15" s="123"/>
+      <c r="N15" s="123"/>
+      <c r="O15" s="123"/>
+      <c r="P15" s="123"/>
+      <c r="Q15" s="123"/>
+      <c r="R15" s="124"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="6">
         <v>12</v>
       </c>
-      <c r="B16" s="112"/>
-      <c r="C16" s="113"/>
-      <c r="D16" s="112"/>
-      <c r="E16" s="113"/>
-      <c r="F16" s="112"/>
-      <c r="G16" s="114"/>
-      <c r="H16" s="113"/>
-      <c r="I16" s="115"/>
-      <c r="J16" s="116"/>
-      <c r="K16" s="116"/>
-      <c r="L16" s="116"/>
-      <c r="M16" s="116"/>
-      <c r="N16" s="116"/>
-      <c r="O16" s="116"/>
-      <c r="P16" s="116"/>
-      <c r="Q16" s="116"/>
-      <c r="R16" s="117"/>
+      <c r="B16" s="119"/>
+      <c r="C16" s="118"/>
+      <c r="D16" s="119"/>
+      <c r="E16" s="118"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="126"/>
+      <c r="H16" s="118"/>
+      <c r="I16" s="125"/>
+      <c r="J16" s="123"/>
+      <c r="K16" s="123"/>
+      <c r="L16" s="123"/>
+      <c r="M16" s="123"/>
+      <c r="N16" s="123"/>
+      <c r="O16" s="123"/>
+      <c r="P16" s="123"/>
+      <c r="Q16" s="123"/>
+      <c r="R16" s="124"/>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="6">
         <v>13</v>
       </c>
-      <c r="B17" s="112"/>
-      <c r="C17" s="113"/>
-      <c r="D17" s="112"/>
-      <c r="E17" s="113"/>
-      <c r="F17" s="112"/>
-      <c r="G17" s="114"/>
-      <c r="H17" s="113"/>
-      <c r="I17" s="115"/>
-      <c r="J17" s="116"/>
-      <c r="K17" s="116"/>
-      <c r="L17" s="116"/>
-      <c r="M17" s="116"/>
-      <c r="N17" s="116"/>
-      <c r="O17" s="116"/>
-      <c r="P17" s="116"/>
-      <c r="Q17" s="116"/>
-      <c r="R17" s="117"/>
+      <c r="B17" s="119"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="119"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="119"/>
+      <c r="G17" s="126"/>
+      <c r="H17" s="118"/>
+      <c r="I17" s="125"/>
+      <c r="J17" s="123"/>
+      <c r="K17" s="123"/>
+      <c r="L17" s="123"/>
+      <c r="M17" s="123"/>
+      <c r="N17" s="123"/>
+      <c r="O17" s="123"/>
+      <c r="P17" s="123"/>
+      <c r="Q17" s="123"/>
+      <c r="R17" s="124"/>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="6">
         <v>14</v>
       </c>
-      <c r="B18" s="112"/>
-      <c r="C18" s="113"/>
-      <c r="D18" s="112"/>
-      <c r="E18" s="113"/>
-      <c r="F18" s="112"/>
-      <c r="G18" s="114"/>
-      <c r="H18" s="113"/>
-      <c r="I18" s="115"/>
-      <c r="J18" s="116"/>
-      <c r="K18" s="116"/>
-      <c r="L18" s="116"/>
-      <c r="M18" s="116"/>
-      <c r="N18" s="116"/>
-      <c r="O18" s="116"/>
-      <c r="P18" s="116"/>
-      <c r="Q18" s="116"/>
-      <c r="R18" s="117"/>
+      <c r="B18" s="119"/>
+      <c r="C18" s="118"/>
+      <c r="D18" s="119"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="119"/>
+      <c r="G18" s="126"/>
+      <c r="H18" s="118"/>
+      <c r="I18" s="125"/>
+      <c r="J18" s="123"/>
+      <c r="K18" s="123"/>
+      <c r="L18" s="123"/>
+      <c r="M18" s="123"/>
+      <c r="N18" s="123"/>
+      <c r="O18" s="123"/>
+      <c r="P18" s="123"/>
+      <c r="Q18" s="123"/>
+      <c r="R18" s="124"/>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="6">
         <v>15</v>
       </c>
-      <c r="B19" s="112"/>
-      <c r="C19" s="113"/>
-      <c r="D19" s="112"/>
-      <c r="E19" s="113"/>
-      <c r="F19" s="112"/>
-      <c r="G19" s="114"/>
-      <c r="H19" s="113"/>
-      <c r="I19" s="115"/>
-      <c r="J19" s="116"/>
-      <c r="K19" s="116"/>
-      <c r="L19" s="116"/>
-      <c r="M19" s="116"/>
-      <c r="N19" s="116"/>
-      <c r="O19" s="116"/>
-      <c r="P19" s="116"/>
-      <c r="Q19" s="116"/>
-      <c r="R19" s="117"/>
+      <c r="B19" s="119"/>
+      <c r="C19" s="118"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="118"/>
+      <c r="F19" s="119"/>
+      <c r="G19" s="126"/>
+      <c r="H19" s="118"/>
+      <c r="I19" s="125"/>
+      <c r="J19" s="123"/>
+      <c r="K19" s="123"/>
+      <c r="L19" s="123"/>
+      <c r="M19" s="123"/>
+      <c r="N19" s="123"/>
+      <c r="O19" s="123"/>
+      <c r="P19" s="123"/>
+      <c r="Q19" s="123"/>
+      <c r="R19" s="124"/>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="6">
         <v>16</v>
       </c>
-      <c r="B20" s="112"/>
-      <c r="C20" s="113"/>
-      <c r="D20" s="112"/>
-      <c r="E20" s="113"/>
-      <c r="F20" s="112"/>
-      <c r="G20" s="114"/>
-      <c r="H20" s="113"/>
-      <c r="I20" s="115"/>
-      <c r="J20" s="116"/>
-      <c r="K20" s="116"/>
-      <c r="L20" s="116"/>
-      <c r="M20" s="116"/>
-      <c r="N20" s="116"/>
-      <c r="O20" s="116"/>
-      <c r="P20" s="116"/>
-      <c r="Q20" s="116"/>
-      <c r="R20" s="117"/>
+      <c r="B20" s="119"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="119"/>
+      <c r="E20" s="118"/>
+      <c r="F20" s="119"/>
+      <c r="G20" s="126"/>
+      <c r="H20" s="118"/>
+      <c r="I20" s="125"/>
+      <c r="J20" s="123"/>
+      <c r="K20" s="123"/>
+      <c r="L20" s="123"/>
+      <c r="M20" s="123"/>
+      <c r="N20" s="123"/>
+      <c r="O20" s="123"/>
+      <c r="P20" s="123"/>
+      <c r="Q20" s="123"/>
+      <c r="R20" s="124"/>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="6">
         <v>17</v>
       </c>
-      <c r="B21" s="112"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="112"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="112"/>
-      <c r="G21" s="114"/>
-      <c r="H21" s="113"/>
-      <c r="I21" s="115"/>
-      <c r="J21" s="116"/>
-      <c r="K21" s="116"/>
-      <c r="L21" s="116"/>
-      <c r="M21" s="116"/>
-      <c r="N21" s="116"/>
-      <c r="O21" s="116"/>
-      <c r="P21" s="116"/>
-      <c r="Q21" s="116"/>
-      <c r="R21" s="117"/>
+      <c r="B21" s="119"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="119"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="119"/>
+      <c r="G21" s="126"/>
+      <c r="H21" s="118"/>
+      <c r="I21" s="125"/>
+      <c r="J21" s="123"/>
+      <c r="K21" s="123"/>
+      <c r="L21" s="123"/>
+      <c r="M21" s="123"/>
+      <c r="N21" s="123"/>
+      <c r="O21" s="123"/>
+      <c r="P21" s="123"/>
+      <c r="Q21" s="123"/>
+      <c r="R21" s="124"/>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="6">
         <v>18</v>
       </c>
-      <c r="B22" s="112"/>
-      <c r="C22" s="113"/>
-      <c r="D22" s="112"/>
-      <c r="E22" s="113"/>
-      <c r="F22" s="112"/>
-      <c r="G22" s="114"/>
-      <c r="H22" s="113"/>
-      <c r="I22" s="115"/>
-      <c r="J22" s="116"/>
-      <c r="K22" s="116"/>
-      <c r="L22" s="116"/>
-      <c r="M22" s="116"/>
-      <c r="N22" s="116"/>
-      <c r="O22" s="116"/>
-      <c r="P22" s="116"/>
-      <c r="Q22" s="116"/>
-      <c r="R22" s="117"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="118"/>
+      <c r="D22" s="119"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="119"/>
+      <c r="G22" s="126"/>
+      <c r="H22" s="118"/>
+      <c r="I22" s="125"/>
+      <c r="J22" s="123"/>
+      <c r="K22" s="123"/>
+      <c r="L22" s="123"/>
+      <c r="M22" s="123"/>
+      <c r="N22" s="123"/>
+      <c r="O22" s="123"/>
+      <c r="P22" s="123"/>
+      <c r="Q22" s="123"/>
+      <c r="R22" s="124"/>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="5"/>
@@ -3738,60 +4058,62 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDFF7F1E-AE30-4269-AC6F-F8A3C5E0A4BA}">
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:17">
-      <c r="A1" s="76" t="s">
+    <row r="1" spans="1:16">
+      <c r="A1" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="76" t="s">
+      <c r="B1" s="90"/>
+      <c r="C1" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="93"/>
-      <c r="J1" s="93"/>
-      <c r="K1" s="93"/>
-      <c r="L1" s="93"/>
-      <c r="M1" s="93"/>
-      <c r="N1" s="24" t="s">
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="89"/>
+      <c r="L1" s="90"/>
+      <c r="M1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="22"/>
-      <c r="P1" s="25" t="s">
+      <c r="N1" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="O1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="26"/>
-    </row>
-    <row r="2" spans="1:17">
-      <c r="A2" s="78"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94"/>
-      <c r="L2" s="94"/>
-      <c r="M2" s="94"/>
-      <c r="N2" s="27" t="s">
+      <c r="P1" s="161">
+        <v>46273</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="91"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="93"/>
+      <c r="M2" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="28"/>
-      <c r="P2" s="29" t="s">
+      <c r="N2" s="28"/>
+      <c r="O2" s="160" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="30"/>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="P2" s="30"/>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="32"/>
       <c r="B3" s="33"/>
       <c r="C3" s="32"/>
@@ -3807,497 +4129,410 @@
       <c r="M3" s="32"/>
       <c r="N3" s="32"/>
       <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="P3" s="156"/>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="118" t="s">
+      <c r="B4" s="127" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="119"/>
-      <c r="D4" s="119"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="120"/>
-      <c r="H4" s="35" t="s">
+      <c r="C4" s="128"/>
+      <c r="D4" s="128"/>
+      <c r="E4" s="128"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="159" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="127" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="128"/>
+      <c r="L4" s="128"/>
+      <c r="M4" s="128"/>
+      <c r="N4" s="128"/>
+      <c r="O4" s="129"/>
+      <c r="P4" s="157"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="16"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="35"/>
+      <c r="N5" s="35"/>
+      <c r="O5" s="35"/>
+      <c r="P5" s="157"/>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="31"/>
-      <c r="J4" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" s="118" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="119"/>
-      <c r="M4" s="119"/>
-      <c r="N4" s="119"/>
-      <c r="O4" s="119"/>
-      <c r="P4" s="120"/>
-      <c r="Q4" s="35" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17">
-      <c r="A5" s="16"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-    </row>
-    <row r="6" spans="1:17">
-      <c r="A6" s="37" t="s">
-        <v>19</v>
-      </c>
       <c r="B6" s="31" t="s">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
       <c r="E6" s="31"/>
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>
-      <c r="H6" s="37">
-        <v>1</v>
-      </c>
-      <c r="I6" s="7"/>
-      <c r="J6" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" s="31" t="s">
-        <v>20</v>
-      </c>
+      <c r="H6" s="7"/>
+      <c r="I6" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="J6" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="K6" s="31"/>
       <c r="L6" s="31"/>
       <c r="M6" s="31"/>
       <c r="N6" s="31"/>
       <c r="O6" s="31"/>
-      <c r="P6" s="31"/>
-      <c r="Q6" s="37">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17">
-      <c r="A7" s="37">
-        <v>1.1000000000000001</v>
+      <c r="P6" s="158"/>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="154" t="s">
+        <v>132</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>22</v>
+        <v>138</v>
       </c>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
       <c r="E7" s="31"/>
       <c r="F7" s="31"/>
       <c r="G7" s="31"/>
-      <c r="H7" s="37">
-        <v>2</v>
-      </c>
-      <c r="I7" s="7"/>
-      <c r="J7" s="37">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="K7" s="31" t="s">
-        <v>22</v>
-      </c>
+      <c r="H7" s="7"/>
+      <c r="I7" s="154" t="s">
+        <v>152</v>
+      </c>
+      <c r="J7" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="K7" s="31"/>
       <c r="L7" s="31"/>
       <c r="M7" s="31"/>
       <c r="N7" s="31"/>
       <c r="O7" s="31"/>
-      <c r="P7" s="31"/>
-      <c r="Q7" s="37">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17">
-      <c r="A8" s="37">
-        <v>1.2</v>
-      </c>
-      <c r="B8" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="37">
-        <v>3</v>
-      </c>
-      <c r="I8" s="7"/>
-      <c r="J8" s="37">
-        <v>4.2</v>
-      </c>
-      <c r="K8" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="L8" s="36"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="37">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17">
-      <c r="A9" s="37">
-        <v>1.3</v>
+      <c r="P7" s="158"/>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="154" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="154" t="s">
+        <v>154</v>
+      </c>
+      <c r="J8" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="K8" s="35"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="35"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="158"/>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="154" t="s">
+        <v>134</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>24</v>
+        <v>139</v>
       </c>
       <c r="C9" s="31"/>
       <c r="D9" s="31"/>
       <c r="E9" s="31"/>
       <c r="F9" s="31"/>
       <c r="G9" s="31"/>
-      <c r="H9" s="37">
-        <v>4</v>
-      </c>
-      <c r="I9" s="7"/>
-      <c r="J9" s="37">
-        <v>4.3</v>
-      </c>
-      <c r="K9" s="31" t="s">
-        <v>24</v>
-      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="154"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
       <c r="L9" s="31"/>
       <c r="M9" s="31"/>
       <c r="N9" s="31"/>
       <c r="O9" s="31"/>
-      <c r="P9" s="31"/>
-      <c r="Q9" s="37">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17">
-      <c r="A10" s="37">
-        <v>1.4</v>
+      <c r="P9" s="158"/>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="154" t="s">
+        <v>135</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="C10" s="31"/>
       <c r="D10" s="31"/>
       <c r="E10" s="31"/>
       <c r="F10" s="31"/>
       <c r="G10" s="31"/>
-      <c r="H10" s="37">
-        <v>5</v>
-      </c>
-      <c r="I10" s="7"/>
-      <c r="J10" s="37">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="K10" s="31" t="s">
-        <v>25</v>
-      </c>
+      <c r="H10" s="7"/>
+      <c r="I10" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
       <c r="L10" s="31"/>
       <c r="M10" s="31"/>
       <c r="N10" s="31"/>
       <c r="O10" s="31"/>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="37">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17">
-      <c r="A11" s="37">
+      <c r="P10" s="158"/>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="36">
         <v>1.5</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>26</v>
+        <v>141</v>
       </c>
       <c r="C11" s="31"/>
       <c r="D11" s="31"/>
       <c r="E11" s="31"/>
       <c r="F11" s="31"/>
       <c r="G11" s="31"/>
-      <c r="H11" s="37">
-        <v>6</v>
-      </c>
-      <c r="I11" s="7"/>
-      <c r="J11" s="37">
-        <v>4.5</v>
-      </c>
-      <c r="K11" s="31" t="s">
-        <v>26</v>
-      </c>
+      <c r="H11" s="7"/>
+      <c r="I11" s="155" t="s">
+        <v>157</v>
+      </c>
+      <c r="J11" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="K11" s="31"/>
       <c r="L11" s="31"/>
       <c r="M11" s="31"/>
       <c r="N11" s="31"/>
       <c r="O11" s="31"/>
-      <c r="P11" s="31"/>
-      <c r="Q11" s="37">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17">
-      <c r="A12" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="31" t="s">
-        <v>28</v>
-      </c>
+      <c r="P11" s="158"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="36"/>
+      <c r="B12" s="31"/>
       <c r="C12" s="31"/>
       <c r="D12" s="31"/>
       <c r="E12" s="31"/>
       <c r="F12" s="31"/>
       <c r="G12" s="31"/>
-      <c r="H12" s="37">
-        <v>7</v>
-      </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="31"/>
       <c r="K12" s="31"/>
       <c r="L12" s="31"/>
       <c r="M12" s="31"/>
       <c r="N12" s="31"/>
       <c r="O12" s="31"/>
-      <c r="P12" s="31"/>
-      <c r="Q12" s="31"/>
-    </row>
-    <row r="13" spans="1:17">
-      <c r="A13" s="37">
-        <v>2.1</v>
+      <c r="P12" s="158"/>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="36" t="s">
+        <v>20</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="C13" s="31"/>
       <c r="D13" s="31"/>
       <c r="E13" s="31"/>
       <c r="F13" s="31"/>
       <c r="G13" s="31"/>
-      <c r="H13" s="37">
-        <v>8</v>
-      </c>
-      <c r="I13" s="31"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7" t="s">
+        <v>159</v>
+      </c>
       <c r="J13" s="31"/>
       <c r="K13" s="31"/>
       <c r="L13" s="31"/>
       <c r="M13" s="31"/>
       <c r="N13" s="31"/>
       <c r="O13" s="31"/>
-      <c r="P13" s="31"/>
-      <c r="Q13" s="31"/>
-    </row>
-    <row r="14" spans="1:17">
-      <c r="A14" s="37">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="B14" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="37">
-        <v>9</v>
-      </c>
-      <c r="I14" s="31"/>
-      <c r="J14" s="31"/>
+      <c r="P13" s="156"/>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="155" t="s">
+        <v>144</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="155" t="s">
+        <v>160</v>
+      </c>
+      <c r="J14" s="31" t="s">
+        <v>161</v>
+      </c>
       <c r="K14" s="31"/>
       <c r="L14" s="31"/>
       <c r="M14" s="31"/>
       <c r="N14" s="31"/>
       <c r="O14" s="31"/>
       <c r="P14" s="31"/>
-      <c r="Q14" s="31"/>
-    </row>
-    <row r="15" spans="1:17">
-      <c r="A15" s="37">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="B15" s="31" t="s">
-        <v>24</v>
-      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="155"/>
+      <c r="B15" s="31"/>
       <c r="C15" s="31"/>
       <c r="D15" s="31"/>
       <c r="E15" s="31"/>
       <c r="F15" s="31"/>
       <c r="G15" s="31"/>
-      <c r="H15" s="37">
-        <v>10</v>
-      </c>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
       <c r="K15" s="31"/>
       <c r="L15" s="31"/>
       <c r="M15" s="31"/>
       <c r="N15" s="31"/>
       <c r="O15" s="31"/>
       <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-    </row>
-    <row r="16" spans="1:17">
-      <c r="A16" s="37">
-        <v>2.4</v>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="36" t="s">
+        <v>21</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>25</v>
+        <v>145</v>
       </c>
       <c r="C16" s="31"/>
       <c r="D16" s="31"/>
       <c r="E16" s="31"/>
       <c r="F16" s="31"/>
       <c r="G16" s="31"/>
-      <c r="H16" s="37">
-        <v>11</v>
-      </c>
+      <c r="H16" s="7"/>
       <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
+      <c r="J16" s="31"/>
       <c r="K16" s="31"/>
       <c r="L16" s="31"/>
       <c r="M16" s="31"/>
       <c r="N16" s="31"/>
       <c r="O16" s="31"/>
       <c r="P16" s="31"/>
-      <c r="Q16" s="31"/>
-    </row>
-    <row r="17" spans="1:17">
-      <c r="A17" s="37">
-        <v>2.5</v>
+    </row>
+    <row r="17" spans="1:16" ht="26.5">
+      <c r="A17" s="155" t="s">
+        <v>146</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>26</v>
+        <v>147</v>
       </c>
       <c r="C17" s="31"/>
       <c r="D17" s="31"/>
       <c r="E17" s="31"/>
       <c r="F17" s="31"/>
       <c r="G17" s="31"/>
-      <c r="H17" s="37">
-        <v>12</v>
-      </c>
+      <c r="H17" s="7"/>
       <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="31"/>
-      <c r="M17" s="31"/>
-      <c r="N17" s="31"/>
-      <c r="O17" s="31"/>
-      <c r="P17" s="31"/>
-      <c r="Q17" s="31"/>
-    </row>
-    <row r="18" spans="1:17">
-      <c r="A18" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="37">
-        <v>13</v>
-      </c>
+      <c r="J17" s="37"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="37"/>
+      <c r="M17" s="37"/>
+      <c r="N17" s="37"/>
+      <c r="O17" s="37"/>
+      <c r="P17" s="37"/>
+    </row>
+    <row r="18" spans="1:16" ht="26.5">
+      <c r="A18" s="155" t="s">
+        <v>148</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="7"/>
       <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="31"/>
-      <c r="L18" s="31"/>
-      <c r="M18" s="31"/>
-      <c r="N18" s="31"/>
-      <c r="O18" s="31"/>
-      <c r="P18" s="31"/>
-      <c r="Q18" s="31"/>
-    </row>
-    <row r="19" spans="1:17" ht="26.5">
-      <c r="A19" s="37">
-        <v>3.1</v>
-      </c>
-      <c r="B19" s="31" t="s">
-        <v>29</v>
-      </c>
+      <c r="J18" s="37"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="37"/>
+      <c r="M18" s="37"/>
+      <c r="N18" s="37"/>
+      <c r="O18" s="37"/>
+      <c r="P18" s="37"/>
+    </row>
+    <row r="19" spans="1:16" ht="26.5">
+      <c r="A19" s="36"/>
+      <c r="B19" s="31"/>
       <c r="C19" s="31"/>
       <c r="D19" s="31"/>
       <c r="E19" s="31"/>
       <c r="F19" s="31"/>
       <c r="G19" s="31"/>
-      <c r="H19" s="37">
-        <v>14</v>
-      </c>
+      <c r="H19" s="7"/>
       <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="38"/>
-      <c r="L19" s="38"/>
-      <c r="M19" s="38"/>
-      <c r="N19" s="38"/>
-      <c r="O19" s="38"/>
-      <c r="P19" s="38"/>
-      <c r="Q19" s="38"/>
-    </row>
-    <row r="20" spans="1:17" ht="26.5">
-      <c r="A20" s="37">
-        <v>3.2</v>
-      </c>
-      <c r="B20" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="37">
-        <v>15</v>
-      </c>
+      <c r="J19" s="37"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="37"/>
+      <c r="M19" s="37"/>
+      <c r="N19" s="37"/>
+      <c r="O19" s="37"/>
+      <c r="P19" s="37"/>
+    </row>
+    <row r="20" spans="1:16" ht="26.5">
+      <c r="A20" s="37"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="7"/>
       <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="38"/>
-      <c r="L20" s="38"/>
-      <c r="M20" s="38"/>
-      <c r="N20" s="38"/>
-      <c r="O20" s="38"/>
-      <c r="P20" s="38"/>
-      <c r="Q20" s="38"/>
-    </row>
-    <row r="21" spans="1:17" ht="26.5">
-      <c r="A21" s="37">
-        <v>3.3</v>
-      </c>
-      <c r="B21" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="37">
-        <v>16</v>
-      </c>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="38"/>
-      <c r="L21" s="38"/>
-      <c r="M21" s="38"/>
-      <c r="N21" s="38"/>
-      <c r="O21" s="38"/>
-      <c r="P21" s="38"/>
-      <c r="Q21" s="38"/>
-    </row>
-    <row r="22" spans="1:17" ht="26.5">
-      <c r="A22" s="38"/>
+      <c r="J20" s="37"/>
+      <c r="K20" s="37"/>
+      <c r="L20" s="37"/>
+      <c r="M20" s="37"/>
+      <c r="N20" s="37"/>
+      <c r="O20" s="37"/>
+      <c r="P20" s="37"/>
+    </row>
+    <row r="21" spans="1:16" ht="26.5">
+      <c r="A21" s="37"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="37"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="37"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="37"/>
+      <c r="M21" s="37"/>
+      <c r="N21" s="37"/>
+      <c r="O21" s="37"/>
+      <c r="P21" s="37"/>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="7"/>
       <c r="B22" s="16"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
@@ -4307,58 +4542,19 @@
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
-      <c r="K22" s="38"/>
-      <c r="L22" s="38"/>
-      <c r="M22" s="38"/>
-      <c r="N22" s="38"/>
-      <c r="O22" s="38"/>
-      <c r="P22" s="38"/>
-      <c r="Q22" s="38"/>
-    </row>
-    <row r="23" spans="1:17" ht="26.5">
-      <c r="A23" s="38"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="38"/>
-      <c r="O23" s="38"/>
-      <c r="P23" s="38"/>
-      <c r="Q23" s="38"/>
-    </row>
-    <row r="24" spans="1:17">
-      <c r="A24" s="7"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:M2"/>
+    <mergeCell ref="C1:L2"/>
     <mergeCell ref="B4:G4"/>
-    <mergeCell ref="K4:P4"/>
+    <mergeCell ref="J4:O4"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4374,82 +4570,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="80" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="81"/>
-      <c r="E1" s="82" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="84"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="131" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="132"/>
+      <c r="E1" s="133" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="135"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="40">
+      <c r="O1" s="39">
         <v>46260</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="78"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="84"/>
+      <c r="A2" s="91"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="134"/>
+      <c r="I2" s="134"/>
+      <c r="J2" s="134"/>
+      <c r="K2" s="135"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
       <c r="M2" s="26" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="N2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="74">
+      <c r="O2" s="73">
         <v>46266</v>
       </c>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="41"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
+      <c r="A3" s="40"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
-      <c r="B4" s="36" t="s">
-        <v>33</v>
+      <c r="B4" s="35" t="s">
+        <v>24</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -4467,80 +4663,80 @@
     </row>
     <row r="5" spans="1:15" ht="18" customHeight="1">
       <c r="A5" s="8"/>
-      <c r="B5" s="122" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" s="122"/>
-      <c r="D5" s="122"/>
-      <c r="E5" s="122"/>
-      <c r="F5" s="122"/>
-      <c r="G5" s="122"/>
-      <c r="H5" s="122"/>
-      <c r="I5" s="122"/>
-      <c r="J5" s="122"/>
-      <c r="K5" s="122"/>
-      <c r="L5" s="122"/>
-      <c r="M5" s="122"/>
-      <c r="N5" s="122"/>
+      <c r="B5" s="136" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="136"/>
+      <c r="G5" s="136"/>
+      <c r="H5" s="136"/>
+      <c r="I5" s="136"/>
+      <c r="J5" s="136"/>
+      <c r="K5" s="136"/>
+      <c r="L5" s="136"/>
+      <c r="M5" s="136"/>
+      <c r="N5" s="136"/>
       <c r="O5" s="8"/>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6" s="36"/>
-      <c r="B6" s="122"/>
-      <c r="C6" s="122"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="122"/>
-      <c r="J6" s="122"/>
-      <c r="K6" s="122"/>
-      <c r="L6" s="122"/>
-      <c r="M6" s="122"/>
-      <c r="N6" s="122"/>
-      <c r="O6" s="36"/>
+      <c r="A6" s="35"/>
+      <c r="B6" s="136"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="136"/>
+      <c r="F6" s="136"/>
+      <c r="G6" s="136"/>
+      <c r="H6" s="136"/>
+      <c r="I6" s="136"/>
+      <c r="J6" s="136"/>
+      <c r="K6" s="136"/>
+      <c r="L6" s="136"/>
+      <c r="M6" s="136"/>
+      <c r="N6" s="136"/>
+      <c r="O6" s="35"/>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="36"/>
-      <c r="B7" s="36" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
+      <c r="A7" s="35"/>
+      <c r="B7" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
       <c r="I7" s="8"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="35"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="35"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="36"/>
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
+      <c r="A8" s="35"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
       <c r="I8" s="8"/>
-      <c r="J8" s="36"/>
-      <c r="K8" s="36"/>
-      <c r="L8" s="36"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="35"/>
+      <c r="O8" s="35"/>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="36"/>
-      <c r="B9" s="36" t="s">
-        <v>34</v>
+      <c r="A9" s="35"/>
+      <c r="B9" s="35" t="s">
+        <v>25</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -4554,12 +4750,12 @@
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
       <c r="N9" s="8"/>
-      <c r="O9" s="36"/>
+      <c r="O9" s="35"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="36"/>
+      <c r="A10" s="35"/>
       <c r="B10" s="8" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -4573,10 +4769,10 @@
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
-      <c r="O10" s="36"/>
+      <c r="O10" s="35"/>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11" s="36"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -4590,232 +4786,232 @@
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
-      <c r="O11" s="36"/>
+      <c r="O11" s="35"/>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="36"/>
-      <c r="B12" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
+      <c r="A12" s="35"/>
+      <c r="B12" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
     </row>
     <row r="13" spans="1:15" ht="18" customHeight="1">
-      <c r="A13" s="36"/>
-      <c r="B13" s="121" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="121"/>
-      <c r="D13" s="121"/>
-      <c r="E13" s="121"/>
-      <c r="F13" s="121"/>
-      <c r="G13" s="121"/>
-      <c r="H13" s="121"/>
-      <c r="I13" s="121"/>
-      <c r="J13" s="121"/>
-      <c r="K13" s="121"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="121"/>
-      <c r="N13" s="121"/>
-      <c r="O13" s="121"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="130" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="130"/>
+      <c r="D13" s="130"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="130"/>
+      <c r="G13" s="130"/>
+      <c r="H13" s="130"/>
+      <c r="I13" s="130"/>
+      <c r="J13" s="130"/>
+      <c r="K13" s="130"/>
+      <c r="L13" s="130"/>
+      <c r="M13" s="130"/>
+      <c r="N13" s="130"/>
+      <c r="O13" s="130"/>
     </row>
     <row r="14" spans="1:15" ht="18" customHeight="1">
-      <c r="A14" s="36"/>
-      <c r="B14" s="121" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="121"/>
-      <c r="D14" s="121"/>
-      <c r="E14" s="121"/>
-      <c r="F14" s="121"/>
-      <c r="G14" s="121"/>
-      <c r="H14" s="121"/>
-      <c r="I14" s="121"/>
-      <c r="J14" s="121"/>
-      <c r="K14" s="121"/>
-      <c r="L14" s="121"/>
-      <c r="M14" s="121"/>
-      <c r="N14" s="121"/>
-      <c r="O14" s="121"/>
+      <c r="A14" s="35"/>
+      <c r="B14" s="130" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="130"/>
+      <c r="D14" s="130"/>
+      <c r="E14" s="130"/>
+      <c r="F14" s="130"/>
+      <c r="G14" s="130"/>
+      <c r="H14" s="130"/>
+      <c r="I14" s="130"/>
+      <c r="J14" s="130"/>
+      <c r="K14" s="130"/>
+      <c r="L14" s="130"/>
+      <c r="M14" s="130"/>
+      <c r="N14" s="130"/>
+      <c r="O14" s="130"/>
     </row>
     <row r="15" spans="1:15" ht="18" customHeight="1">
-      <c r="A15" s="36"/>
-      <c r="B15" s="121" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" s="121"/>
-      <c r="D15" s="121"/>
-      <c r="E15" s="121"/>
-      <c r="F15" s="121"/>
-      <c r="G15" s="121"/>
-      <c r="H15" s="121"/>
-      <c r="I15" s="121"/>
-      <c r="J15" s="121"/>
-      <c r="K15" s="121"/>
-      <c r="L15" s="121"/>
-      <c r="M15" s="121"/>
-      <c r="N15" s="121"/>
-      <c r="O15" s="121"/>
+      <c r="A15" s="35"/>
+      <c r="B15" s="130" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="130"/>
+      <c r="D15" s="130"/>
+      <c r="E15" s="130"/>
+      <c r="F15" s="130"/>
+      <c r="G15" s="130"/>
+      <c r="H15" s="130"/>
+      <c r="I15" s="130"/>
+      <c r="J15" s="130"/>
+      <c r="K15" s="130"/>
+      <c r="L15" s="130"/>
+      <c r="M15" s="130"/>
+      <c r="N15" s="130"/>
+      <c r="O15" s="130"/>
     </row>
     <row r="16" spans="1:15" ht="18" customHeight="1">
-      <c r="A16" s="36"/>
-      <c r="B16" s="121" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" s="121"/>
-      <c r="D16" s="121"/>
-      <c r="E16" s="121"/>
-      <c r="F16" s="121"/>
-      <c r="G16" s="121"/>
-      <c r="H16" s="121"/>
-      <c r="I16" s="121"/>
-      <c r="J16" s="121"/>
-      <c r="K16" s="121"/>
-      <c r="L16" s="121"/>
-      <c r="M16" s="121"/>
-      <c r="N16" s="121"/>
-      <c r="O16" s="121"/>
+      <c r="A16" s="35"/>
+      <c r="B16" s="130" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="130"/>
+      <c r="D16" s="130"/>
+      <c r="E16" s="130"/>
+      <c r="F16" s="130"/>
+      <c r="G16" s="130"/>
+      <c r="H16" s="130"/>
+      <c r="I16" s="130"/>
+      <c r="J16" s="130"/>
+      <c r="K16" s="130"/>
+      <c r="L16" s="130"/>
+      <c r="M16" s="130"/>
+      <c r="N16" s="130"/>
+      <c r="O16" s="130"/>
     </row>
     <row r="17" spans="1:15" ht="18" customHeight="1">
-      <c r="A17" s="36"/>
-      <c r="B17" s="121" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="121"/>
-      <c r="H17" s="121"/>
-      <c r="I17" s="121"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="121"/>
-      <c r="L17" s="121"/>
-      <c r="M17" s="121"/>
-      <c r="N17" s="121"/>
-      <c r="O17" s="121"/>
+      <c r="A17" s="35"/>
+      <c r="B17" s="130" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="130"/>
+      <c r="D17" s="130"/>
+      <c r="E17" s="130"/>
+      <c r="F17" s="130"/>
+      <c r="G17" s="130"/>
+      <c r="H17" s="130"/>
+      <c r="I17" s="130"/>
+      <c r="J17" s="130"/>
+      <c r="K17" s="130"/>
+      <c r="L17" s="130"/>
+      <c r="M17" s="130"/>
+      <c r="N17" s="130"/>
+      <c r="O17" s="130"/>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="36"/>
-      <c r="B18" s="121"/>
-      <c r="C18" s="121"/>
-      <c r="D18" s="121"/>
-      <c r="E18" s="121"/>
-      <c r="F18" s="121"/>
-      <c r="G18" s="121"/>
-      <c r="H18" s="121"/>
-      <c r="I18" s="121"/>
-      <c r="J18" s="121"/>
-      <c r="K18" s="121"/>
-      <c r="L18" s="121"/>
-      <c r="M18" s="121"/>
-      <c r="N18" s="121"/>
-      <c r="O18" s="121"/>
+      <c r="A18" s="35"/>
+      <c r="B18" s="130"/>
+      <c r="C18" s="130"/>
+      <c r="D18" s="130"/>
+      <c r="E18" s="130"/>
+      <c r="F18" s="130"/>
+      <c r="G18" s="130"/>
+      <c r="H18" s="130"/>
+      <c r="I18" s="130"/>
+      <c r="J18" s="130"/>
+      <c r="K18" s="130"/>
+      <c r="L18" s="130"/>
+      <c r="M18" s="130"/>
+      <c r="N18" s="130"/>
+      <c r="O18" s="130"/>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="36"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="42"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="42"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="42"/>
-      <c r="O19" s="42"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="41"/>
+      <c r="M19" s="41"/>
+      <c r="N19" s="41"/>
+      <c r="O19" s="41"/>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="36"/>
-      <c r="B20" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="44"/>
-      <c r="L20" s="44"/>
-      <c r="M20" s="44"/>
-      <c r="N20" s="44"/>
-      <c r="O20" s="44"/>
+      <c r="A20" s="35"/>
+      <c r="B20" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="43"/>
+      <c r="M20" s="43"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="43"/>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="36"/>
-      <c r="B21" s="43" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="44"/>
-      <c r="K21" s="44"/>
-      <c r="L21" s="44"/>
-      <c r="M21" s="44"/>
-      <c r="N21" s="44"/>
-      <c r="O21" s="44"/>
+      <c r="A21" s="35"/>
+      <c r="B21" s="42" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="43"/>
+      <c r="M21" s="43"/>
+      <c r="N21" s="43"/>
+      <c r="O21" s="43"/>
     </row>
     <row r="22" spans="1:15">
-      <c r="A22" s="36"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="44"/>
-      <c r="K22" s="44"/>
-      <c r="L22" s="44"/>
-      <c r="M22" s="44"/>
-      <c r="N22" s="44"/>
-      <c r="O22" s="44"/>
+      <c r="A22" s="35"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="43"/>
+      <c r="M22" s="43"/>
+      <c r="N22" s="43"/>
+      <c r="O22" s="43"/>
     </row>
     <row r="23" spans="1:15" ht="26.5">
-      <c r="A23" s="45"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="45"/>
-      <c r="M23" s="45"/>
-      <c r="N23" s="45"/>
-      <c r="O23" s="45"/>
+      <c r="A23" s="44"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="44"/>
+      <c r="L23" s="44"/>
+      <c r="M23" s="44"/>
+      <c r="N23" s="44"/>
+      <c r="O23" s="44"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="8" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
@@ -4833,81 +5029,81 @@
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
-      <c r="B25" s="46" t="s">
-        <v>95</v>
-      </c>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="47"/>
-      <c r="J25" s="47"/>
-      <c r="K25" s="47"/>
-      <c r="L25" s="47"/>
-      <c r="M25" s="47"/>
-      <c r="N25" s="47"/>
-      <c r="O25" s="47"/>
+      <c r="B25" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="46"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="46"/>
+      <c r="K25" s="46"/>
+      <c r="L25" s="46"/>
+      <c r="M25" s="46"/>
+      <c r="N25" s="46"/>
+      <c r="O25" s="46"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
-      <c r="B26" s="46" t="s">
-        <v>96</v>
-      </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="47"/>
-      <c r="K26" s="47"/>
-      <c r="L26" s="47"/>
-      <c r="M26" s="47"/>
-      <c r="N26" s="47"/>
-      <c r="O26" s="47"/>
+      <c r="B26" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="46"/>
+      <c r="K26" s="46"/>
+      <c r="L26" s="46"/>
+      <c r="M26" s="46"/>
+      <c r="N26" s="46"/>
+      <c r="O26" s="46"/>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
-      <c r="B27" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="C27" s="47"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="47"/>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="47"/>
-      <c r="O27" s="47"/>
+      <c r="B27" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="46"/>
+      <c r="J27" s="46"/>
+      <c r="K27" s="46"/>
+      <c r="L27" s="46"/>
+      <c r="M27" s="46"/>
+      <c r="N27" s="46"/>
+      <c r="O27" s="46"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
-      <c r="B28" s="47"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="47"/>
-      <c r="I28" s="47"/>
-      <c r="J28" s="47"/>
-      <c r="K28" s="47"/>
-      <c r="L28" s="47"/>
-      <c r="M28" s="47"/>
-      <c r="N28" s="47"/>
-      <c r="O28" s="47"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+      <c r="I28" s="46"/>
+      <c r="J28" s="46"/>
+      <c r="K28" s="46"/>
+      <c r="L28" s="46"/>
+      <c r="M28" s="46"/>
+      <c r="N28" s="46"/>
+      <c r="O28" s="46"/>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
       <c r="B29" s="8" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
@@ -4925,8 +5121,8 @@
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
-      <c r="B30" s="48" t="s">
-        <v>102</v>
+      <c r="B30" s="47" t="s">
+        <v>88</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -4944,8 +5140,8 @@
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="8"/>
-      <c r="B31" s="48" t="s">
-        <v>101</v>
+      <c r="B31" s="47" t="s">
+        <v>87</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -4963,8 +5159,8 @@
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
-      <c r="B32" s="48" t="s">
-        <v>98</v>
+      <c r="B32" s="47" t="s">
+        <v>84</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -4982,7 +5178,7 @@
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="8"/>
-      <c r="B33" s="48"/>
+      <c r="B33" s="47"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
@@ -5026,82 +5222,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="80" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="81"/>
-      <c r="E1" s="82" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="84"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="131" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="132"/>
+      <c r="E1" s="133" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="135"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="40">
+      <c r="O1" s="39">
         <v>46260</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="78"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="84"/>
+      <c r="A2" s="91"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="134"/>
+      <c r="I2" s="134"/>
+      <c r="J2" s="134"/>
+      <c r="K2" s="135"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
       <c r="M2" s="26" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="N2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="75">
+      <c r="O2" s="74">
         <v>46266</v>
       </c>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="41"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
+      <c r="A3" s="40"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
-      <c r="B4" s="36" t="s">
-        <v>41</v>
+      <c r="B4" s="35" t="s">
+        <v>32</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -5119,86 +5315,86 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
-      <c r="L5" s="49"/>
-      <c r="M5" s="49"/>
-      <c r="N5" s="49"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="48"/>
       <c r="O5" s="8"/>
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1">
-      <c r="A6" s="36"/>
-      <c r="B6" s="125" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="126"/>
-      <c r="D6" s="50" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="49"/>
-      <c r="M6" s="49"/>
-      <c r="N6" s="49"/>
-      <c r="O6" s="36"/>
+      <c r="A6" s="35"/>
+      <c r="B6" s="139" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="140"/>
+      <c r="D6" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="50"/>
+      <c r="J6" s="50"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="48"/>
+      <c r="N6" s="48"/>
+      <c r="O6" s="35"/>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="36"/>
-      <c r="B7" s="123" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" s="124"/>
-      <c r="D7" s="54" t="s">
-        <v>84</v>
-      </c>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="52"/>
+      <c r="A7" s="35"/>
+      <c r="B7" s="137" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="138"/>
+      <c r="D7" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="51"/>
       <c r="I7" s="23"/>
-      <c r="J7" s="55"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="35"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="35"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="36"/>
-      <c r="B8" s="123" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="124"/>
+      <c r="A8" s="35"/>
+      <c r="B8" s="137" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="138"/>
       <c r="D8" s="17" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
       <c r="G8" s="23"/>
-      <c r="H8" s="52"/>
+      <c r="H8" s="51"/>
       <c r="I8" s="23"/>
       <c r="J8" s="23"/>
-      <c r="K8" s="57"/>
+      <c r="K8" s="56"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
       <c r="N8" s="8"/>
-      <c r="O8" s="36"/>
+      <c r="O8" s="35"/>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="36"/>
+      <c r="A9" s="35"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -5212,10 +5408,10 @@
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
       <c r="N9" s="8"/>
-      <c r="O9" s="36"/>
+      <c r="O9" s="35"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="36"/>
+      <c r="A10" s="35"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -5229,211 +5425,211 @@
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
-      <c r="O10" s="36"/>
+      <c r="O10" s="35"/>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11" s="36"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
+      <c r="A11" s="35"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="35"/>
+      <c r="O11" s="35"/>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="36"/>
-      <c r="B12" s="44"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="44"/>
-      <c r="M12" s="44"/>
-      <c r="N12" s="44"/>
-      <c r="O12" s="44"/>
+      <c r="A12" s="35"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="36"/>
-      <c r="B13" s="44"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="44"/>
-      <c r="K13" s="44"/>
-      <c r="L13" s="44"/>
-      <c r="M13" s="44"/>
-      <c r="N13" s="44"/>
-      <c r="O13" s="44"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+      <c r="L13" s="43"/>
+      <c r="M13" s="43"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
     </row>
     <row r="14" spans="1:15">
-      <c r="A14" s="36"/>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="44"/>
-      <c r="L14" s="44"/>
-      <c r="M14" s="44"/>
-      <c r="N14" s="44"/>
-      <c r="O14" s="44"/>
+      <c r="A14" s="35"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
+      <c r="L14" s="43"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="O14" s="43"/>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15" s="36"/>
-      <c r="B15" s="44"/>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="44"/>
-      <c r="I15" s="44"/>
-      <c r="J15" s="44"/>
-      <c r="K15" s="44"/>
-      <c r="L15" s="44"/>
-      <c r="M15" s="44"/>
-      <c r="N15" s="44"/>
-      <c r="O15" s="44"/>
+      <c r="A15" s="35"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+      <c r="L15" s="43"/>
+      <c r="M15" s="43"/>
+      <c r="N15" s="43"/>
+      <c r="O15" s="43"/>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="36"/>
-      <c r="B16" s="44"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="44"/>
-      <c r="K16" s="44"/>
-      <c r="L16" s="44"/>
-      <c r="M16" s="44"/>
-      <c r="N16" s="44"/>
-      <c r="O16" s="44"/>
+      <c r="A16" s="35"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+      <c r="L16" s="43"/>
+      <c r="M16" s="43"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="43"/>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="36"/>
-      <c r="B17" s="44"/>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="44"/>
-      <c r="K17" s="44"/>
-      <c r="L17" s="44"/>
-      <c r="M17" s="44"/>
-      <c r="N17" s="44"/>
-      <c r="O17" s="44"/>
+      <c r="A17" s="35"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="43"/>
+      <c r="L17" s="43"/>
+      <c r="M17" s="43"/>
+      <c r="N17" s="43"/>
+      <c r="O17" s="43"/>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="36"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="42"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="42"/>
-      <c r="M18" s="42"/>
-      <c r="N18" s="42"/>
-      <c r="O18" s="42"/>
+      <c r="A18" s="35"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="41"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="41"/>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="36"/>
-      <c r="B19" s="43"/>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44"/>
-      <c r="K19" s="44"/>
-      <c r="L19" s="44"/>
-      <c r="M19" s="44"/>
-      <c r="N19" s="44"/>
-      <c r="O19" s="44"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="43"/>
+      <c r="M19" s="43"/>
+      <c r="N19" s="43"/>
+      <c r="O19" s="43"/>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="36"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="44"/>
-      <c r="L20" s="44"/>
-      <c r="M20" s="44"/>
-      <c r="N20" s="44"/>
-      <c r="O20" s="44"/>
+      <c r="A20" s="35"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="43"/>
+      <c r="M20" s="43"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="43"/>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="36"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="44"/>
-      <c r="K21" s="44"/>
-      <c r="L21" s="44"/>
-      <c r="M21" s="44"/>
-      <c r="N21" s="44"/>
-      <c r="O21" s="44"/>
+      <c r="A21" s="35"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="43"/>
+      <c r="M21" s="43"/>
+      <c r="N21" s="43"/>
+      <c r="O21" s="43"/>
     </row>
     <row r="22" spans="1:15" ht="26.5">
-      <c r="A22" s="45"/>
-      <c r="B22" s="45"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="45"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="45"/>
-      <c r="M22" s="45"/>
-      <c r="N22" s="45"/>
-      <c r="O22" s="45"/>
+      <c r="A22" s="44"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="44"/>
+      <c r="K22" s="44"/>
+      <c r="L22" s="44"/>
+      <c r="M22" s="44"/>
+      <c r="N22" s="44"/>
+      <c r="O22" s="44"/>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="8"/>
@@ -5454,88 +5650,88 @@
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
-      <c r="B24" s="58"/>
-      <c r="C24" s="47"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="47"/>
-      <c r="J24" s="47"/>
-      <c r="K24" s="47"/>
-      <c r="L24" s="47"/>
-      <c r="M24" s="47"/>
-      <c r="N24" s="47"/>
-      <c r="O24" s="47"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="46"/>
+      <c r="L24" s="46"/>
+      <c r="M24" s="46"/>
+      <c r="N24" s="46"/>
+      <c r="O24" s="46"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
-      <c r="B25" s="58"/>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="47"/>
-      <c r="J25" s="47"/>
-      <c r="K25" s="47"/>
-      <c r="L25" s="47"/>
-      <c r="M25" s="47"/>
-      <c r="N25" s="47"/>
-      <c r="O25" s="47"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="46"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="46"/>
+      <c r="K25" s="46"/>
+      <c r="L25" s="46"/>
+      <c r="M25" s="46"/>
+      <c r="N25" s="46"/>
+      <c r="O25" s="46"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
-      <c r="B26" s="58"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="47"/>
-      <c r="K26" s="47"/>
-      <c r="L26" s="47"/>
-      <c r="M26" s="47"/>
-      <c r="N26" s="47"/>
-      <c r="O26" s="47"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="46"/>
+      <c r="K26" s="46"/>
+      <c r="L26" s="46"/>
+      <c r="M26" s="46"/>
+      <c r="N26" s="46"/>
+      <c r="O26" s="46"/>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
-      <c r="B27" s="58"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="47"/>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="47"/>
-      <c r="O27" s="47"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="46"/>
+      <c r="J27" s="46"/>
+      <c r="K27" s="46"/>
+      <c r="L27" s="46"/>
+      <c r="M27" s="46"/>
+      <c r="N27" s="46"/>
+      <c r="O27" s="46"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
-      <c r="B28" s="47"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="47"/>
-      <c r="I28" s="47"/>
-      <c r="J28" s="47"/>
-      <c r="K28" s="47"/>
-      <c r="L28" s="47"/>
-      <c r="M28" s="47"/>
-      <c r="N28" s="47"/>
-      <c r="O28" s="47"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="46"/>
+      <c r="J28" s="46"/>
+      <c r="K28" s="46"/>
+      <c r="L28" s="46"/>
+      <c r="M28" s="46"/>
+      <c r="N28" s="46"/>
+      <c r="O28" s="46"/>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
@@ -5647,47 +5843,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="80" t="s">
-        <v>30</v>
-      </c>
-      <c r="D1" s="81"/>
-      <c r="E1" s="72" t="s">
-        <v>90</v>
-      </c>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="73"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="131" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="132"/>
+      <c r="E1" s="71" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="72"/>
       <c r="K1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="L1" s="26" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="M1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="129">
+      <c r="N1" s="143">
         <v>46260</v>
       </c>
-      <c r="O1" s="129"/>
+      <c r="O1" s="143"/>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="78"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="84"/>
+      <c r="A2" s="91"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="134"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="134"/>
+      <c r="I2" s="134"/>
+      <c r="J2" s="135"/>
       <c r="K2" s="29" t="s">
         <v>14</v>
       </c>
@@ -5695,30 +5891,30 @@
       <c r="M2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="130"/>
-      <c r="O2" s="130"/>
+      <c r="N2" s="144"/>
+      <c r="O2" s="144"/>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="41"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="36"/>
+      <c r="A3" s="40"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="35"/>
       <c r="O3" s="7"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
-      <c r="B4" s="36" t="s">
-        <v>66</v>
+      <c r="B4" s="35" t="s">
+        <v>52</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -5736,138 +5932,138 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
-      <c r="L5" s="49"/>
-      <c r="M5" s="49"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="48"/>
       <c r="N5" s="8"/>
       <c r="O5" s="7"/>
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1">
-      <c r="A6" s="36"/>
-      <c r="B6" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="50" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="50" t="s">
+      <c r="A6" s="35"/>
+      <c r="B6" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="49" t="s">
+        <v>55</v>
+      </c>
+      <c r="L6" s="55"/>
+      <c r="M6" s="70"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="7"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="35"/>
+      <c r="B7" s="53" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="68" t="s">
+        <v>72</v>
+      </c>
+      <c r="F7" s="23"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="69" t="s">
         <v>69</v>
       </c>
-      <c r="L6" s="56"/>
-      <c r="M6" s="71"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="7"/>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="36"/>
-      <c r="B7" s="54" t="s">
-        <v>85</v>
-      </c>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="69" t="s">
-        <v>86</v>
-      </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="70" t="s">
-        <v>83</v>
-      </c>
-      <c r="L7" s="56"/>
+      <c r="L7" s="55"/>
       <c r="M7" s="31"/>
-      <c r="N7" s="36"/>
+      <c r="N7" s="35"/>
       <c r="O7" s="7"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="36"/>
-      <c r="B8" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="C8" s="55"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="69" t="s">
-        <v>91</v>
+      <c r="A8" s="35"/>
+      <c r="B8" s="53" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="68" t="s">
+        <v>77</v>
       </c>
       <c r="F8" s="23"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="55"/>
-      <c r="I8" s="55"/>
-      <c r="J8" s="56"/>
-      <c r="K8" s="70" t="s">
-        <v>92</v>
-      </c>
-      <c r="L8" s="56"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="55"/>
+      <c r="K8" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="L8" s="55"/>
       <c r="M8" s="31"/>
-      <c r="N8" s="36"/>
+      <c r="N8" s="35"/>
       <c r="O8" s="7"/>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="36"/>
-      <c r="B9" s="54" t="s">
-        <v>87</v>
-      </c>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="69" t="s">
-        <v>89</v>
+      <c r="A9" s="35"/>
+      <c r="B9" s="53" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="68" t="s">
+        <v>75</v>
       </c>
       <c r="F9" s="23"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="55"/>
-      <c r="J9" s="56"/>
-      <c r="K9" s="70" t="s">
-        <v>92</v>
-      </c>
-      <c r="L9" s="56"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="55"/>
+      <c r="K9" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="L9" s="55"/>
       <c r="M9" s="31"/>
-      <c r="N9" s="36"/>
+      <c r="N9" s="35"/>
       <c r="O9" s="7"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="36"/>
+      <c r="A10" s="35"/>
       <c r="B10" s="17" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
-      <c r="E10" s="69" t="s">
-        <v>94</v>
+      <c r="E10" s="68" t="s">
+        <v>80</v>
       </c>
       <c r="F10" s="23"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="55"/>
-      <c r="J10" s="56"/>
-      <c r="K10" s="127" t="s">
-        <v>109</v>
-      </c>
-      <c r="L10" s="128"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="55"/>
+      <c r="K10" s="141" t="s">
+        <v>95</v>
+      </c>
+      <c r="L10" s="142"/>
       <c r="M10" s="31"/>
-      <c r="N10" s="36"/>
+      <c r="N10" s="35"/>
       <c r="O10" s="7"/>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11" s="36"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -5880,188 +6076,188 @@
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
-      <c r="N11" s="36"/>
+      <c r="N11" s="35"/>
       <c r="O11" s="7"/>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="36"/>
-      <c r="B12" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
+      <c r="A12" s="35"/>
+      <c r="B12" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="36"/>
-      <c r="B13" s="43" t="s">
-        <v>99</v>
-      </c>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
-      <c r="N13" s="43"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="42" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="42"/>
       <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15">
-      <c r="A14" s="36"/>
+      <c r="A14" s="35"/>
       <c r="B14" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
+        <v>89</v>
+      </c>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="42"/>
+      <c r="N14" s="42"/>
       <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15" s="36"/>
+      <c r="A15" s="35"/>
       <c r="B15" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="58"/>
-      <c r="H15" s="58"/>
-      <c r="I15" s="58"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="43"/>
+        <v>90</v>
+      </c>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="57"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="57"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="42"/>
+      <c r="M15" s="42"/>
+      <c r="N15" s="42"/>
       <c r="O15" s="7"/>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="36"/>
+      <c r="A16" s="35"/>
       <c r="B16" s="7"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="58"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="43"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="42"/>
+      <c r="M16" s="42"/>
+      <c r="N16" s="42"/>
       <c r="O16" s="7"/>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="36"/>
+      <c r="A17" s="35"/>
       <c r="B17" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="58"/>
-      <c r="H17" s="58"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="43"/>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
+        <v>97</v>
+      </c>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="42"/>
+      <c r="M17" s="42"/>
+      <c r="N17" s="42"/>
       <c r="O17" s="7"/>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="36"/>
-      <c r="B18" s="58" t="s">
-        <v>107</v>
-      </c>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="43"/>
-      <c r="M18" s="43"/>
-      <c r="N18" s="43"/>
+      <c r="A18" s="35"/>
+      <c r="B18" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="42"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="42"/>
       <c r="O18" s="7"/>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="36"/>
+      <c r="A19" s="35"/>
       <c r="B19" s="31"/>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="43"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
-      <c r="L19" s="43"/>
-      <c r="M19" s="43"/>
-      <c r="N19" s="43"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="42"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="42"/>
       <c r="O19" s="7"/>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="36"/>
+      <c r="A20" s="35"/>
       <c r="B20" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="43"/>
-      <c r="N20" s="43"/>
+        <v>91</v>
+      </c>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="42"/>
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" ht="18" customHeight="1">
-      <c r="A21" s="45"/>
-      <c r="B21" s="58" t="s">
-        <v>106</v>
-      </c>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
-      <c r="K21" s="45"/>
-      <c r="L21" s="45"/>
-      <c r="M21" s="45"/>
-      <c r="N21" s="45"/>
+      <c r="A21" s="44"/>
+      <c r="B21" s="57" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="44"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="44"/>
       <c r="O21" s="7"/>
     </row>
     <row r="22" spans="1:15" ht="18" customHeight="1">
       <c r="A22" s="8"/>
       <c r="B22" s="7" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
@@ -6079,91 +6275,91 @@
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="8"/>
-      <c r="B23" s="58"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="47"/>
-      <c r="K23" s="47"/>
-      <c r="L23" s="47"/>
-      <c r="M23" s="47"/>
-      <c r="N23" s="47"/>
+      <c r="B23" s="57"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="46"/>
+      <c r="J23" s="46"/>
+      <c r="K23" s="46"/>
+      <c r="L23" s="46"/>
+      <c r="M23" s="46"/>
+      <c r="N23" s="46"/>
       <c r="O23" s="7"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
-      <c r="B24" s="43" t="s">
-        <v>112</v>
-      </c>
-      <c r="C24" s="47"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="47"/>
-      <c r="J24" s="47"/>
-      <c r="K24" s="47"/>
-      <c r="L24" s="47"/>
-      <c r="M24" s="47"/>
-      <c r="N24" s="47"/>
+      <c r="B24" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="46"/>
+      <c r="L24" s="46"/>
+      <c r="M24" s="46"/>
+      <c r="N24" s="46"/>
       <c r="O24" s="7"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
-      <c r="B25" s="58" t="s">
-        <v>113</v>
-      </c>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="47"/>
-      <c r="J25" s="47"/>
-      <c r="K25" s="47"/>
-      <c r="L25" s="47"/>
-      <c r="M25" s="47"/>
-      <c r="N25" s="47"/>
+      <c r="B25" s="57" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" s="46"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="46"/>
+      <c r="K25" s="46"/>
+      <c r="L25" s="46"/>
+      <c r="M25" s="46"/>
+      <c r="N25" s="46"/>
       <c r="O25" s="7"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
-      <c r="B26" s="58"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="47"/>
-      <c r="K26" s="47"/>
-      <c r="L26" s="47"/>
-      <c r="M26" s="47"/>
-      <c r="N26" s="47"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="46"/>
+      <c r="K26" s="46"/>
+      <c r="L26" s="46"/>
+      <c r="M26" s="46"/>
+      <c r="N26" s="46"/>
       <c r="O26" s="7"/>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
-      <c r="B27" s="47"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="47"/>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="47"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="46"/>
+      <c r="J27" s="46"/>
+      <c r="K27" s="46"/>
+      <c r="L27" s="46"/>
+      <c r="M27" s="46"/>
+      <c r="N27" s="46"/>
       <c r="O27" s="7"/>
     </row>
     <row r="28" spans="1:15">
@@ -6272,78 +6468,78 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="80" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="81"/>
-      <c r="E1" s="82" t="s">
-        <v>45</v>
-      </c>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="84"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="131" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="132"/>
+      <c r="E1" s="133" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="135"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="40">
+      <c r="O1" s="39">
         <v>46001</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="78"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="84"/>
+      <c r="A2" s="91"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="134"/>
+      <c r="I2" s="134"/>
+      <c r="J2" s="134"/>
+      <c r="K2" s="135"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="59"/>
+      <c r="M2" s="58"/>
       <c r="N2" s="25" t="s">
         <v>15</v>
       </c>
       <c r="O2" s="26"/>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="41"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
+      <c r="A3" s="40"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
-      <c r="B4" s="36" t="s">
-        <v>46</v>
+      <c r="B4" s="35" t="s">
+        <v>37</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -6361,9 +6557,7 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
-      <c r="B5" s="31" t="s">
-        <v>47</v>
-      </c>
+      <c r="B5" s="31"/>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
       <c r="E5" s="31"/>
@@ -6379,7 +6573,7 @@
       <c r="O5" s="8"/>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6" s="36"/>
+      <c r="A6" s="35"/>
       <c r="B6" s="31"/>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
@@ -6393,51 +6587,47 @@
       <c r="L6" s="31"/>
       <c r="M6" s="31"/>
       <c r="N6" s="31"/>
-      <c r="O6" s="36"/>
+      <c r="O6" s="35"/>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="36"/>
-      <c r="B7" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
+      <c r="A7" s="35"/>
+      <c r="B7" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
       <c r="I7" s="8"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="35"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="35"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="36"/>
-      <c r="B8" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
+      <c r="A8" s="35"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
       <c r="I8" s="8"/>
-      <c r="J8" s="36"/>
-      <c r="K8" s="36"/>
-      <c r="L8" s="36"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="35"/>
+      <c r="O8" s="35"/>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="36"/>
-      <c r="B9" s="36" t="s">
-        <v>50</v>
-      </c>
+      <c r="A9" s="35"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -6450,10 +6640,10 @@
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
       <c r="N9" s="8"/>
-      <c r="O9" s="36"/>
+      <c r="O9" s="35"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="36"/>
+      <c r="A10" s="35"/>
       <c r="B10" s="7"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -6467,12 +6657,12 @@
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
-      <c r="O10" s="36"/>
+      <c r="O10" s="35"/>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11" s="36"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="8" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -6486,215 +6676,211 @@
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
-      <c r="O11" s="36"/>
+      <c r="O11" s="35"/>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="36"/>
-      <c r="B12" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
+      <c r="A12" s="35"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="42"/>
+      <c r="O13" s="42"/>
     </row>
     <row r="14" spans="1:15">
-      <c r="A14" s="36"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
+      <c r="A14" s="35"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="42"/>
+      <c r="N14" s="42"/>
+      <c r="O14" s="42"/>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15" s="36"/>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="43"/>
+      <c r="A15" s="35"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="42"/>
+      <c r="M15" s="42"/>
+      <c r="N15" s="42"/>
+      <c r="O15" s="42"/>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="36"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="43"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="43"/>
+      <c r="A16" s="35"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="42"/>
+      <c r="M16" s="42"/>
+      <c r="N16" s="42"/>
+      <c r="O16" s="42"/>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="36"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="43"/>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="43"/>
+      <c r="A17" s="35"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="42"/>
+      <c r="M17" s="42"/>
+      <c r="N17" s="42"/>
+      <c r="O17" s="42"/>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="36"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="43"/>
-      <c r="M18" s="43"/>
-      <c r="N18" s="43"/>
-      <c r="O18" s="43"/>
+      <c r="A18" s="35"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="42"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="42"/>
+      <c r="O18" s="42"/>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="36"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
-      <c r="H19" s="60"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="60"/>
-      <c r="K19" s="60"/>
-      <c r="L19" s="60"/>
-      <c r="M19" s="60"/>
-      <c r="N19" s="60"/>
-      <c r="O19" s="60"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="59"/>
+      <c r="K19" s="59"/>
+      <c r="L19" s="59"/>
+      <c r="M19" s="59"/>
+      <c r="N19" s="59"/>
+      <c r="O19" s="59"/>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="36"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="43"/>
-      <c r="N20" s="43"/>
-      <c r="O20" s="43"/>
+      <c r="A20" s="35"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="42"/>
+      <c r="O20" s="42"/>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="36"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="43"/>
-      <c r="J21" s="43"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="43"/>
-      <c r="M21" s="43"/>
-      <c r="N21" s="43"/>
-      <c r="O21" s="43"/>
+      <c r="A21" s="35"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="42"/>
+      <c r="L21" s="42"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="42"/>
+      <c r="O21" s="42"/>
     </row>
     <row r="22" spans="1:15">
-      <c r="A22" s="36"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="43"/>
-      <c r="M22" s="43"/>
-      <c r="N22" s="43"/>
-      <c r="O22" s="43"/>
+      <c r="A22" s="35"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="42"/>
+      <c r="M22" s="42"/>
+      <c r="N22" s="42"/>
+      <c r="O22" s="42"/>
     </row>
     <row r="23" spans="1:15" ht="26.5">
-      <c r="A23" s="45"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="45"/>
-      <c r="M23" s="45"/>
-      <c r="N23" s="45"/>
-      <c r="O23" s="45"/>
+      <c r="A23" s="44"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="44"/>
+      <c r="L23" s="44"/>
+      <c r="M23" s="44"/>
+      <c r="N23" s="44"/>
+      <c r="O23" s="44"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
@@ -6715,88 +6901,88 @@
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
-      <c r="B25" s="58"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="58"/>
-      <c r="K25" s="58"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="58"/>
-      <c r="N25" s="58"/>
-      <c r="O25" s="58"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="57"/>
+      <c r="M25" s="57"/>
+      <c r="N25" s="57"/>
+      <c r="O25" s="57"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
-      <c r="B26" s="58"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
-      <c r="J26" s="58"/>
-      <c r="K26" s="58"/>
-      <c r="L26" s="58"/>
-      <c r="M26" s="58"/>
-      <c r="N26" s="58"/>
-      <c r="O26" s="58"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="57"/>
+      <c r="N26" s="57"/>
+      <c r="O26" s="57"/>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
-      <c r="B27" s="58"/>
-      <c r="C27" s="58"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="58"/>
-      <c r="K27" s="58"/>
-      <c r="L27" s="58"/>
-      <c r="M27" s="58"/>
-      <c r="N27" s="58"/>
-      <c r="O27" s="58"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="57"/>
+      <c r="M27" s="57"/>
+      <c r="N27" s="57"/>
+      <c r="O27" s="57"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
-      <c r="B28" s="58"/>
-      <c r="C28" s="58"/>
-      <c r="D28" s="58"/>
-      <c r="E28" s="58"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
-      <c r="I28" s="58"/>
-      <c r="J28" s="58"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="58"/>
-      <c r="M28" s="58"/>
-      <c r="N28" s="58"/>
-      <c r="O28" s="58"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="57"/>
+      <c r="K28" s="57"/>
+      <c r="L28" s="57"/>
+      <c r="M28" s="57"/>
+      <c r="N28" s="57"/>
+      <c r="O28" s="57"/>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
-      <c r="B29" s="58"/>
-      <c r="C29" s="58"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="58"/>
-      <c r="J29" s="58"/>
-      <c r="K29" s="58"/>
-      <c r="L29" s="58"/>
-      <c r="M29" s="58"/>
-      <c r="N29" s="58"/>
-      <c r="O29" s="58"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="57"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="57"/>
+      <c r="M29" s="57"/>
+      <c r="N29" s="57"/>
+      <c r="O29" s="57"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
@@ -6902,77 +7088,77 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="80" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" s="81"/>
-      <c r="E1" s="82" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="84"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="131" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="132"/>
+      <c r="E1" s="133" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="135"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="40">
+      <c r="O1" s="39">
         <v>46268</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="78"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="84"/>
+      <c r="A2" s="91"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="134"/>
+      <c r="I2" s="134"/>
+      <c r="J2" s="134"/>
+      <c r="K2" s="135"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="59"/>
+      <c r="M2" s="58"/>
       <c r="N2" s="25" t="s">
         <v>15</v>
       </c>
       <c r="O2" s="26"/>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="41"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
+      <c r="A3" s="40"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
-      <c r="B4" s="36"/>
+      <c r="B4" s="35"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -6989,432 +7175,432 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
-      <c r="B5" s="61" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="62"/>
-      <c r="D5" s="61" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="62"/>
-      <c r="F5" s="61" t="s">
-        <v>57</v>
-      </c>
-      <c r="G5" s="62"/>
-      <c r="H5" s="61" t="s">
-        <v>58</v>
-      </c>
-      <c r="I5" s="62"/>
-      <c r="J5" s="61" t="s">
-        <v>59</v>
-      </c>
-      <c r="K5" s="55"/>
-      <c r="L5" s="63"/>
-      <c r="M5" s="64"/>
+      <c r="B5" s="60" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="61"/>
+      <c r="D5" s="60" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="61"/>
+      <c r="F5" s="60" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="61"/>
+      <c r="H5" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" s="61"/>
+      <c r="J5" s="60" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="54"/>
+      <c r="L5" s="62"/>
+      <c r="M5" s="63"/>
       <c r="N5" s="31"/>
       <c r="O5" s="8"/>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6" s="36"/>
-      <c r="B6" s="54" t="s">
+      <c r="A6" s="35"/>
+      <c r="B6" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="56"/>
+      <c r="D6" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" s="56"/>
+      <c r="F6" s="53">
+        <v>100</v>
+      </c>
+      <c r="G6" s="56"/>
+      <c r="H6" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" s="56"/>
+      <c r="J6" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="K6" s="54"/>
+      <c r="L6" s="62"/>
+      <c r="M6" s="63"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="35"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="35"/>
+      <c r="B7" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="56"/>
+      <c r="D7" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="56"/>
+      <c r="F7" s="53">
+        <v>100</v>
+      </c>
+      <c r="G7" s="56"/>
+      <c r="H7" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" s="56"/>
+      <c r="J7" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="K7" s="23"/>
+      <c r="L7" s="54"/>
+      <c r="M7" s="55"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="35"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="35"/>
+      <c r="B8" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="56"/>
+      <c r="D8" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" s="56"/>
+      <c r="F8" s="53">
+        <v>1</v>
+      </c>
+      <c r="G8" s="56"/>
+      <c r="H8" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8" s="56"/>
+      <c r="J8" s="53" t="s">
         <v>114</v>
       </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="54" t="s">
-        <v>125</v>
-      </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="54">
-        <v>100</v>
-      </c>
-      <c r="G6" s="57"/>
-      <c r="H6" s="54" t="s">
-        <v>61</v>
-      </c>
-      <c r="I6" s="57"/>
-      <c r="J6" s="54" t="s">
-        <v>127</v>
-      </c>
-      <c r="K6" s="55"/>
-      <c r="L6" s="63"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="31"/>
-      <c r="O6" s="36"/>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="36"/>
-      <c r="B7" s="54" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="57"/>
-      <c r="D7" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="57"/>
-      <c r="F7" s="54">
-        <v>100</v>
-      </c>
-      <c r="G7" s="57"/>
-      <c r="H7" s="54" t="s">
-        <v>61</v>
-      </c>
-      <c r="I7" s="57"/>
-      <c r="J7" s="54" t="s">
-        <v>127</v>
-      </c>
-      <c r="K7" s="23"/>
-      <c r="L7" s="55"/>
-      <c r="M7" s="56"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="36"/>
-      <c r="B8" s="54" t="s">
-        <v>116</v>
-      </c>
-      <c r="C8" s="57"/>
-      <c r="D8" s="54" t="s">
-        <v>126</v>
-      </c>
-      <c r="E8" s="57"/>
-      <c r="F8" s="54">
-        <v>1</v>
-      </c>
-      <c r="G8" s="57"/>
-      <c r="H8" s="54" t="s">
-        <v>61</v>
-      </c>
-      <c r="I8" s="57"/>
-      <c r="J8" s="54" t="s">
-        <v>128</v>
-      </c>
       <c r="K8" s="23"/>
-      <c r="L8" s="55"/>
-      <c r="M8" s="56"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="36"/>
+      <c r="L8" s="54"/>
+      <c r="M8" s="55"/>
+      <c r="N8" s="35"/>
+      <c r="O8" s="35"/>
     </row>
     <row r="9" spans="1:15" ht="36" customHeight="1">
-      <c r="A9" s="36"/>
-      <c r="B9" s="54" t="s">
-        <v>117</v>
-      </c>
-      <c r="C9" s="57"/>
+      <c r="A9" s="35"/>
+      <c r="B9" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="56"/>
       <c r="D9" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="E9" s="57"/>
+        <v>104</v>
+      </c>
+      <c r="E9" s="56"/>
       <c r="F9" s="17">
         <v>8</v>
       </c>
-      <c r="G9" s="57"/>
+      <c r="G9" s="56"/>
       <c r="H9" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="I9" s="57"/>
-      <c r="J9" s="133" t="s">
-        <v>129</v>
-      </c>
-      <c r="K9" s="134"/>
-      <c r="L9" s="134"/>
-      <c r="M9" s="135"/>
+        <v>47</v>
+      </c>
+      <c r="I9" s="56"/>
+      <c r="J9" s="145" t="s">
+        <v>115</v>
+      </c>
+      <c r="K9" s="146"/>
+      <c r="L9" s="146"/>
+      <c r="M9" s="147"/>
       <c r="N9" s="8"/>
-      <c r="O9" s="36"/>
+      <c r="O9" s="35"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="36"/>
-      <c r="B10" s="69" t="s">
-        <v>119</v>
-      </c>
-      <c r="C10" s="57"/>
+      <c r="A10" s="35"/>
+      <c r="B10" s="68" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="56"/>
       <c r="D10" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E10" s="57"/>
+        <v>111</v>
+      </c>
+      <c r="E10" s="56"/>
       <c r="F10" s="17">
         <v>100</v>
       </c>
-      <c r="G10" s="57"/>
+      <c r="G10" s="56"/>
       <c r="H10" s="17" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="17"/>
       <c r="K10" s="23"/>
       <c r="L10" s="23"/>
-      <c r="M10" s="57"/>
+      <c r="M10" s="56"/>
       <c r="N10" s="8"/>
-      <c r="O10" s="36"/>
+      <c r="O10" s="35"/>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11" s="36"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="C11" s="57"/>
+        <v>106</v>
+      </c>
+      <c r="C11" s="56"/>
       <c r="D11" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="E11" s="57"/>
+        <v>112</v>
+      </c>
+      <c r="E11" s="56"/>
       <c r="F11" s="17">
         <v>11</v>
       </c>
-      <c r="G11" s="57"/>
+      <c r="G11" s="56"/>
       <c r="H11" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="I11" s="57"/>
+        <v>47</v>
+      </c>
+      <c r="I11" s="56"/>
       <c r="J11" s="17" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="K11" s="23"/>
       <c r="L11" s="23"/>
-      <c r="M11" s="57"/>
+      <c r="M11" s="56"/>
       <c r="N11" s="8"/>
-      <c r="O11" s="36"/>
+      <c r="O11" s="35"/>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="36"/>
+      <c r="A12" s="35"/>
       <c r="B12" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="C12" s="56"/>
+        <v>107</v>
+      </c>
+      <c r="C12" s="55"/>
       <c r="D12" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="E12" s="57"/>
+        <v>112</v>
+      </c>
+      <c r="E12" s="56"/>
       <c r="F12" s="17">
         <v>7</v>
       </c>
-      <c r="G12" s="57"/>
+      <c r="G12" s="56"/>
       <c r="H12" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="I12" s="57"/>
+        <v>47</v>
+      </c>
+      <c r="I12" s="56"/>
       <c r="J12" s="17" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="23"/>
-      <c r="M12" s="57"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
+      <c r="M12" s="56"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="36"/>
-      <c r="B13" s="54" t="s">
-        <v>122</v>
-      </c>
-      <c r="C13" s="131"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="53" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="75"/>
       <c r="D13" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E13" s="57"/>
+        <v>111</v>
+      </c>
+      <c r="E13" s="56"/>
       <c r="F13" s="17">
         <v>100</v>
       </c>
-      <c r="G13" s="57"/>
+      <c r="G13" s="56"/>
       <c r="H13" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="I13" s="57"/>
+        <v>47</v>
+      </c>
+      <c r="I13" s="56"/>
       <c r="J13" s="17"/>
       <c r="K13" s="23"/>
       <c r="L13" s="23"/>
-      <c r="M13" s="57"/>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
+      <c r="M13" s="56"/>
+      <c r="N13" s="42"/>
+      <c r="O13" s="42"/>
     </row>
     <row r="14" spans="1:15" ht="54" customHeight="1">
-      <c r="A14" s="36"/>
-      <c r="B14" s="132" t="s">
-        <v>123</v>
-      </c>
-      <c r="C14" s="131"/>
+      <c r="A14" s="35"/>
+      <c r="B14" s="76" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="75"/>
       <c r="D14" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E14" s="57"/>
+        <v>111</v>
+      </c>
+      <c r="E14" s="56"/>
       <c r="F14" s="17">
         <v>10</v>
       </c>
-      <c r="G14" s="57"/>
+      <c r="G14" s="56"/>
       <c r="H14" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="I14" s="57"/>
-      <c r="J14" s="137" t="s">
-        <v>131</v>
-      </c>
-      <c r="K14" s="138"/>
-      <c r="L14" s="138"/>
-      <c r="M14" s="139"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
+        <v>47</v>
+      </c>
+      <c r="I14" s="56"/>
+      <c r="J14" s="148" t="s">
+        <v>117</v>
+      </c>
+      <c r="K14" s="149"/>
+      <c r="L14" s="149"/>
+      <c r="M14" s="150"/>
+      <c r="N14" s="42"/>
+      <c r="O14" s="42"/>
     </row>
     <row r="15" spans="1:15" ht="36" customHeight="1">
-      <c r="A15" s="36"/>
-      <c r="B15" s="132" t="s">
-        <v>124</v>
-      </c>
-      <c r="C15" s="131"/>
+      <c r="A15" s="35"/>
+      <c r="B15" s="76" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="75"/>
       <c r="D15" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E15" s="57"/>
+        <v>111</v>
+      </c>
+      <c r="E15" s="56"/>
       <c r="F15" s="17">
         <v>3</v>
       </c>
-      <c r="G15" s="57"/>
+      <c r="G15" s="56"/>
       <c r="H15" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="I15" s="57"/>
-      <c r="J15" s="136" t="s">
-        <v>132</v>
-      </c>
-      <c r="K15" s="140"/>
-      <c r="L15" s="140"/>
-      <c r="M15" s="141"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="43"/>
+        <v>47</v>
+      </c>
+      <c r="I15" s="56"/>
+      <c r="J15" s="151" t="s">
+        <v>118</v>
+      </c>
+      <c r="K15" s="152"/>
+      <c r="L15" s="152"/>
+      <c r="M15" s="153"/>
+      <c r="N15" s="42"/>
+      <c r="O15" s="42"/>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="36"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
+      <c r="A16" s="35"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
       <c r="J16" s="17"/>
       <c r="K16" s="23"/>
       <c r="L16" s="23"/>
-      <c r="M16" s="57"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="43"/>
+      <c r="M16" s="56"/>
+      <c r="N16" s="42"/>
+      <c r="O16" s="42"/>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="36"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="43"/>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="43"/>
+      <c r="A17" s="35"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="42"/>
+      <c r="M17" s="42"/>
+      <c r="N17" s="42"/>
+      <c r="O17" s="42"/>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="36"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="43"/>
-      <c r="M18" s="43"/>
-      <c r="N18" s="43"/>
-      <c r="O18" s="43"/>
+      <c r="A18" s="35"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="42"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="42"/>
+      <c r="O18" s="42"/>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="36"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
-      <c r="H19" s="60"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="60"/>
-      <c r="K19" s="60"/>
-      <c r="L19" s="60"/>
-      <c r="M19" s="60"/>
-      <c r="N19" s="60"/>
-      <c r="O19" s="60"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="59"/>
+      <c r="K19" s="59"/>
+      <c r="L19" s="59"/>
+      <c r="M19" s="59"/>
+      <c r="N19" s="59"/>
+      <c r="O19" s="59"/>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="36"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="43"/>
-      <c r="N20" s="43"/>
-      <c r="O20" s="43"/>
+      <c r="A20" s="35"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="42"/>
+      <c r="O20" s="42"/>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="36"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="43"/>
-      <c r="J21" s="43"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="43"/>
-      <c r="M21" s="43"/>
-      <c r="N21" s="43"/>
-      <c r="O21" s="43"/>
+      <c r="A21" s="35"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="42"/>
+      <c r="L21" s="42"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="42"/>
+      <c r="O21" s="42"/>
     </row>
     <row r="22" spans="1:15">
-      <c r="A22" s="36"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="43"/>
-      <c r="M22" s="43"/>
-      <c r="N22" s="43"/>
-      <c r="O22" s="43"/>
+      <c r="A22" s="35"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="42"/>
+      <c r="M22" s="42"/>
+      <c r="N22" s="42"/>
+      <c r="O22" s="42"/>
     </row>
     <row r="23" spans="1:15" ht="26.5">
-      <c r="A23" s="45"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="45"/>
-      <c r="M23" s="45"/>
-      <c r="N23" s="45"/>
-      <c r="O23" s="45"/>
+      <c r="A23" s="44"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="44"/>
+      <c r="L23" s="44"/>
+      <c r="M23" s="44"/>
+      <c r="N23" s="44"/>
+      <c r="O23" s="44"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
@@ -7435,88 +7621,88 @@
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
-      <c r="B25" s="58"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="58"/>
-      <c r="K25" s="58"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="58"/>
-      <c r="N25" s="58"/>
-      <c r="O25" s="58"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="57"/>
+      <c r="M25" s="57"/>
+      <c r="N25" s="57"/>
+      <c r="O25" s="57"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
-      <c r="B26" s="58"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
-      <c r="J26" s="58"/>
-      <c r="K26" s="58"/>
-      <c r="L26" s="58"/>
-      <c r="M26" s="58"/>
-      <c r="N26" s="58"/>
-      <c r="O26" s="58"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="57"/>
+      <c r="N26" s="57"/>
+      <c r="O26" s="57"/>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
-      <c r="B27" s="58"/>
-      <c r="C27" s="58"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="58"/>
-      <c r="K27" s="58"/>
-      <c r="L27" s="58"/>
-      <c r="M27" s="58"/>
-      <c r="N27" s="58"/>
-      <c r="O27" s="58"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="57"/>
+      <c r="M27" s="57"/>
+      <c r="N27" s="57"/>
+      <c r="O27" s="57"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
-      <c r="B28" s="58"/>
-      <c r="C28" s="58"/>
-      <c r="D28" s="58"/>
-      <c r="E28" s="58"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
-      <c r="I28" s="58"/>
-      <c r="J28" s="58"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="58"/>
-      <c r="M28" s="58"/>
-      <c r="N28" s="58"/>
-      <c r="O28" s="58"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="57"/>
+      <c r="K28" s="57"/>
+      <c r="L28" s="57"/>
+      <c r="M28" s="57"/>
+      <c r="N28" s="57"/>
+      <c r="O28" s="57"/>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
-      <c r="B29" s="58"/>
-      <c r="C29" s="58"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="58"/>
-      <c r="J29" s="58"/>
-      <c r="K29" s="58"/>
-      <c r="L29" s="58"/>
-      <c r="M29" s="58"/>
-      <c r="N29" s="58"/>
-      <c r="O29" s="58"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="57"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="57"/>
+      <c r="M29" s="57"/>
+      <c r="N29" s="57"/>
+      <c r="O29" s="57"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
@@ -7625,77 +7811,77 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:16" ht="20">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="80" t="s">
-        <v>72</v>
-      </c>
-      <c r="D1" s="81"/>
-      <c r="E1" s="82" t="s">
-        <v>62</v>
-      </c>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="84"/>
+      <c r="B1" s="90"/>
+      <c r="C1" s="131" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="132"/>
+      <c r="E1" s="133" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="134"/>
+      <c r="G1" s="134"/>
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="135"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="40">
+      <c r="O1" s="39">
         <v>46268</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="20">
-      <c r="A2" s="78"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="84"/>
+      <c r="A2" s="91"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="134"/>
+      <c r="H2" s="134"/>
+      <c r="I2" s="134"/>
+      <c r="J2" s="134"/>
+      <c r="K2" s="135"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="59"/>
+      <c r="M2" s="58"/>
       <c r="N2" s="25" t="s">
         <v>15</v>
       </c>
       <c r="O2" s="26"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="41"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="36"/>
+      <c r="A3" s="40"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="35"/>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="8"/>
-      <c r="B4" s="36"/>
+      <c r="B4" s="35"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -7712,118 +7898,118 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="8"/>
-      <c r="B5" s="65" t="s">
+      <c r="B5" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="61" t="s">
-        <v>63</v>
-      </c>
-      <c r="D5" s="52"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="I5" s="66"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="67"/>
-      <c r="M5" s="61" t="s">
-        <v>65</v>
-      </c>
-      <c r="N5" s="63"/>
-      <c r="O5" s="57"/>
+      <c r="C5" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="51"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="65"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="51"/>
+      <c r="L5" s="66"/>
+      <c r="M5" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="N5" s="62"/>
+      <c r="O5" s="56"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="36"/>
-      <c r="B6" s="68">
+      <c r="A6" s="35"/>
+      <c r="B6" s="67">
         <v>1</v>
       </c>
-      <c r="C6" s="54" t="s">
-        <v>134</v>
-      </c>
-      <c r="D6" s="52"/>
+      <c r="C6" s="53" t="s">
+        <v>120</v>
+      </c>
+      <c r="D6" s="51"/>
       <c r="E6" s="23"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="54" t="s">
-        <v>135</v>
+      <c r="F6" s="51"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="53" t="s">
+        <v>121</v>
       </c>
       <c r="I6" s="23"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="67"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="66"/>
       <c r="M6" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="N6" s="63"/>
-      <c r="O6" s="56"/>
+        <v>122</v>
+      </c>
+      <c r="N6" s="62"/>
+      <c r="O6" s="55"/>
       <c r="P6" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="36"/>
-      <c r="B7" s="68">
+      <c r="A7" s="35"/>
+      <c r="B7" s="67">
         <v>2</v>
       </c>
-      <c r="C7" s="54" t="s">
-        <v>137</v>
-      </c>
-      <c r="D7" s="52"/>
+      <c r="C7" s="53" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="51"/>
       <c r="E7" s="23"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="54" t="s">
-        <v>138</v>
+      <c r="F7" s="51"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="53" t="s">
+        <v>124</v>
       </c>
       <c r="I7" s="23"/>
-      <c r="J7" s="52"/>
-      <c r="K7" s="52"/>
-      <c r="L7" s="67"/>
-      <c r="M7" s="142" t="s">
-        <v>139</v>
-      </c>
-      <c r="N7" s="55"/>
-      <c r="O7" s="56"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="51"/>
+      <c r="L7" s="66"/>
+      <c r="M7" s="77" t="s">
+        <v>125</v>
+      </c>
+      <c r="N7" s="54"/>
+      <c r="O7" s="55"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="36"/>
-      <c r="B8" s="68"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="52"/>
+      <c r="A8" s="35"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="51"/>
       <c r="E8" s="23"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="53"/>
       <c r="I8" s="23"/>
-      <c r="J8" s="52"/>
-      <c r="K8" s="52"/>
-      <c r="L8" s="67"/>
-      <c r="M8" s="54"/>
-      <c r="N8" s="55"/>
-      <c r="O8" s="56"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="66"/>
+      <c r="M8" s="53"/>
+      <c r="N8" s="54"/>
+      <c r="O8" s="55"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="36"/>
-      <c r="B9" s="68"/>
+      <c r="A9" s="35"/>
+      <c r="B9" s="67"/>
       <c r="C9" s="17"/>
-      <c r="D9" s="52"/>
+      <c r="D9" s="51"/>
       <c r="E9" s="23"/>
       <c r="F9" s="23"/>
-      <c r="G9" s="57"/>
+      <c r="G9" s="56"/>
       <c r="H9" s="17"/>
       <c r="I9" s="23"/>
-      <c r="J9" s="52"/>
-      <c r="K9" s="52"/>
-      <c r="L9" s="67"/>
+      <c r="J9" s="51"/>
+      <c r="K9" s="51"/>
+      <c r="L9" s="66"/>
       <c r="M9" s="17"/>
       <c r="N9" s="23"/>
-      <c r="O9" s="56"/>
+      <c r="O9" s="55"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="36"/>
+      <c r="A10" s="35"/>
       <c r="B10" s="7"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -7837,10 +8023,10 @@
       <c r="L10" s="8"/>
       <c r="M10" s="8"/>
       <c r="N10" s="8"/>
-      <c r="O10" s="36"/>
+      <c r="O10" s="35"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="36"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -7854,211 +8040,211 @@
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
       <c r="N11" s="8"/>
-      <c r="O11" s="36"/>
+      <c r="O11" s="35"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="36"/>
+      <c r="A12" s="35"/>
       <c r="B12" s="8"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="42"/>
+      <c r="O13" s="42"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="36"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
+      <c r="A14" s="35"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="42"/>
+      <c r="N14" s="42"/>
+      <c r="O14" s="42"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="36"/>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="43"/>
+      <c r="A15" s="35"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="42"/>
+      <c r="M15" s="42"/>
+      <c r="N15" s="42"/>
+      <c r="O15" s="42"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="36"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="43"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="43"/>
+      <c r="A16" s="35"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="42"/>
+      <c r="M16" s="42"/>
+      <c r="N16" s="42"/>
+      <c r="O16" s="42"/>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="36"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="43"/>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="43"/>
+      <c r="A17" s="35"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="42"/>
+      <c r="M17" s="42"/>
+      <c r="N17" s="42"/>
+      <c r="O17" s="42"/>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="36"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="43"/>
-      <c r="M18" s="43"/>
-      <c r="N18" s="43"/>
-      <c r="O18" s="43"/>
+      <c r="A18" s="35"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="42"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="42"/>
+      <c r="O18" s="42"/>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="36"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
-      <c r="H19" s="60"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="60"/>
-      <c r="K19" s="60"/>
-      <c r="L19" s="60"/>
-      <c r="M19" s="60"/>
-      <c r="N19" s="60"/>
-      <c r="O19" s="60"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="59"/>
+      <c r="J19" s="59"/>
+      <c r="K19" s="59"/>
+      <c r="L19" s="59"/>
+      <c r="M19" s="59"/>
+      <c r="N19" s="59"/>
+      <c r="O19" s="59"/>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="36"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="43"/>
-      <c r="N20" s="43"/>
-      <c r="O20" s="43"/>
+      <c r="A20" s="35"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="42"/>
+      <c r="O20" s="42"/>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="36"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="43"/>
-      <c r="J21" s="43"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="43"/>
-      <c r="M21" s="43"/>
-      <c r="N21" s="43"/>
-      <c r="O21" s="43"/>
+      <c r="A21" s="35"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="42"/>
+      <c r="L21" s="42"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="42"/>
+      <c r="O21" s="42"/>
     </row>
     <row r="22" spans="1:15">
-      <c r="A22" s="36"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="43"/>
-      <c r="M22" s="43"/>
-      <c r="N22" s="43"/>
-      <c r="O22" s="43"/>
+      <c r="A22" s="35"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="42"/>
+      <c r="M22" s="42"/>
+      <c r="N22" s="42"/>
+      <c r="O22" s="42"/>
     </row>
     <row r="23" spans="1:15" ht="26.5">
-      <c r="A23" s="45"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="45"/>
-      <c r="M23" s="45"/>
-      <c r="N23" s="45"/>
-      <c r="O23" s="45"/>
+      <c r="A23" s="44"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="44"/>
+      <c r="L23" s="44"/>
+      <c r="M23" s="44"/>
+      <c r="N23" s="44"/>
+      <c r="O23" s="44"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
@@ -8079,88 +8265,88 @@
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
-      <c r="B25" s="58"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="58"/>
-      <c r="K25" s="58"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="58"/>
-      <c r="N25" s="58"/>
-      <c r="O25" s="58"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="57"/>
+      <c r="M25" s="57"/>
+      <c r="N25" s="57"/>
+      <c r="O25" s="57"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
-      <c r="B26" s="58"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
-      <c r="J26" s="58"/>
-      <c r="K26" s="58"/>
-      <c r="L26" s="58"/>
-      <c r="M26" s="58"/>
-      <c r="N26" s="58"/>
-      <c r="O26" s="58"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="57"/>
+      <c r="N26" s="57"/>
+      <c r="O26" s="57"/>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
-      <c r="B27" s="58"/>
-      <c r="C27" s="58"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="58"/>
-      <c r="K27" s="58"/>
-      <c r="L27" s="58"/>
-      <c r="M27" s="58"/>
-      <c r="N27" s="58"/>
-      <c r="O27" s="58"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="57"/>
+      <c r="M27" s="57"/>
+      <c r="N27" s="57"/>
+      <c r="O27" s="57"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
-      <c r="B28" s="58"/>
-      <c r="C28" s="58"/>
-      <c r="D28" s="58"/>
-      <c r="E28" s="58"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
-      <c r="I28" s="58"/>
-      <c r="J28" s="58"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="58"/>
-      <c r="M28" s="58"/>
-      <c r="N28" s="58"/>
-      <c r="O28" s="58"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="57"/>
+      <c r="K28" s="57"/>
+      <c r="L28" s="57"/>
+      <c r="M28" s="57"/>
+      <c r="N28" s="57"/>
+      <c r="O28" s="57"/>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
-      <c r="B29" s="58"/>
-      <c r="C29" s="58"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="58"/>
-      <c r="J29" s="58"/>
-      <c r="K29" s="58"/>
-      <c r="L29" s="58"/>
-      <c r="M29" s="58"/>
-      <c r="N29" s="58"/>
-      <c r="O29" s="58"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="57"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="57"/>
+      <c r="M29" s="57"/>
+      <c r="N29" s="57"/>
+      <c r="O29" s="57"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>

--- a/要件定義書（採用管理システム）.xlsx
+++ b/要件定義書（採用管理システム）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\my_application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D9DC5D-8B87-4010-9778-55E4143366B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29BF7BBA-EB00-4953-8397-493A528573A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="7" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="180">
   <si>
     <t>要件定義</t>
   </si>
@@ -135,9 +135,6 @@
   </si>
   <si>
     <t>利用者区分</t>
-  </si>
-  <si>
-    <t>役割</t>
   </si>
   <si>
     <t>管理者</t>
@@ -764,6 +761,703 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
+    <t>・応募情報（氏名・カナ・性別・生年月日・メールアドレス・電話番号・郵便番号・住所・最終学歴・希望勤務地）の入力</t>
+    <rPh sb="1" eb="3">
+      <t>オウボ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セイベツ</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>セイネンガッピ</t>
+    </rPh>
+    <rPh sb="28" eb="32">
+      <t>デンワバンゴウ</t>
+    </rPh>
+    <rPh sb="33" eb="37">
+      <t>ユウビンバンゴウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ジュウショ</t>
+    </rPh>
+    <rPh sb="41" eb="45">
+      <t>サイシュウガクレキ</t>
+    </rPh>
+    <rPh sb="46" eb="51">
+      <t>キボウキンムチ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・上記情報のDBへの登録</t>
+    <rPh sb="1" eb="5">
+      <t>ジョウキジョウホウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>■応募者状況一覧</t>
+    <rPh sb="1" eb="6">
+      <t>オウボシャジョウキョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イチラン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・応募者情報を検索→表示（氏名・カナ・性別・メールアドレス・電話番号・面接予定日・選考状況・担当者・合否）</t>
+    <rPh sb="1" eb="4">
+      <t>オウボシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>セイベツ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>デンワ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>バンゴウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>メンセツ</t>
+    </rPh>
+    <rPh sb="37" eb="40">
+      <t>ヨテイビ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>センコウ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="46" eb="49">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ゴウヒ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・更新ボタンより変更・登録が可能</t>
+    <rPh sb="1" eb="3">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>採用関連部署全ユーザー</t>
+    <rPh sb="0" eb="2">
+      <t>サイヨウ</t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t>カンレンブショ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>面接日・担当者登録、面接希望者状況一覧閲覧、スケジュールカレンダー</t>
+    <rPh sb="0" eb="3">
+      <t>メンセツビ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="10" eb="15">
+      <t>メンセツキボウシャ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>エツラン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>■応募者検索</t>
+    <rPh sb="1" eb="4">
+      <t>オウボシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケンサク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>■スケジュールカレンダー</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・採用スケジュールカレンダーへ自動反映</t>
+    <rPh sb="1" eb="3">
+      <t>サイヨウ</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>ジドウハンエイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>氏名</t>
+    <rPh sb="0" eb="2">
+      <t>シメイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>カナ</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>性別</t>
+    <rPh sb="0" eb="2">
+      <t>セイベツ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>生年月日</t>
+    <rPh sb="0" eb="4">
+      <t>セイネンガッピ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>メールアドレス</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>電話番号</t>
+    <rPh sb="0" eb="4">
+      <t>デンワバンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>郵便番号</t>
+    <rPh sb="0" eb="4">
+      <t>ユウビンバンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>住所</t>
+    <rPh sb="0" eb="2">
+      <t>ジュウショ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>最終学歴</t>
+    <rPh sb="0" eb="4">
+      <t>サイシュウガクレキ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>希望勤務地</t>
+    <rPh sb="0" eb="5">
+      <t>キボウキンムチ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>文字列</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>数値</t>
+    <rPh sb="0" eb="2">
+      <t>スウチ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>全角</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>ラジオボタン</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>プルダウン
+年：1946～2026　月：1～12　日：1～31</t>
+    <rPh sb="6" eb="7">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ヒ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>ハイフンなし（ハイフンなしと表示する）</t>
+    <rPh sb="14" eb="16">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>プルダウン
+「中学校卒業」「高等学校卒業」「専門学校卒業」
+「短期大学卒業」「四年制大学卒業」「大学院修了」
+「その他」</t>
+    <rPh sb="7" eb="10">
+      <t>チュウガッコウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ソツギョウ</t>
+    </rPh>
+    <rPh sb="14" eb="20">
+      <t>コウトウガッコウソツギョウ</t>
+    </rPh>
+    <rPh sb="22" eb="26">
+      <t>センモンガッコウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ソツギョウ</t>
+    </rPh>
+    <rPh sb="31" eb="35">
+      <t>タンキダイガク</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ソツギョウ</t>
+    </rPh>
+    <rPh sb="39" eb="44">
+      <t>ヨネンセイダイガク</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ソツギョウ</t>
+    </rPh>
+    <rPh sb="48" eb="53">
+      <t>ダイガクインシュウリョウ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>プルダウン
+「東京」「神奈川」「愛知」「大阪」「福岡」</t>
+    <rPh sb="7" eb="9">
+      <t>トウキョウ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>カナガワ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>アイチ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>オオサカ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>フクオカ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>渡辺のぞみ</t>
+    <rPh sb="0" eb="2">
+      <t>ワタナベ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>件数増えることでのスケジュール重複</t>
+    <rPh sb="0" eb="3">
+      <t>ケンスウフ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>チョウフク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>要再度対応</t>
+    <rPh sb="0" eb="1">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="1" eb="5">
+      <t>サイドタイオウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>メールにて担当者へ通知</t>
+    <rPh sb="5" eb="8">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ツウチ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>一覧表示の際のデータ過多</t>
+    <rPh sb="0" eb="4">
+      <t>イチランヒョウジ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カタ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>表示に時間がかかる</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>ステータスの選択を作り、表示件数を絞る</t>
+    <rPh sb="6" eb="8">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>ヒョウジケンスウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>シボ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>非機能要件</t>
+    <rPh sb="0" eb="3">
+      <t>ヒキノウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヨウケン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>渡辺のぞみ</t>
+    <rPh sb="0" eb="2">
+      <t>ワタナベ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>業務要件、利用者・権限定義、機能要件（途中）</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>業務要件、利用者・権限定義（修正・追記）、機能要件（作成）</t>
+    <rPh sb="0" eb="1">
+      <t>ギョウ</t>
+    </rPh>
+    <rPh sb="21" eb="25">
+      <t>キノウヨウケン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>データ項目定義、リスク・課題（作成）</t>
+    <rPh sb="3" eb="7">
+      <t>コウモクテイギ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>業務要件：1-3、1-4追記
+利用者・権限：管理者の権限内容変更</t>
+    <rPh sb="0" eb="4">
+      <t>ギョウムヨウケン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ツイキ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>リヨウシャ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ケンゲン</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>カンリシャ</t>
+    </rPh>
+    <rPh sb="26" eb="30">
+      <t>ケンゲンナイヨウ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>1-1</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>1-2</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>1-3</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>1-4</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>業務要件</t>
+    <rPh sb="0" eb="4">
+      <t>ギョウムヨウケン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>システム化の目的</t>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>モクテキ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>システム化の背景</t>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>システム化の範囲</t>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>現状の課題</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>改善後の姿</t>
+    <rPh sb="0" eb="3">
+      <t>カイゼンゴ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>スガタ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>利用者区分</t>
+    <rPh sb="0" eb="5">
+      <t>リヨウシャクブン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>利用者・権限</t>
+    <rPh sb="0" eb="3">
+      <t>リヨウシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケンゲン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>2-1</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>機能要件</t>
+    <rPh sb="0" eb="4">
+      <t>キノウヨウケン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>3-1</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>機能一覧</t>
+    <rPh sb="0" eb="4">
+      <t>キノウイチラン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>3-2</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>機能詳細</t>
+    <rPh sb="0" eb="4">
+      <t>キノウショウサイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>第4章</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>非機能要件</t>
+    <rPh sb="0" eb="3">
+      <t>ヒキノウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヨウケン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>4-1</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>性能要件</t>
+    <rPh sb="0" eb="4">
+      <t>セイノウヨウケン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>4-2</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>セキュリティ要件</t>
+    <rPh sb="6" eb="8">
+      <t>ヨウケン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>第5章</t>
+    <rPh sb="0" eb="1">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ショウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>5-1</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>データ項目定義</t>
+    <rPh sb="3" eb="7">
+      <t>コウモクテイギ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>第6章</t>
+    <rPh sb="0" eb="1">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ショウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>6-1</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>リスク・課題</t>
+    <rPh sb="4" eb="6">
+      <t>カダイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>渡辺のぞみ</t>
+    <rPh sb="0" eb="2">
+      <t>ワタナベ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>目次作成</t>
+    <rPh sb="0" eb="2">
+      <t>モクジ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
     <r>
       <t>w</t>
     </r>
@@ -782,7 +1476,7 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t>問い合わせのあった応募者を一覧（次回面接設定日・選考状況）で閲覧できるため</t>
+      <t>問い合わせのあった応募者を一覧（次回面接設定日・選考状況）で閲覧できる</t>
     </r>
     <rPh sb="2" eb="3">
       <t>ト</t>
@@ -814,311 +1508,38 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>・応募情報（氏名・カナ・性別・生年月日・メールアドレス・電話番号・郵便番号・住所・最終学歴・希望勤務地）の入力</t>
-    <rPh sb="1" eb="3">
-      <t>オウボ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>シメイ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>セイベツ</t>
-    </rPh>
-    <rPh sb="15" eb="19">
-      <t>セイネンガッピ</t>
-    </rPh>
-    <rPh sb="28" eb="32">
-      <t>デンワバンゴウ</t>
-    </rPh>
-    <rPh sb="33" eb="37">
-      <t>ユウビンバンゴウ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>ジュウショ</t>
-    </rPh>
-    <rPh sb="41" eb="45">
-      <t>サイシュウガクレキ</t>
-    </rPh>
-    <rPh sb="46" eb="51">
-      <t>キボウキンムチ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>・上記情報のDBへの登録</t>
-    <rPh sb="1" eb="5">
-      <t>ジョウキジョウホウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>■応募者状況一覧</t>
-    <rPh sb="1" eb="6">
-      <t>オウボシャジョウキョウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>イチラン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>・応募者情報を一覧表示（応募者ID・氏名・カナ・性別・メールアドレス・電話番号・応募日・面接予定日・選考状況・更新日時・担当者・合否・更新ボタン）</t>
-    <rPh sb="1" eb="4">
-      <t>オウボシャ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="12" eb="15">
-      <t>オウボシャ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>シメイ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>セイベツ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>デンワ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>バンゴウ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>オウボ</t>
-    </rPh>
-    <rPh sb="42" eb="43">
-      <t>ビ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>メンセツ</t>
-    </rPh>
-    <rPh sb="46" eb="49">
-      <t>ヨテイビ</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>センコウ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="57" eb="59">
-      <t>ニチジ</t>
-    </rPh>
-    <rPh sb="60" eb="63">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="64" eb="66">
-      <t>ゴウヒ</t>
-    </rPh>
-    <rPh sb="67" eb="69">
-      <t>コウシン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>・応募者情報を検索→表示（氏名・カナ・性別・メールアドレス・電話番号・面接予定日・選考状況・担当者・合否）</t>
-    <rPh sb="1" eb="4">
-      <t>オウボシャ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ケンサク</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>シメイ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>セイベツ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>デンワ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>バンゴウ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>メンセツ</t>
-    </rPh>
-    <rPh sb="37" eb="40">
-      <t>ヨテイビ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>センコウ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="46" eb="49">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>ゴウヒ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>・更新ボタンより変更・登録が可能</t>
-    <rPh sb="1" eb="3">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>カノウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>採用関連部署全ユーザー</t>
+    <t>役割・権限</t>
+    <rPh sb="3" eb="5">
+      <t>ケンゲン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>応募日</t>
+    <rPh sb="0" eb="3">
+      <t>オウボビ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>日付</t>
     <rPh sb="0" eb="2">
-      <t>サイヨウ</t>
-    </rPh>
-    <rPh sb="2" eb="6">
-      <t>カンレンブショ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>面接日・担当者登録、面接希望者状況一覧閲覧、スケジュールカレンダー</t>
-    <rPh sb="0" eb="3">
-      <t>メンセツビ</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="10" eb="15">
-      <t>メンセツキボウシャ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>エツラン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>■応募者検索</t>
-    <rPh sb="1" eb="4">
-      <t>オウボシャ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ケンサク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>■スケジュールカレンダー</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>・採用スケジュールカレンダーへ自動反映</t>
-    <rPh sb="1" eb="3">
-      <t>サイヨウ</t>
-    </rPh>
-    <rPh sb="15" eb="19">
-      <t>ジドウハンエイ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>氏名</t>
-    <rPh sb="0" eb="2">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>カナ</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>性別</t>
-    <rPh sb="0" eb="2">
-      <t>セイベツ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>生年月日</t>
+      <t>ヒヅケ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>選考状況</t>
     <rPh sb="0" eb="4">
-      <t>セイネンガッピ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>データ</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>メールアドレス</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>電話番号</t>
-    <rPh sb="0" eb="4">
-      <t>デンワバンゴウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>郵便番号</t>
-    <rPh sb="0" eb="4">
-      <t>ユウビンバンゴウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>住所</t>
-    <rPh sb="0" eb="2">
-      <t>ジュウショ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>最終学歴</t>
-    <rPh sb="0" eb="4">
-      <t>サイシュウガクレキ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>希望勤務地</t>
+      <t>センコウジョウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>面接予定日</t>
     <rPh sb="0" eb="5">
-      <t>キボウキンムチ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>文字列</t>
+      <t>メンセツヨテイヒ</t>
+    </rPh>
     <phoneticPr fontId="13"/>
   </si>
   <si>
@@ -1129,442 +1550,199 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>全角</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>ラジオボタン</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>プルダウン
-年：1946～2026　月：1～12　日：1～31</t>
-    <rPh sb="6" eb="7">
-      <t>ネン</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ツキ</t>
+    <t>ー</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>必須</t>
+    <rPh sb="0" eb="2">
+      <t>ヒッス</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>初期値：「応募受付」
+「書類選考」「1次面接」「2次面接」
+「最終面接」「内定」「不採用」「返事待ち」「辞退」</t>
+    <rPh sb="0" eb="3">
+      <t>ショキチ</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>オウボウケツケ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ショルイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>センコウ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>メンセツ</t>
     </rPh>
     <rPh sb="25" eb="26">
-      <t>ヒ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>ハイフンなし（ハイフンなしと表示する）</t>
-    <rPh sb="14" eb="16">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>メンセツ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>サイシュウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>メンセツ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ナイテイ</t>
+    </rPh>
+    <rPh sb="41" eb="44">
+      <t>フサイヨウ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ジタイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>更新日時</t>
+    <rPh sb="0" eb="4">
+      <t>コウシンニチジ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>担当者</t>
+    <rPh sb="0" eb="3">
+      <t>タントウシャ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>日付</t>
+    <rPh sb="0" eb="2">
+      <t>ヒヅケ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>―</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>ー（自動入力）</t>
+    <rPh sb="2" eb="6">
+      <t>ジドウニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>必須</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>自動入力</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>初期値：空欄
+自動入力</t>
+    <rPh sb="0" eb="3">
+      <t>ショキチ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>クウラン</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>ジドウニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・応募者情報を一覧表示（応募者ID・氏名・カナ・性別・メールアドレス・電話番号・応募日・面接予定日・選考状況・更新日時・担当者・更新ボタン）</t>
+    <rPh sb="1" eb="4">
+      <t>オウボシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>プルダウン
-「中学校卒業」「高等学校卒業」「専門学校卒業」
-「短期大学卒業」「四年制大学卒業」「大学院修了」
-「その他」</t>
-    <rPh sb="7" eb="10">
-      <t>チュウガッコウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ソツギョウ</t>
-    </rPh>
-    <rPh sb="14" eb="20">
-      <t>コウトウガッコウソツギョウ</t>
-    </rPh>
-    <rPh sb="22" eb="26">
-      <t>センモンガッコウ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ソツギョウ</t>
-    </rPh>
-    <rPh sb="31" eb="35">
-      <t>タンキダイガク</t>
+    <rPh sb="12" eb="15">
+      <t>オウボシャ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>セイベツ</t>
     </rPh>
     <rPh sb="35" eb="37">
-      <t>ソツギョウ</t>
-    </rPh>
-    <rPh sb="39" eb="44">
-      <t>ヨネンセイダイガク</t>
+      <t>デンワ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>バンゴウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>オウボ</t>
+    </rPh>
+    <rPh sb="42" eb="43">
+      <t>ビ</t>
     </rPh>
     <rPh sb="44" eb="46">
-      <t>ソツギョウ</t>
-    </rPh>
-    <rPh sb="48" eb="53">
-      <t>ダイガクインシュウリョウ</t>
-    </rPh>
-    <rPh sb="58" eb="59">
-      <t>タ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>プルダウン
-「東京」「神奈川」「愛知」「大阪」「福岡」</t>
-    <rPh sb="7" eb="9">
-      <t>トウキョウ</t>
-    </rPh>
-    <rPh sb="11" eb="14">
-      <t>カナガワ</t>
+      <t>メンセツ</t>
+    </rPh>
+    <rPh sb="46" eb="49">
+      <t>ヨテイビ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>センコウ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>ニチジ</t>
+    </rPh>
+    <rPh sb="60" eb="63">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="64" eb="66">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>初期値：空欄
+「渡辺」「鈴木」「田中」「小林」「高橋」</t>
+    <rPh sb="0" eb="3">
+      <t>ショキチ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>クウラン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ワタナベ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>スズキ</t>
     </rPh>
     <rPh sb="16" eb="18">
-      <t>アイチ</t>
+      <t>タナカ</t>
     </rPh>
     <rPh sb="20" eb="22">
-      <t>オオサカ</t>
+      <t>コバヤシ</t>
     </rPh>
     <rPh sb="24" eb="26">
-      <t>フクオカ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>渡辺のぞみ</t>
-    <rPh sb="0" eb="2">
-      <t>ワタナベ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>件数増えることでのスケジュール重複</t>
-    <rPh sb="0" eb="3">
-      <t>ケンスウフ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>チョウフク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>要再度対応</t>
-    <rPh sb="0" eb="1">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="1" eb="5">
-      <t>サイドタイオウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>メールにて担当者へ通知</t>
-    <rPh sb="5" eb="8">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ツウチ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>一覧表示の際のデータ過多</t>
-    <rPh sb="0" eb="4">
-      <t>イチランヒョウジ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>サイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>カタ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>表示に時間がかかる</t>
-    <rPh sb="0" eb="2">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ジカン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>ステータスの選択を作り、表示件数を絞る</t>
-    <rPh sb="6" eb="8">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ツク</t>
-    </rPh>
-    <rPh sb="12" eb="16">
-      <t>ヒョウジケンスウ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>シボ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>非機能要件</t>
-    <rPh sb="0" eb="3">
-      <t>ヒキノウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ヨウケン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>渡辺のぞみ</t>
-    <rPh sb="0" eb="2">
-      <t>ワタナベ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>業務要件、利用者・権限定義、機能要件（途中）</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>業務要件、利用者・権限定義（修正・追記）、機能要件（作成）</t>
-    <rPh sb="0" eb="1">
-      <t>ギョウ</t>
-    </rPh>
-    <rPh sb="21" eb="25">
-      <t>キノウヨウケン</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>サクセイ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>データ項目定義、リスク・課題（作成）</t>
-    <rPh sb="3" eb="7">
-      <t>コウモクテイギ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>カダイ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>サクセイ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>業務要件：1-3、1-4追記
-利用者・権限：管理者の権限内容変更</t>
-    <rPh sb="0" eb="4">
-      <t>ギョウムヨウケン</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ツイキ</t>
-    </rPh>
-    <rPh sb="15" eb="18">
-      <t>リヨウシャ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ケンゲン</t>
-    </rPh>
-    <rPh sb="22" eb="25">
-      <t>カンリシャ</t>
-    </rPh>
-    <rPh sb="26" eb="30">
-      <t>ケンゲンナイヨウ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ヘンコウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>1-1</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>1-2</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>1-3</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>1-4</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>業務要件</t>
-    <rPh sb="0" eb="4">
-      <t>ギョウムヨウケン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>システム化の目的</t>
-    <rPh sb="4" eb="5">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>モクテキ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>システム化の背景</t>
-    <rPh sb="4" eb="5">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ハイケイ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>システム化の範囲</t>
-    <rPh sb="4" eb="5">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ハンイ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>現状の課題</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>改善後の姿</t>
-    <rPh sb="0" eb="3">
-      <t>カイゼンゴ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>スガタ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>利用者区分</t>
-    <rPh sb="0" eb="5">
-      <t>リヨウシャクブン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>利用者・権限</t>
-    <rPh sb="0" eb="3">
-      <t>リヨウシャ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ケンゲン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>2-1</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>機能要件</t>
-    <rPh sb="0" eb="4">
-      <t>キノウヨウケン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>3-1</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>機能一覧</t>
-    <rPh sb="0" eb="4">
-      <t>キノウイチラン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>3-2</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>機能詳細</t>
-    <rPh sb="0" eb="4">
-      <t>キノウショウサイ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>第4章</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>非機能要件</t>
-    <rPh sb="0" eb="3">
-      <t>ヒキノウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ヨウケン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>4-1</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>性能要件</t>
-    <rPh sb="0" eb="4">
-      <t>セイノウヨウケン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>4-2</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>セキュリティ要件</t>
-    <rPh sb="6" eb="8">
-      <t>ヨウケン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>第5章</t>
-    <rPh sb="0" eb="1">
-      <t>ダイ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ショウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>5-1</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>データ項目定義</t>
-    <rPh sb="3" eb="7">
-      <t>コウモクテイギ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>第6章</t>
-    <rPh sb="0" eb="1">
-      <t>ダイ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ショウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>6-1</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>リスク・課題</t>
-    <rPh sb="4" eb="6">
-      <t>カダイ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>渡辺のぞみ</t>
-    <rPh sb="0" eb="2">
-      <t>ワタナベ</t>
+      <t>タカハシ</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -2079,7 +2257,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2299,9 +2477,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2314,6 +2489,63 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="56" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2344,24 +2576,12 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2473,37 +2693,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2512,9 +2705,6 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2542,29 +2732,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="56" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2974,44 +3146,44 @@
       <c r="P5" s="8"/>
     </row>
     <row r="6" spans="1:16" ht="39" customHeight="1">
-      <c r="A6" s="78"/>
-      <c r="B6" s="79"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="81" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="81"/>
-      <c r="K6" s="81"/>
-      <c r="L6" s="81"/>
-      <c r="M6" s="81"/>
-      <c r="N6" s="79"/>
-      <c r="O6" s="80"/>
-      <c r="P6" s="78"/>
+      <c r="A6" s="96"/>
+      <c r="B6" s="97"/>
+      <c r="C6" s="98"/>
+      <c r="D6" s="99" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="99"/>
+      <c r="F6" s="99"/>
+      <c r="G6" s="99"/>
+      <c r="H6" s="99"/>
+      <c r="I6" s="99"/>
+      <c r="J6" s="99"/>
+      <c r="K6" s="99"/>
+      <c r="L6" s="99"/>
+      <c r="M6" s="99"/>
+      <c r="N6" s="97"/>
+      <c r="O6" s="98"/>
+      <c r="P6" s="96"/>
     </row>
     <row r="7" spans="1:16" ht="39" customHeight="1">
-      <c r="A7" s="78"/>
-      <c r="B7" s="79"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="81" t="s">
+      <c r="A7" s="96"/>
+      <c r="B7" s="97"/>
+      <c r="C7" s="98"/>
+      <c r="D7" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81"/>
-      <c r="I7" s="81"/>
-      <c r="J7" s="81"/>
-      <c r="K7" s="81"/>
-      <c r="L7" s="81"/>
-      <c r="M7" s="81"/>
-      <c r="N7" s="79"/>
-      <c r="O7" s="80"/>
-      <c r="P7" s="78"/>
+      <c r="E7" s="99"/>
+      <c r="F7" s="99"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="99"/>
+      <c r="I7" s="99"/>
+      <c r="J7" s="99"/>
+      <c r="K7" s="99"/>
+      <c r="L7" s="99"/>
+      <c r="M7" s="99"/>
+      <c r="N7" s="97"/>
+      <c r="O7" s="98"/>
+      <c r="P7" s="96"/>
     </row>
     <row r="8" spans="1:16" ht="18.5" thickBot="1">
       <c r="A8" s="8"/>
@@ -3073,16 +3245,16 @@
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
-      <c r="F11" s="82" t="s">
+      <c r="F11" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="83"/>
-      <c r="H11" s="84" t="s">
-        <v>60</v>
-      </c>
-      <c r="I11" s="85"/>
-      <c r="J11" s="85"/>
-      <c r="K11" s="85"/>
+      <c r="G11" s="101"/>
+      <c r="H11" s="102" t="s">
+        <v>59</v>
+      </c>
+      <c r="I11" s="103"/>
+      <c r="J11" s="103"/>
+      <c r="K11" s="103"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -3095,16 +3267,16 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
-      <c r="F12" s="82" t="s">
+      <c r="F12" s="100" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="83"/>
-      <c r="H12" s="86">
+      <c r="G12" s="101"/>
+      <c r="H12" s="104">
         <v>46265</v>
       </c>
-      <c r="I12" s="87"/>
-      <c r="J12" s="87"/>
-      <c r="K12" s="87"/>
+      <c r="I12" s="105"/>
+      <c r="J12" s="105"/>
+      <c r="K12" s="105"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
@@ -3117,16 +3289,16 @@
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
-      <c r="F13" s="82" t="s">
+      <c r="F13" s="100" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="83"/>
-      <c r="H13" s="86">
+      <c r="G13" s="101"/>
+      <c r="H13" s="104">
         <v>46273</v>
       </c>
-      <c r="I13" s="87"/>
-      <c r="J13" s="87"/>
-      <c r="K13" s="87"/>
+      <c r="I13" s="105"/>
+      <c r="J13" s="105"/>
+      <c r="K13" s="105"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
@@ -3139,14 +3311,14 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
-      <c r="F14" s="82" t="s">
+      <c r="F14" s="100" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="83"/>
-      <c r="H14" s="84"/>
-      <c r="I14" s="85"/>
-      <c r="J14" s="85"/>
-      <c r="K14" s="85"/>
+      <c r="G14" s="101"/>
+      <c r="H14" s="102"/>
+      <c r="I14" s="103"/>
+      <c r="J14" s="103"/>
+      <c r="K14" s="103"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
@@ -3311,56 +3483,56 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="94" t="s">
+      <c r="B1" s="106"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="108" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="95"/>
-      <c r="L1" s="95"/>
-      <c r="M1" s="95"/>
-      <c r="N1" s="95"/>
-      <c r="O1" s="96"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="110"/>
       <c r="P1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="100" t="s">
-        <v>127</v>
-      </c>
-      <c r="R1" s="101"/>
+      <c r="Q1" s="114" t="s">
+        <v>123</v>
+      </c>
+      <c r="R1" s="115"/>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="91"/>
-      <c r="B2" s="92"/>
-      <c r="C2" s="93"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="99"/>
+      <c r="A2" s="87"/>
+      <c r="B2" s="107"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="112"/>
+      <c r="F2" s="112"/>
+      <c r="G2" s="112"/>
+      <c r="H2" s="112"/>
+      <c r="I2" s="112"/>
+      <c r="J2" s="112"/>
+      <c r="K2" s="112"/>
+      <c r="L2" s="112"/>
+      <c r="M2" s="112"/>
+      <c r="N2" s="112"/>
+      <c r="O2" s="113"/>
       <c r="P2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="102">
+      <c r="Q2" s="116">
         <v>46273</v>
       </c>
-      <c r="R2" s="103"/>
+      <c r="R2" s="117"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="2"/>
@@ -3386,447 +3558,453 @@
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="104" t="s">
+      <c r="B4" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="105"/>
-      <c r="D4" s="104" t="s">
+      <c r="C4" s="119"/>
+      <c r="D4" s="118" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="105"/>
-      <c r="F4" s="104" t="s">
+      <c r="E4" s="119"/>
+      <c r="F4" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="106"/>
-      <c r="H4" s="105"/>
-      <c r="I4" s="104" t="s">
+      <c r="G4" s="120"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="118" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="106"/>
-      <c r="K4" s="106"/>
-      <c r="L4" s="106"/>
-      <c r="M4" s="106"/>
-      <c r="N4" s="106"/>
-      <c r="O4" s="106"/>
-      <c r="P4" s="106"/>
-      <c r="Q4" s="106"/>
-      <c r="R4" s="105"/>
+      <c r="J4" s="120"/>
+      <c r="K4" s="120"/>
+      <c r="L4" s="120"/>
+      <c r="M4" s="120"/>
+      <c r="N4" s="120"/>
+      <c r="O4" s="120"/>
+      <c r="P4" s="120"/>
+      <c r="Q4" s="120"/>
+      <c r="R4" s="119"/>
     </row>
     <row r="5" spans="1:18" ht="36" customHeight="1">
       <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="107">
+      <c r="B5" s="121">
         <v>46260</v>
       </c>
-      <c r="C5" s="108"/>
-      <c r="D5" s="109" t="s">
-        <v>127</v>
-      </c>
-      <c r="E5" s="110"/>
-      <c r="F5" s="111" t="s">
-        <v>128</v>
-      </c>
-      <c r="G5" s="112"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="114"/>
-      <c r="J5" s="115"/>
-      <c r="K5" s="115"/>
-      <c r="L5" s="115"/>
-      <c r="M5" s="115"/>
-      <c r="N5" s="115"/>
-      <c r="O5" s="115"/>
-      <c r="P5" s="115"/>
-      <c r="Q5" s="115"/>
-      <c r="R5" s="116"/>
+      <c r="C5" s="122"/>
+      <c r="D5" s="123" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" s="124"/>
+      <c r="F5" s="125" t="s">
+        <v>124</v>
+      </c>
+      <c r="G5" s="126"/>
+      <c r="H5" s="127"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="129"/>
+      <c r="K5" s="129"/>
+      <c r="L5" s="129"/>
+      <c r="M5" s="129"/>
+      <c r="N5" s="129"/>
+      <c r="O5" s="129"/>
+      <c r="P5" s="129"/>
+      <c r="Q5" s="129"/>
+      <c r="R5" s="130"/>
     </row>
     <row r="6" spans="1:18" ht="36" customHeight="1">
       <c r="A6" s="6">
         <v>2</v>
       </c>
-      <c r="B6" s="117">
+      <c r="B6" s="131">
         <v>46266</v>
       </c>
-      <c r="C6" s="118"/>
-      <c r="D6" s="119" t="s">
+      <c r="C6" s="132"/>
+      <c r="D6" s="133" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" s="132"/>
+      <c r="F6" s="134" t="s">
+        <v>125</v>
+      </c>
+      <c r="G6" s="135"/>
+      <c r="H6" s="136"/>
+      <c r="I6" s="134" t="s">
         <v>127</v>
       </c>
-      <c r="E6" s="118"/>
-      <c r="F6" s="120" t="s">
-        <v>129</v>
-      </c>
-      <c r="G6" s="121"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="120" t="s">
-        <v>131</v>
-      </c>
-      <c r="J6" s="123"/>
-      <c r="K6" s="123"/>
-      <c r="L6" s="123"/>
-      <c r="M6" s="123"/>
-      <c r="N6" s="123"/>
-      <c r="O6" s="123"/>
-      <c r="P6" s="123"/>
-      <c r="Q6" s="123"/>
-      <c r="R6" s="124"/>
+      <c r="J6" s="137"/>
+      <c r="K6" s="137"/>
+      <c r="L6" s="137"/>
+      <c r="M6" s="137"/>
+      <c r="N6" s="137"/>
+      <c r="O6" s="137"/>
+      <c r="P6" s="137"/>
+      <c r="Q6" s="137"/>
+      <c r="R6" s="138"/>
     </row>
     <row r="7" spans="1:18" ht="36" customHeight="1">
       <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="117">
+      <c r="B7" s="131">
         <v>46268</v>
       </c>
-      <c r="C7" s="118"/>
-      <c r="D7" s="119" t="s">
-        <v>127</v>
-      </c>
-      <c r="E7" s="118"/>
-      <c r="F7" s="120" t="s">
-        <v>130</v>
-      </c>
-      <c r="G7" s="121"/>
-      <c r="H7" s="122"/>
-      <c r="I7" s="125"/>
-      <c r="J7" s="123"/>
-      <c r="K7" s="123"/>
-      <c r="L7" s="123"/>
-      <c r="M7" s="123"/>
-      <c r="N7" s="123"/>
-      <c r="O7" s="123"/>
-      <c r="P7" s="123"/>
-      <c r="Q7" s="123"/>
-      <c r="R7" s="124"/>
+      <c r="C7" s="132"/>
+      <c r="D7" s="133" t="s">
+        <v>123</v>
+      </c>
+      <c r="E7" s="132"/>
+      <c r="F7" s="134" t="s">
+        <v>126</v>
+      </c>
+      <c r="G7" s="135"/>
+      <c r="H7" s="136"/>
+      <c r="I7" s="139"/>
+      <c r="J7" s="137"/>
+      <c r="K7" s="137"/>
+      <c r="L7" s="137"/>
+      <c r="M7" s="137"/>
+      <c r="N7" s="137"/>
+      <c r="O7" s="137"/>
+      <c r="P7" s="137"/>
+      <c r="Q7" s="137"/>
+      <c r="R7" s="138"/>
     </row>
     <row r="8" spans="1:18" ht="36" customHeight="1">
       <c r="A8" s="6">
         <v>4</v>
       </c>
-      <c r="B8" s="119"/>
-      <c r="C8" s="118"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="118"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="126"/>
-      <c r="H8" s="118"/>
-      <c r="I8" s="125"/>
-      <c r="J8" s="123"/>
-      <c r="K8" s="123"/>
-      <c r="L8" s="123"/>
-      <c r="M8" s="123"/>
-      <c r="N8" s="123"/>
-      <c r="O8" s="123"/>
-      <c r="P8" s="123"/>
-      <c r="Q8" s="123"/>
-      <c r="R8" s="124"/>
+      <c r="B8" s="131">
+        <v>46273</v>
+      </c>
+      <c r="C8" s="132"/>
+      <c r="D8" s="133" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="132"/>
+      <c r="F8" s="139" t="s">
+        <v>159</v>
+      </c>
+      <c r="G8" s="137"/>
+      <c r="H8" s="138"/>
+      <c r="I8" s="139"/>
+      <c r="J8" s="137"/>
+      <c r="K8" s="137"/>
+      <c r="L8" s="137"/>
+      <c r="M8" s="137"/>
+      <c r="N8" s="137"/>
+      <c r="O8" s="137"/>
+      <c r="P8" s="137"/>
+      <c r="Q8" s="137"/>
+      <c r="R8" s="138"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="6">
         <v>5</v>
       </c>
-      <c r="B9" s="119"/>
-      <c r="C9" s="118"/>
-      <c r="D9" s="119"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="126"/>
-      <c r="H9" s="118"/>
-      <c r="I9" s="125"/>
-      <c r="J9" s="123"/>
-      <c r="K9" s="123"/>
-      <c r="L9" s="123"/>
-      <c r="M9" s="123"/>
-      <c r="N9" s="123"/>
-      <c r="O9" s="123"/>
-      <c r="P9" s="123"/>
-      <c r="Q9" s="123"/>
-      <c r="R9" s="124"/>
+      <c r="B9" s="133"/>
+      <c r="C9" s="132"/>
+      <c r="D9" s="133"/>
+      <c r="E9" s="132"/>
+      <c r="F9" s="133"/>
+      <c r="G9" s="140"/>
+      <c r="H9" s="132"/>
+      <c r="I9" s="139"/>
+      <c r="J9" s="137"/>
+      <c r="K9" s="137"/>
+      <c r="L9" s="137"/>
+      <c r="M9" s="137"/>
+      <c r="N9" s="137"/>
+      <c r="O9" s="137"/>
+      <c r="P9" s="137"/>
+      <c r="Q9" s="137"/>
+      <c r="R9" s="138"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="6">
         <v>6</v>
       </c>
-      <c r="B10" s="119"/>
-      <c r="C10" s="118"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="118"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="126"/>
-      <c r="H10" s="118"/>
-      <c r="I10" s="125"/>
-      <c r="J10" s="123"/>
-      <c r="K10" s="123"/>
-      <c r="L10" s="123"/>
-      <c r="M10" s="123"/>
-      <c r="N10" s="123"/>
-      <c r="O10" s="123"/>
-      <c r="P10" s="123"/>
-      <c r="Q10" s="123"/>
-      <c r="R10" s="124"/>
+      <c r="B10" s="133"/>
+      <c r="C10" s="132"/>
+      <c r="D10" s="133"/>
+      <c r="E10" s="132"/>
+      <c r="F10" s="133"/>
+      <c r="G10" s="140"/>
+      <c r="H10" s="132"/>
+      <c r="I10" s="139"/>
+      <c r="J10" s="137"/>
+      <c r="K10" s="137"/>
+      <c r="L10" s="137"/>
+      <c r="M10" s="137"/>
+      <c r="N10" s="137"/>
+      <c r="O10" s="137"/>
+      <c r="P10" s="137"/>
+      <c r="Q10" s="137"/>
+      <c r="R10" s="138"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="6">
         <v>7</v>
       </c>
-      <c r="B11" s="119"/>
-      <c r="C11" s="118"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="118"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="126"/>
-      <c r="H11" s="118"/>
-      <c r="I11" s="125"/>
-      <c r="J11" s="123"/>
-      <c r="K11" s="123"/>
-      <c r="L11" s="123"/>
-      <c r="M11" s="123"/>
-      <c r="N11" s="123"/>
-      <c r="O11" s="123"/>
-      <c r="P11" s="123"/>
-      <c r="Q11" s="123"/>
-      <c r="R11" s="124"/>
+      <c r="B11" s="133"/>
+      <c r="C11" s="132"/>
+      <c r="D11" s="133"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="133"/>
+      <c r="G11" s="140"/>
+      <c r="H11" s="132"/>
+      <c r="I11" s="139"/>
+      <c r="J11" s="137"/>
+      <c r="K11" s="137"/>
+      <c r="L11" s="137"/>
+      <c r="M11" s="137"/>
+      <c r="N11" s="137"/>
+      <c r="O11" s="137"/>
+      <c r="P11" s="137"/>
+      <c r="Q11" s="137"/>
+      <c r="R11" s="138"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="6">
         <v>8</v>
       </c>
-      <c r="B12" s="119"/>
-      <c r="C12" s="118"/>
-      <c r="D12" s="119"/>
-      <c r="E12" s="118"/>
-      <c r="F12" s="119"/>
-      <c r="G12" s="126"/>
-      <c r="H12" s="118"/>
-      <c r="I12" s="125"/>
-      <c r="J12" s="123"/>
-      <c r="K12" s="123"/>
-      <c r="L12" s="123"/>
-      <c r="M12" s="123"/>
-      <c r="N12" s="123"/>
-      <c r="O12" s="123"/>
-      <c r="P12" s="123"/>
-      <c r="Q12" s="123"/>
-      <c r="R12" s="124"/>
+      <c r="B12" s="133"/>
+      <c r="C12" s="132"/>
+      <c r="D12" s="133"/>
+      <c r="E12" s="132"/>
+      <c r="F12" s="133"/>
+      <c r="G12" s="140"/>
+      <c r="H12" s="132"/>
+      <c r="I12" s="139"/>
+      <c r="J12" s="137"/>
+      <c r="K12" s="137"/>
+      <c r="L12" s="137"/>
+      <c r="M12" s="137"/>
+      <c r="N12" s="137"/>
+      <c r="O12" s="137"/>
+      <c r="P12" s="137"/>
+      <c r="Q12" s="137"/>
+      <c r="R12" s="138"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="6">
         <v>9</v>
       </c>
-      <c r="B13" s="119"/>
-      <c r="C13" s="118"/>
-      <c r="D13" s="119"/>
-      <c r="E13" s="118"/>
-      <c r="F13" s="119"/>
-      <c r="G13" s="126"/>
-      <c r="H13" s="118"/>
-      <c r="I13" s="125"/>
-      <c r="J13" s="123"/>
-      <c r="K13" s="123"/>
-      <c r="L13" s="123"/>
-      <c r="M13" s="123"/>
-      <c r="N13" s="123"/>
-      <c r="O13" s="123"/>
-      <c r="P13" s="123"/>
-      <c r="Q13" s="123"/>
-      <c r="R13" s="124"/>
+      <c r="B13" s="133"/>
+      <c r="C13" s="132"/>
+      <c r="D13" s="133"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="133"/>
+      <c r="G13" s="140"/>
+      <c r="H13" s="132"/>
+      <c r="I13" s="139"/>
+      <c r="J13" s="137"/>
+      <c r="K13" s="137"/>
+      <c r="L13" s="137"/>
+      <c r="M13" s="137"/>
+      <c r="N13" s="137"/>
+      <c r="O13" s="137"/>
+      <c r="P13" s="137"/>
+      <c r="Q13" s="137"/>
+      <c r="R13" s="138"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="6">
         <v>10</v>
       </c>
-      <c r="B14" s="119"/>
-      <c r="C14" s="118"/>
-      <c r="D14" s="119"/>
-      <c r="E14" s="118"/>
-      <c r="F14" s="119"/>
-      <c r="G14" s="126"/>
-      <c r="H14" s="118"/>
-      <c r="I14" s="125"/>
-      <c r="J14" s="123"/>
-      <c r="K14" s="123"/>
-      <c r="L14" s="123"/>
-      <c r="M14" s="123"/>
-      <c r="N14" s="123"/>
-      <c r="O14" s="123"/>
-      <c r="P14" s="123"/>
-      <c r="Q14" s="123"/>
-      <c r="R14" s="124"/>
+      <c r="B14" s="133"/>
+      <c r="C14" s="132"/>
+      <c r="D14" s="133"/>
+      <c r="E14" s="132"/>
+      <c r="F14" s="133"/>
+      <c r="G14" s="140"/>
+      <c r="H14" s="132"/>
+      <c r="I14" s="139"/>
+      <c r="J14" s="137"/>
+      <c r="K14" s="137"/>
+      <c r="L14" s="137"/>
+      <c r="M14" s="137"/>
+      <c r="N14" s="137"/>
+      <c r="O14" s="137"/>
+      <c r="P14" s="137"/>
+      <c r="Q14" s="137"/>
+      <c r="R14" s="138"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="6">
         <v>11</v>
       </c>
-      <c r="B15" s="119"/>
-      <c r="C15" s="118"/>
-      <c r="D15" s="119"/>
-      <c r="E15" s="118"/>
-      <c r="F15" s="119"/>
-      <c r="G15" s="126"/>
-      <c r="H15" s="118"/>
-      <c r="I15" s="125"/>
-      <c r="J15" s="123"/>
-      <c r="K15" s="123"/>
-      <c r="L15" s="123"/>
-      <c r="M15" s="123"/>
-      <c r="N15" s="123"/>
-      <c r="O15" s="123"/>
-      <c r="P15" s="123"/>
-      <c r="Q15" s="123"/>
-      <c r="R15" s="124"/>
+      <c r="B15" s="133"/>
+      <c r="C15" s="132"/>
+      <c r="D15" s="133"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="140"/>
+      <c r="H15" s="132"/>
+      <c r="I15" s="139"/>
+      <c r="J15" s="137"/>
+      <c r="K15" s="137"/>
+      <c r="L15" s="137"/>
+      <c r="M15" s="137"/>
+      <c r="N15" s="137"/>
+      <c r="O15" s="137"/>
+      <c r="P15" s="137"/>
+      <c r="Q15" s="137"/>
+      <c r="R15" s="138"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="6">
         <v>12</v>
       </c>
-      <c r="B16" s="119"/>
-      <c r="C16" s="118"/>
-      <c r="D16" s="119"/>
-      <c r="E16" s="118"/>
-      <c r="F16" s="119"/>
-      <c r="G16" s="126"/>
-      <c r="H16" s="118"/>
-      <c r="I16" s="125"/>
-      <c r="J16" s="123"/>
-      <c r="K16" s="123"/>
-      <c r="L16" s="123"/>
-      <c r="M16" s="123"/>
-      <c r="N16" s="123"/>
-      <c r="O16" s="123"/>
-      <c r="P16" s="123"/>
-      <c r="Q16" s="123"/>
-      <c r="R16" s="124"/>
+      <c r="B16" s="133"/>
+      <c r="C16" s="132"/>
+      <c r="D16" s="133"/>
+      <c r="E16" s="132"/>
+      <c r="F16" s="133"/>
+      <c r="G16" s="140"/>
+      <c r="H16" s="132"/>
+      <c r="I16" s="139"/>
+      <c r="J16" s="137"/>
+      <c r="K16" s="137"/>
+      <c r="L16" s="137"/>
+      <c r="M16" s="137"/>
+      <c r="N16" s="137"/>
+      <c r="O16" s="137"/>
+      <c r="P16" s="137"/>
+      <c r="Q16" s="137"/>
+      <c r="R16" s="138"/>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="6">
         <v>13</v>
       </c>
-      <c r="B17" s="119"/>
-      <c r="C17" s="118"/>
-      <c r="D17" s="119"/>
-      <c r="E17" s="118"/>
-      <c r="F17" s="119"/>
-      <c r="G17" s="126"/>
-      <c r="H17" s="118"/>
-      <c r="I17" s="125"/>
-      <c r="J17" s="123"/>
-      <c r="K17" s="123"/>
-      <c r="L17" s="123"/>
-      <c r="M17" s="123"/>
-      <c r="N17" s="123"/>
-      <c r="O17" s="123"/>
-      <c r="P17" s="123"/>
-      <c r="Q17" s="123"/>
-      <c r="R17" s="124"/>
+      <c r="B17" s="133"/>
+      <c r="C17" s="132"/>
+      <c r="D17" s="133"/>
+      <c r="E17" s="132"/>
+      <c r="F17" s="133"/>
+      <c r="G17" s="140"/>
+      <c r="H17" s="132"/>
+      <c r="I17" s="139"/>
+      <c r="J17" s="137"/>
+      <c r="K17" s="137"/>
+      <c r="L17" s="137"/>
+      <c r="M17" s="137"/>
+      <c r="N17" s="137"/>
+      <c r="O17" s="137"/>
+      <c r="P17" s="137"/>
+      <c r="Q17" s="137"/>
+      <c r="R17" s="138"/>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="6">
         <v>14</v>
       </c>
-      <c r="B18" s="119"/>
-      <c r="C18" s="118"/>
-      <c r="D18" s="119"/>
-      <c r="E18" s="118"/>
-      <c r="F18" s="119"/>
-      <c r="G18" s="126"/>
-      <c r="H18" s="118"/>
-      <c r="I18" s="125"/>
-      <c r="J18" s="123"/>
-      <c r="K18" s="123"/>
-      <c r="L18" s="123"/>
-      <c r="M18" s="123"/>
-      <c r="N18" s="123"/>
-      <c r="O18" s="123"/>
-      <c r="P18" s="123"/>
-      <c r="Q18" s="123"/>
-      <c r="R18" s="124"/>
+      <c r="B18" s="133"/>
+      <c r="C18" s="132"/>
+      <c r="D18" s="133"/>
+      <c r="E18" s="132"/>
+      <c r="F18" s="133"/>
+      <c r="G18" s="140"/>
+      <c r="H18" s="132"/>
+      <c r="I18" s="139"/>
+      <c r="J18" s="137"/>
+      <c r="K18" s="137"/>
+      <c r="L18" s="137"/>
+      <c r="M18" s="137"/>
+      <c r="N18" s="137"/>
+      <c r="O18" s="137"/>
+      <c r="P18" s="137"/>
+      <c r="Q18" s="137"/>
+      <c r="R18" s="138"/>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="6">
         <v>15</v>
       </c>
-      <c r="B19" s="119"/>
-      <c r="C19" s="118"/>
-      <c r="D19" s="119"/>
-      <c r="E19" s="118"/>
-      <c r="F19" s="119"/>
-      <c r="G19" s="126"/>
-      <c r="H19" s="118"/>
-      <c r="I19" s="125"/>
-      <c r="J19" s="123"/>
-      <c r="K19" s="123"/>
-      <c r="L19" s="123"/>
-      <c r="M19" s="123"/>
-      <c r="N19" s="123"/>
-      <c r="O19" s="123"/>
-      <c r="P19" s="123"/>
-      <c r="Q19" s="123"/>
-      <c r="R19" s="124"/>
+      <c r="B19" s="133"/>
+      <c r="C19" s="132"/>
+      <c r="D19" s="133"/>
+      <c r="E19" s="132"/>
+      <c r="F19" s="133"/>
+      <c r="G19" s="140"/>
+      <c r="H19" s="132"/>
+      <c r="I19" s="139"/>
+      <c r="J19" s="137"/>
+      <c r="K19" s="137"/>
+      <c r="L19" s="137"/>
+      <c r="M19" s="137"/>
+      <c r="N19" s="137"/>
+      <c r="O19" s="137"/>
+      <c r="P19" s="137"/>
+      <c r="Q19" s="137"/>
+      <c r="R19" s="138"/>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="6">
         <v>16</v>
       </c>
-      <c r="B20" s="119"/>
-      <c r="C20" s="118"/>
-      <c r="D20" s="119"/>
-      <c r="E20" s="118"/>
-      <c r="F20" s="119"/>
-      <c r="G20" s="126"/>
-      <c r="H20" s="118"/>
-      <c r="I20" s="125"/>
-      <c r="J20" s="123"/>
-      <c r="K20" s="123"/>
-      <c r="L20" s="123"/>
-      <c r="M20" s="123"/>
-      <c r="N20" s="123"/>
-      <c r="O20" s="123"/>
-      <c r="P20" s="123"/>
-      <c r="Q20" s="123"/>
-      <c r="R20" s="124"/>
+      <c r="B20" s="133"/>
+      <c r="C20" s="132"/>
+      <c r="D20" s="133"/>
+      <c r="E20" s="132"/>
+      <c r="F20" s="133"/>
+      <c r="G20" s="140"/>
+      <c r="H20" s="132"/>
+      <c r="I20" s="139"/>
+      <c r="J20" s="137"/>
+      <c r="K20" s="137"/>
+      <c r="L20" s="137"/>
+      <c r="M20" s="137"/>
+      <c r="N20" s="137"/>
+      <c r="O20" s="137"/>
+      <c r="P20" s="137"/>
+      <c r="Q20" s="137"/>
+      <c r="R20" s="138"/>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="6">
         <v>17</v>
       </c>
-      <c r="B21" s="119"/>
-      <c r="C21" s="118"/>
-      <c r="D21" s="119"/>
-      <c r="E21" s="118"/>
-      <c r="F21" s="119"/>
-      <c r="G21" s="126"/>
-      <c r="H21" s="118"/>
-      <c r="I21" s="125"/>
-      <c r="J21" s="123"/>
-      <c r="K21" s="123"/>
-      <c r="L21" s="123"/>
-      <c r="M21" s="123"/>
-      <c r="N21" s="123"/>
-      <c r="O21" s="123"/>
-      <c r="P21" s="123"/>
-      <c r="Q21" s="123"/>
-      <c r="R21" s="124"/>
+      <c r="B21" s="133"/>
+      <c r="C21" s="132"/>
+      <c r="D21" s="133"/>
+      <c r="E21" s="132"/>
+      <c r="F21" s="133"/>
+      <c r="G21" s="140"/>
+      <c r="H21" s="132"/>
+      <c r="I21" s="139"/>
+      <c r="J21" s="137"/>
+      <c r="K21" s="137"/>
+      <c r="L21" s="137"/>
+      <c r="M21" s="137"/>
+      <c r="N21" s="137"/>
+      <c r="O21" s="137"/>
+      <c r="P21" s="137"/>
+      <c r="Q21" s="137"/>
+      <c r="R21" s="138"/>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="6">
         <v>18</v>
       </c>
-      <c r="B22" s="119"/>
-      <c r="C22" s="118"/>
-      <c r="D22" s="119"/>
-      <c r="E22" s="118"/>
-      <c r="F22" s="119"/>
-      <c r="G22" s="126"/>
-      <c r="H22" s="118"/>
-      <c r="I22" s="125"/>
-      <c r="J22" s="123"/>
-      <c r="K22" s="123"/>
-      <c r="L22" s="123"/>
-      <c r="M22" s="123"/>
-      <c r="N22" s="123"/>
-      <c r="O22" s="123"/>
-      <c r="P22" s="123"/>
-      <c r="Q22" s="123"/>
-      <c r="R22" s="124"/>
+      <c r="B22" s="133"/>
+      <c r="C22" s="132"/>
+      <c r="D22" s="133"/>
+      <c r="E22" s="132"/>
+      <c r="F22" s="133"/>
+      <c r="G22" s="140"/>
+      <c r="H22" s="132"/>
+      <c r="I22" s="139"/>
+      <c r="J22" s="137"/>
+      <c r="K22" s="137"/>
+      <c r="L22" s="137"/>
+      <c r="M22" s="137"/>
+      <c r="N22" s="137"/>
+      <c r="O22" s="137"/>
+      <c r="P22" s="137"/>
+      <c r="Q22" s="137"/>
+      <c r="R22" s="138"/>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="5"/>
@@ -4062,53 +4240,53 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="88" t="s">
+      <c r="B1" s="86"/>
+      <c r="C1" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
-      <c r="J1" s="89"/>
-      <c r="K1" s="89"/>
-      <c r="L1" s="90"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="86"/>
       <c r="M1" s="24" t="s">
         <v>2</v>
       </c>
       <c r="N1" s="22" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="O1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="161">
+      <c r="P1" s="81">
         <v>46273</v>
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="91"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="91"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="93"/>
+      <c r="A2" s="87"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="107"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="107"/>
+      <c r="I2" s="107"/>
+      <c r="J2" s="107"/>
+      <c r="K2" s="107"/>
+      <c r="L2" s="88"/>
       <c r="M2" s="27" t="s">
         <v>14</v>
       </c>
       <c r="N2" s="28"/>
-      <c r="O2" s="160" t="s">
+      <c r="O2" s="80" t="s">
         <v>15</v>
       </c>
       <c r="P2" s="30"/>
@@ -4129,33 +4307,33 @@
       <c r="M3" s="32"/>
       <c r="N3" s="32"/>
       <c r="O3" s="32"/>
-      <c r="P3" s="156"/>
+      <c r="P3" s="31"/>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="127" t="s">
+      <c r="B4" s="141" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="128"/>
-      <c r="D4" s="128"/>
-      <c r="E4" s="128"/>
-      <c r="F4" s="128"/>
-      <c r="G4" s="129"/>
+      <c r="C4" s="142"/>
+      <c r="D4" s="142"/>
+      <c r="E4" s="142"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="143"/>
       <c r="H4" s="31"/>
-      <c r="I4" s="159" t="s">
+      <c r="I4" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="127" t="s">
+      <c r="J4" s="141" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="128"/>
-      <c r="L4" s="128"/>
-      <c r="M4" s="128"/>
-      <c r="N4" s="128"/>
-      <c r="O4" s="129"/>
-      <c r="P4" s="157"/>
+      <c r="K4" s="142"/>
+      <c r="L4" s="142"/>
+      <c r="M4" s="142"/>
+      <c r="N4" s="142"/>
+      <c r="O4" s="143"/>
+      <c r="P4" s="35"/>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="16"/>
@@ -4173,14 +4351,14 @@
       <c r="M5" s="35"/>
       <c r="N5" s="35"/>
       <c r="O5" s="35"/>
-      <c r="P5" s="157"/>
+      <c r="P5" s="35"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="36" t="s">
         <v>18</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
@@ -4189,24 +4367,24 @@
       <c r="G6" s="31"/>
       <c r="H6" s="7"/>
       <c r="I6" s="36" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J6" s="31" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="K6" s="31"/>
       <c r="L6" s="31"/>
       <c r="M6" s="31"/>
       <c r="N6" s="31"/>
       <c r="O6" s="31"/>
-      <c r="P6" s="158"/>
+      <c r="P6" s="36"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="154" t="s">
-        <v>132</v>
+      <c r="A7" s="77" t="s">
+        <v>128</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
@@ -4214,25 +4392,25 @@
       <c r="F7" s="31"/>
       <c r="G7" s="31"/>
       <c r="H7" s="7"/>
-      <c r="I7" s="154" t="s">
-        <v>152</v>
+      <c r="I7" s="77" t="s">
+        <v>148</v>
       </c>
       <c r="J7" s="31" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="K7" s="31"/>
       <c r="L7" s="31"/>
       <c r="M7" s="31"/>
       <c r="N7" s="31"/>
       <c r="O7" s="31"/>
-      <c r="P7" s="158"/>
+      <c r="P7" s="36"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="154" t="s">
+      <c r="A8" s="77" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="35" t="s">
         <v>133</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>137</v>
       </c>
       <c r="C8" s="35"/>
       <c r="D8" s="35"/>
@@ -4240,25 +4418,25 @@
       <c r="F8" s="35"/>
       <c r="G8" s="35"/>
       <c r="H8" s="7"/>
-      <c r="I8" s="154" t="s">
-        <v>154</v>
+      <c r="I8" s="77" t="s">
+        <v>150</v>
       </c>
       <c r="J8" s="35" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K8" s="35"/>
       <c r="L8" s="35"/>
       <c r="M8" s="35"/>
       <c r="N8" s="35"/>
       <c r="O8" s="35"/>
-      <c r="P8" s="158"/>
+      <c r="P8" s="36"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="154" t="s">
-        <v>134</v>
+      <c r="A9" s="77" t="s">
+        <v>130</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C9" s="31"/>
       <c r="D9" s="31"/>
@@ -4266,21 +4444,21 @@
       <c r="F9" s="31"/>
       <c r="G9" s="31"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="154"/>
+      <c r="I9" s="77"/>
       <c r="J9" s="31"/>
       <c r="K9" s="31"/>
       <c r="L9" s="31"/>
       <c r="M9" s="31"/>
       <c r="N9" s="31"/>
       <c r="O9" s="31"/>
-      <c r="P9" s="158"/>
+      <c r="P9" s="36"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="154" t="s">
-        <v>135</v>
+      <c r="A10" s="77" t="s">
+        <v>131</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C10" s="31"/>
       <c r="D10" s="31"/>
@@ -4289,7 +4467,7 @@
       <c r="G10" s="31"/>
       <c r="H10" s="7"/>
       <c r="I10" s="36" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="J10" s="31"/>
       <c r="K10" s="31"/>
@@ -4297,14 +4475,14 @@
       <c r="M10" s="31"/>
       <c r="N10" s="31"/>
       <c r="O10" s="31"/>
-      <c r="P10" s="158"/>
+      <c r="P10" s="36"/>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="36">
         <v>1.5</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C11" s="31"/>
       <c r="D11" s="31"/>
@@ -4312,18 +4490,18 @@
       <c r="F11" s="31"/>
       <c r="G11" s="31"/>
       <c r="H11" s="7"/>
-      <c r="I11" s="155" t="s">
-        <v>157</v>
+      <c r="I11" s="78" t="s">
+        <v>153</v>
       </c>
       <c r="J11" s="31" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="K11" s="31"/>
       <c r="L11" s="31"/>
       <c r="M11" s="31"/>
       <c r="N11" s="31"/>
       <c r="O11" s="31"/>
-      <c r="P11" s="158"/>
+      <c r="P11" s="36"/>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="36"/>
@@ -4341,14 +4519,14 @@
       <c r="M12" s="31"/>
       <c r="N12" s="31"/>
       <c r="O12" s="31"/>
-      <c r="P12" s="158"/>
+      <c r="P12" s="36"/>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="36" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C13" s="31"/>
       <c r="D13" s="31"/>
@@ -4357,7 +4535,7 @@
       <c r="G13" s="31"/>
       <c r="H13" s="7"/>
       <c r="I13" s="7" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="J13" s="31"/>
       <c r="K13" s="31"/>
@@ -4365,14 +4543,14 @@
       <c r="M13" s="31"/>
       <c r="N13" s="31"/>
       <c r="O13" s="31"/>
-      <c r="P13" s="156"/>
+      <c r="P13" s="31"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="155" t="s">
-        <v>144</v>
+      <c r="A14" s="78" t="s">
+        <v>140</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C14" s="31"/>
       <c r="D14" s="31"/>
@@ -4380,11 +4558,11 @@
       <c r="F14" s="31"/>
       <c r="G14" s="31"/>
       <c r="H14" s="31"/>
-      <c r="I14" s="155" t="s">
-        <v>160</v>
+      <c r="I14" s="78" t="s">
+        <v>156</v>
       </c>
       <c r="J14" s="31" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="K14" s="31"/>
       <c r="L14" s="31"/>
@@ -4394,7 +4572,7 @@
       <c r="P14" s="31"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="155"/>
+      <c r="A15" s="78"/>
       <c r="B15" s="31"/>
       <c r="C15" s="31"/>
       <c r="D15" s="31"/>
@@ -4416,7 +4594,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C16" s="31"/>
       <c r="D16" s="31"/>
@@ -4434,11 +4612,11 @@
       <c r="P16" s="31"/>
     </row>
     <row r="17" spans="1:16" ht="26.5">
-      <c r="A17" s="155" t="s">
-        <v>146</v>
+      <c r="A17" s="78" t="s">
+        <v>142</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C17" s="31"/>
       <c r="D17" s="31"/>
@@ -4456,11 +4634,11 @@
       <c r="P17" s="37"/>
     </row>
     <row r="18" spans="1:16" ht="26.5">
-      <c r="A18" s="155" t="s">
-        <v>148</v>
+      <c r="A18" s="78" t="s">
+        <v>144</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C18" s="35"/>
       <c r="D18" s="35"/>
@@ -4570,28 +4748,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="131" t="s">
+      <c r="B1" s="86"/>
+      <c r="C1" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="132"/>
-      <c r="E1" s="133" t="s">
+      <c r="D1" s="90"/>
+      <c r="E1" s="91" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="135"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="93"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -4601,22 +4779,22 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="91"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="131"/>
-      <c r="D2" s="132"/>
-      <c r="E2" s="133"/>
-      <c r="F2" s="134"/>
-      <c r="G2" s="134"/>
-      <c r="H2" s="134"/>
-      <c r="I2" s="134"/>
-      <c r="J2" s="134"/>
-      <c r="K2" s="135"/>
+      <c r="A2" s="87"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="93"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
       <c r="M2" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N2" s="29" t="s">
         <v>15</v>
@@ -4663,44 +4841,44 @@
     </row>
     <row r="5" spans="1:15" ht="18" customHeight="1">
       <c r="A5" s="8"/>
-      <c r="B5" s="136" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="136"/>
-      <c r="D5" s="136"/>
-      <c r="E5" s="136"/>
-      <c r="F5" s="136"/>
-      <c r="G5" s="136"/>
-      <c r="H5" s="136"/>
-      <c r="I5" s="136"/>
-      <c r="J5" s="136"/>
-      <c r="K5" s="136"/>
-      <c r="L5" s="136"/>
-      <c r="M5" s="136"/>
-      <c r="N5" s="136"/>
+      <c r="B5" s="145" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="145"/>
+      <c r="D5" s="145"/>
+      <c r="E5" s="145"/>
+      <c r="F5" s="145"/>
+      <c r="G5" s="145"/>
+      <c r="H5" s="145"/>
+      <c r="I5" s="145"/>
+      <c r="J5" s="145"/>
+      <c r="K5" s="145"/>
+      <c r="L5" s="145"/>
+      <c r="M5" s="145"/>
+      <c r="N5" s="145"/>
       <c r="O5" s="8"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="35"/>
-      <c r="B6" s="136"/>
-      <c r="C6" s="136"/>
-      <c r="D6" s="136"/>
-      <c r="E6" s="136"/>
-      <c r="F6" s="136"/>
-      <c r="G6" s="136"/>
-      <c r="H6" s="136"/>
-      <c r="I6" s="136"/>
-      <c r="J6" s="136"/>
-      <c r="K6" s="136"/>
-      <c r="L6" s="136"/>
-      <c r="M6" s="136"/>
-      <c r="N6" s="136"/>
+      <c r="B6" s="145"/>
+      <c r="C6" s="145"/>
+      <c r="D6" s="145"/>
+      <c r="E6" s="145"/>
+      <c r="F6" s="145"/>
+      <c r="G6" s="145"/>
+      <c r="H6" s="145"/>
+      <c r="I6" s="145"/>
+      <c r="J6" s="145"/>
+      <c r="K6" s="145"/>
+      <c r="L6" s="145"/>
+      <c r="M6" s="145"/>
+      <c r="N6" s="145"/>
       <c r="O6" s="35"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="35"/>
       <c r="B7" s="35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C7" s="35"/>
       <c r="D7" s="35"/>
@@ -4755,7 +4933,7 @@
     <row r="10" spans="1:15">
       <c r="A10" s="35"/>
       <c r="B10" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -4809,115 +4987,115 @@
     </row>
     <row r="13" spans="1:15" ht="18" customHeight="1">
       <c r="A13" s="35"/>
-      <c r="B13" s="130" t="s">
+      <c r="B13" s="144" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="130"/>
-      <c r="D13" s="130"/>
-      <c r="E13" s="130"/>
-      <c r="F13" s="130"/>
-      <c r="G13" s="130"/>
-      <c r="H13" s="130"/>
-      <c r="I13" s="130"/>
-      <c r="J13" s="130"/>
-      <c r="K13" s="130"/>
-      <c r="L13" s="130"/>
-      <c r="M13" s="130"/>
-      <c r="N13" s="130"/>
-      <c r="O13" s="130"/>
+      <c r="C13" s="144"/>
+      <c r="D13" s="144"/>
+      <c r="E13" s="144"/>
+      <c r="F13" s="144"/>
+      <c r="G13" s="144"/>
+      <c r="H13" s="144"/>
+      <c r="I13" s="144"/>
+      <c r="J13" s="144"/>
+      <c r="K13" s="144"/>
+      <c r="L13" s="144"/>
+      <c r="M13" s="144"/>
+      <c r="N13" s="144"/>
+      <c r="O13" s="144"/>
     </row>
     <row r="14" spans="1:15" ht="18" customHeight="1">
       <c r="A14" s="35"/>
-      <c r="B14" s="130" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" s="130"/>
-      <c r="D14" s="130"/>
-      <c r="E14" s="130"/>
-      <c r="F14" s="130"/>
-      <c r="G14" s="130"/>
-      <c r="H14" s="130"/>
-      <c r="I14" s="130"/>
-      <c r="J14" s="130"/>
-      <c r="K14" s="130"/>
-      <c r="L14" s="130"/>
-      <c r="M14" s="130"/>
-      <c r="N14" s="130"/>
-      <c r="O14" s="130"/>
+      <c r="B14" s="144" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="144"/>
+      <c r="D14" s="144"/>
+      <c r="E14" s="144"/>
+      <c r="F14" s="144"/>
+      <c r="G14" s="144"/>
+      <c r="H14" s="144"/>
+      <c r="I14" s="144"/>
+      <c r="J14" s="144"/>
+      <c r="K14" s="144"/>
+      <c r="L14" s="144"/>
+      <c r="M14" s="144"/>
+      <c r="N14" s="144"/>
+      <c r="O14" s="144"/>
     </row>
     <row r="15" spans="1:15" ht="18" customHeight="1">
       <c r="A15" s="35"/>
-      <c r="B15" s="130" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="130"/>
-      <c r="D15" s="130"/>
-      <c r="E15" s="130"/>
-      <c r="F15" s="130"/>
-      <c r="G15" s="130"/>
-      <c r="H15" s="130"/>
-      <c r="I15" s="130"/>
-      <c r="J15" s="130"/>
-      <c r="K15" s="130"/>
-      <c r="L15" s="130"/>
-      <c r="M15" s="130"/>
-      <c r="N15" s="130"/>
-      <c r="O15" s="130"/>
+      <c r="B15" s="144" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="144"/>
+      <c r="D15" s="144"/>
+      <c r="E15" s="144"/>
+      <c r="F15" s="144"/>
+      <c r="G15" s="144"/>
+      <c r="H15" s="144"/>
+      <c r="I15" s="144"/>
+      <c r="J15" s="144"/>
+      <c r="K15" s="144"/>
+      <c r="L15" s="144"/>
+      <c r="M15" s="144"/>
+      <c r="N15" s="144"/>
+      <c r="O15" s="144"/>
     </row>
     <row r="16" spans="1:15" ht="18" customHeight="1">
       <c r="A16" s="35"/>
-      <c r="B16" s="130" t="s">
-        <v>86</v>
-      </c>
-      <c r="C16" s="130"/>
-      <c r="D16" s="130"/>
-      <c r="E16" s="130"/>
-      <c r="F16" s="130"/>
-      <c r="G16" s="130"/>
-      <c r="H16" s="130"/>
-      <c r="I16" s="130"/>
-      <c r="J16" s="130"/>
-      <c r="K16" s="130"/>
-      <c r="L16" s="130"/>
-      <c r="M16" s="130"/>
-      <c r="N16" s="130"/>
-      <c r="O16" s="130"/>
+      <c r="B16" s="144" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="144"/>
+      <c r="D16" s="144"/>
+      <c r="E16" s="144"/>
+      <c r="F16" s="144"/>
+      <c r="G16" s="144"/>
+      <c r="H16" s="144"/>
+      <c r="I16" s="144"/>
+      <c r="J16" s="144"/>
+      <c r="K16" s="144"/>
+      <c r="L16" s="144"/>
+      <c r="M16" s="144"/>
+      <c r="N16" s="144"/>
+      <c r="O16" s="144"/>
     </row>
     <row r="17" spans="1:15" ht="18" customHeight="1">
       <c r="A17" s="35"/>
-      <c r="B17" s="130" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="130"/>
-      <c r="D17" s="130"/>
-      <c r="E17" s="130"/>
-      <c r="F17" s="130"/>
-      <c r="G17" s="130"/>
-      <c r="H17" s="130"/>
-      <c r="I17" s="130"/>
-      <c r="J17" s="130"/>
-      <c r="K17" s="130"/>
-      <c r="L17" s="130"/>
-      <c r="M17" s="130"/>
-      <c r="N17" s="130"/>
-      <c r="O17" s="130"/>
+      <c r="B17" s="144" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="144"/>
+      <c r="D17" s="144"/>
+      <c r="E17" s="144"/>
+      <c r="F17" s="144"/>
+      <c r="G17" s="144"/>
+      <c r="H17" s="144"/>
+      <c r="I17" s="144"/>
+      <c r="J17" s="144"/>
+      <c r="K17" s="144"/>
+      <c r="L17" s="144"/>
+      <c r="M17" s="144"/>
+      <c r="N17" s="144"/>
+      <c r="O17" s="144"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="35"/>
-      <c r="B18" s="130"/>
-      <c r="C18" s="130"/>
-      <c r="D18" s="130"/>
-      <c r="E18" s="130"/>
-      <c r="F18" s="130"/>
-      <c r="G18" s="130"/>
-      <c r="H18" s="130"/>
-      <c r="I18" s="130"/>
-      <c r="J18" s="130"/>
-      <c r="K18" s="130"/>
-      <c r="L18" s="130"/>
-      <c r="M18" s="130"/>
-      <c r="N18" s="130"/>
-      <c r="O18" s="130"/>
+      <c r="B18" s="144"/>
+      <c r="C18" s="144"/>
+      <c r="D18" s="144"/>
+      <c r="E18" s="144"/>
+      <c r="F18" s="144"/>
+      <c r="G18" s="144"/>
+      <c r="H18" s="144"/>
+      <c r="I18" s="144"/>
+      <c r="J18" s="144"/>
+      <c r="K18" s="144"/>
+      <c r="L18" s="144"/>
+      <c r="M18" s="144"/>
+      <c r="N18" s="144"/>
+      <c r="O18" s="144"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="35"/>
@@ -4958,7 +5136,7 @@
     <row r="21" spans="1:15">
       <c r="A21" s="35"/>
       <c r="B21" s="42" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C21" s="43"/>
       <c r="D21" s="43"/>
@@ -5030,7 +5208,7 @@
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="45" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C25" s="46"/>
       <c r="D25" s="46"/>
@@ -5049,7 +5227,7 @@
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="45" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C26" s="46"/>
       <c r="D26" s="46"/>
@@ -5068,7 +5246,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="45" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C27" s="46"/>
       <c r="D27" s="46"/>
@@ -5122,7 +5300,7 @@
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
       <c r="B30" s="47" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -5141,7 +5319,7 @@
     <row r="31" spans="1:15">
       <c r="A31" s="8"/>
       <c r="B31" s="47" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -5160,7 +5338,7 @@
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="47" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -5222,28 +5400,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="131" t="s">
+      <c r="B1" s="86"/>
+      <c r="C1" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="132"/>
-      <c r="E1" s="133" t="s">
+      <c r="D1" s="90"/>
+      <c r="E1" s="91" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="135"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="93"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -5253,27 +5431,27 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="91"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="131"/>
-      <c r="D2" s="132"/>
-      <c r="E2" s="133"/>
-      <c r="F2" s="134"/>
-      <c r="G2" s="134"/>
-      <c r="H2" s="134"/>
-      <c r="I2" s="134"/>
-      <c r="J2" s="134"/>
-      <c r="K2" s="135"/>
+      <c r="A2" s="87"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="93"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
       <c r="M2" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="74">
+      <c r="O2" s="73">
         <v>46266</v>
       </c>
     </row>
@@ -5332,12 +5510,12 @@
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1">
       <c r="A6" s="35"/>
-      <c r="B6" s="139" t="s">
+      <c r="B6" s="94" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="140"/>
-      <c r="D6" s="49" t="s">
-        <v>34</v>
+      <c r="C6" s="95"/>
+      <c r="D6" s="82" t="s">
+        <v>161</v>
       </c>
       <c r="E6" s="50"/>
       <c r="F6" s="50"/>
@@ -5353,12 +5531,12 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="35"/>
-      <c r="B7" s="137" t="s">
+      <c r="B7" s="83" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="84"/>
+      <c r="D7" s="53" t="s">
         <v>69</v>
-      </c>
-      <c r="C7" s="138"/>
-      <c r="D7" s="53" t="s">
-        <v>70</v>
       </c>
       <c r="E7" s="54"/>
       <c r="F7" s="54"/>
@@ -5374,12 +5552,12 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="35"/>
-      <c r="B8" s="137" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="138"/>
+      <c r="B8" s="83" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="84"/>
       <c r="D8" s="17" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
@@ -5843,16 +6021,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="131" t="s">
+      <c r="B1" s="86"/>
+      <c r="C1" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="132"/>
+      <c r="D1" s="90"/>
       <c r="E1" s="71" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F1" s="71"/>
       <c r="G1" s="71"/>
@@ -5863,36 +6041,40 @@
         <v>2</v>
       </c>
       <c r="L1" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="143">
+      <c r="N1" s="148">
         <v>46260</v>
       </c>
-      <c r="O1" s="143"/>
+      <c r="O1" s="148"/>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="91"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="131"/>
-      <c r="D2" s="132"/>
-      <c r="E2" s="134"/>
-      <c r="F2" s="134"/>
-      <c r="G2" s="134"/>
-      <c r="H2" s="134"/>
-      <c r="I2" s="134"/>
-      <c r="J2" s="135"/>
+      <c r="A2" s="87"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="93"/>
       <c r="K2" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="28"/>
+      <c r="L2" s="26" t="s">
+        <v>67</v>
+      </c>
       <c r="M2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="144"/>
-      <c r="O2" s="144"/>
+      <c r="N2" s="159">
+        <v>46281</v>
+      </c>
+      <c r="O2" s="159"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="40"/>
@@ -5914,7 +6096,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -5950,12 +6132,12 @@
     <row r="6" spans="1:15" ht="18" customHeight="1">
       <c r="A6" s="35"/>
       <c r="B6" s="49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6" s="50"/>
       <c r="D6" s="50"/>
       <c r="E6" s="49" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F6" s="50"/>
       <c r="G6" s="50"/>
@@ -5963,7 +6145,7 @@
       <c r="I6" s="51"/>
       <c r="J6" s="66"/>
       <c r="K6" s="49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L6" s="55"/>
       <c r="M6" s="70"/>
@@ -5973,12 +6155,12 @@
     <row r="7" spans="1:15">
       <c r="A7" s="35"/>
       <c r="B7" s="53" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" s="54"/>
       <c r="D7" s="54"/>
       <c r="E7" s="68" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="54"/>
@@ -5986,7 +6168,7 @@
       <c r="I7" s="54"/>
       <c r="J7" s="55"/>
       <c r="K7" s="69" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L7" s="55"/>
       <c r="M7" s="31"/>
@@ -5996,12 +6178,12 @@
     <row r="8" spans="1:15">
       <c r="A8" s="35"/>
       <c r="B8" s="53" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C8" s="54"/>
       <c r="D8" s="54"/>
       <c r="E8" s="68" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F8" s="23"/>
       <c r="G8" s="54"/>
@@ -6009,7 +6191,7 @@
       <c r="I8" s="54"/>
       <c r="J8" s="55"/>
       <c r="K8" s="69" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L8" s="55"/>
       <c r="M8" s="31"/>
@@ -6019,12 +6201,12 @@
     <row r="9" spans="1:15">
       <c r="A9" s="35"/>
       <c r="B9" s="53" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C9" s="54"/>
       <c r="D9" s="54"/>
       <c r="E9" s="68" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="54"/>
@@ -6032,7 +6214,7 @@
       <c r="I9" s="54"/>
       <c r="J9" s="55"/>
       <c r="K9" s="69" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L9" s="55"/>
       <c r="M9" s="31"/>
@@ -6042,22 +6224,22 @@
     <row r="10" spans="1:15">
       <c r="A10" s="35"/>
       <c r="B10" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
       <c r="E10" s="68" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F10" s="23"/>
       <c r="G10" s="54"/>
       <c r="H10" s="54"/>
       <c r="I10" s="54"/>
       <c r="J10" s="55"/>
-      <c r="K10" s="141" t="s">
-        <v>95</v>
-      </c>
-      <c r="L10" s="142"/>
+      <c r="K10" s="146" t="s">
+        <v>92</v>
+      </c>
+      <c r="L10" s="147"/>
       <c r="M10" s="31"/>
       <c r="N10" s="35"/>
       <c r="O10" s="7"/>
@@ -6082,7 +6264,7 @@
     <row r="12" spans="1:15">
       <c r="A12" s="35"/>
       <c r="B12" s="35" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C12" s="35"/>
       <c r="D12" s="35"/>
@@ -6090,7 +6272,7 @@
     <row r="13" spans="1:15">
       <c r="A13" s="35"/>
       <c r="B13" s="42" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C13" s="42"/>
       <c r="D13" s="42"/>
@@ -6109,7 +6291,7 @@
     <row r="14" spans="1:15">
       <c r="A14" s="35"/>
       <c r="B14" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C14" s="57"/>
       <c r="D14" s="57"/>
@@ -6128,7 +6310,7 @@
     <row r="15" spans="1:15">
       <c r="A15" s="35"/>
       <c r="B15" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C15" s="57"/>
       <c r="D15" s="57"/>
@@ -6164,7 +6346,7 @@
     <row r="17" spans="1:15">
       <c r="A17" s="35"/>
       <c r="B17" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C17" s="57"/>
       <c r="D17" s="57"/>
@@ -6183,7 +6365,7 @@
     <row r="18" spans="1:15">
       <c r="A18" s="35"/>
       <c r="B18" s="57" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C18" s="42"/>
       <c r="D18" s="42"/>
@@ -6219,7 +6401,7 @@
     <row r="20" spans="1:15">
       <c r="A20" s="35"/>
       <c r="B20" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C20" s="42"/>
       <c r="D20" s="42"/>
@@ -6238,7 +6420,7 @@
     <row r="21" spans="1:15" ht="18" customHeight="1">
       <c r="A21" s="44"/>
       <c r="B21" s="57" t="s">
-        <v>92</v>
+        <v>178</v>
       </c>
       <c r="C21" s="44"/>
       <c r="D21" s="44"/>
@@ -6257,7 +6439,7 @@
     <row r="22" spans="1:15" ht="18" customHeight="1">
       <c r="A22" s="8"/>
       <c r="B22" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
@@ -6293,7 +6475,7 @@
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="42" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C24" s="46"/>
       <c r="D24" s="46"/>
@@ -6312,7 +6494,7 @@
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="57" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C25" s="46"/>
       <c r="D25" s="46"/>
@@ -6468,23 +6650,23 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="131" t="s">
+      <c r="B1" s="86"/>
+      <c r="C1" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="132"/>
-      <c r="E1" s="133" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="135"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="91" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="93"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -6499,17 +6681,17 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="91"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="131"/>
-      <c r="D2" s="132"/>
-      <c r="E2" s="133"/>
-      <c r="F2" s="134"/>
-      <c r="G2" s="134"/>
-      <c r="H2" s="134"/>
-      <c r="I2" s="134"/>
-      <c r="J2" s="134"/>
-      <c r="K2" s="135"/>
+      <c r="A2" s="87"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="93"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -6539,7 +6721,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -6592,7 +6774,7 @@
     <row r="7" spans="1:15">
       <c r="A7" s="35"/>
       <c r="B7" s="35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7" s="35"/>
       <c r="D7" s="35"/>
@@ -6662,7 +6844,7 @@
     <row r="11" spans="1:15">
       <c r="A11" s="35"/>
       <c r="B11" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -7084,32 +7266,35 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{140C4B60-E55A-4E72-B14E-C7619F01C68D}">
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="15" max="15" width="9.25" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="131" t="s">
-        <v>57</v>
-      </c>
-      <c r="D1" s="132"/>
-      <c r="E1" s="133" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="135"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="89" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="90"/>
+      <c r="E1" s="91" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="93"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -7119,25 +7304,29 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="91"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="131"/>
-      <c r="D2" s="132"/>
-      <c r="E2" s="133"/>
-      <c r="F2" s="134"/>
-      <c r="G2" s="134"/>
-      <c r="H2" s="134"/>
-      <c r="I2" s="134"/>
-      <c r="J2" s="134"/>
-      <c r="K2" s="135"/>
+      <c r="A2" s="87"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="93"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="58"/>
+      <c r="M2" s="26" t="s">
+        <v>67</v>
+      </c>
       <c r="N2" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="26"/>
+      <c r="O2" s="39">
+        <v>46281</v>
+      </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="40"/>
@@ -7176,23 +7365,23 @@
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
       <c r="B5" s="60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C5" s="61"/>
       <c r="D5" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E5" s="61"/>
       <c r="F5" s="60" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G5" s="61"/>
       <c r="H5" s="60" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I5" s="61"/>
       <c r="J5" s="60" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K5" s="54"/>
       <c r="L5" s="62"/>
@@ -7203,11 +7392,11 @@
     <row r="6" spans="1:15">
       <c r="A6" s="35"/>
       <c r="B6" s="53" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C6" s="56"/>
       <c r="D6" s="53" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="56"/>
       <c r="F6" s="53">
@@ -7215,11 +7404,11 @@
       </c>
       <c r="G6" s="56"/>
       <c r="H6" s="53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I6" s="56"/>
       <c r="J6" s="53" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="K6" s="54"/>
       <c r="L6" s="62"/>
@@ -7230,11 +7419,11 @@
     <row r="7" spans="1:15">
       <c r="A7" s="35"/>
       <c r="B7" s="53" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C7" s="56"/>
       <c r="D7" s="53" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E7" s="56"/>
       <c r="F7" s="53">
@@ -7242,11 +7431,11 @@
       </c>
       <c r="G7" s="56"/>
       <c r="H7" s="53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I7" s="56"/>
       <c r="J7" s="53" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="54"/>
@@ -7257,11 +7446,11 @@
     <row r="8" spans="1:15">
       <c r="A8" s="35"/>
       <c r="B8" s="53" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C8" s="56"/>
       <c r="D8" s="53" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E8" s="56"/>
       <c r="F8" s="53">
@@ -7269,11 +7458,11 @@
       </c>
       <c r="G8" s="56"/>
       <c r="H8" s="53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I8" s="56"/>
       <c r="J8" s="53" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="K8" s="23"/>
       <c r="L8" s="54"/>
@@ -7284,38 +7473,38 @@
     <row r="9" spans="1:15" ht="36" customHeight="1">
       <c r="A9" s="35"/>
       <c r="B9" s="53" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C9" s="56"/>
       <c r="D9" s="17" t="s">
-        <v>104</v>
+        <v>163</v>
       </c>
       <c r="E9" s="56"/>
-      <c r="F9" s="17">
-        <v>8</v>
+      <c r="F9" s="17" t="s">
+        <v>173</v>
       </c>
       <c r="G9" s="56"/>
       <c r="H9" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I9" s="56"/>
-      <c r="J9" s="145" t="s">
-        <v>115</v>
-      </c>
-      <c r="K9" s="146"/>
-      <c r="L9" s="146"/>
-      <c r="M9" s="147"/>
+      <c r="J9" s="149" t="s">
+        <v>111</v>
+      </c>
+      <c r="K9" s="150"/>
+      <c r="L9" s="150"/>
+      <c r="M9" s="151"/>
       <c r="N9" s="8"/>
       <c r="O9" s="35"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="35"/>
       <c r="B10" s="68" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C10" s="56"/>
       <c r="D10" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E10" s="56"/>
       <c r="F10" s="17">
@@ -7323,7 +7512,7 @@
       </c>
       <c r="G10" s="56"/>
       <c r="H10" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="17"/>
@@ -7336,11 +7525,11 @@
     <row r="11" spans="1:15">
       <c r="A11" s="35"/>
       <c r="B11" s="17" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C11" s="56"/>
       <c r="D11" s="17" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E11" s="56"/>
       <c r="F11" s="17">
@@ -7348,11 +7537,11 @@
       </c>
       <c r="G11" s="56"/>
       <c r="H11" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I11" s="56"/>
       <c r="J11" s="17" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="K11" s="23"/>
       <c r="L11" s="23"/>
@@ -7363,11 +7552,11 @@
     <row r="12" spans="1:15">
       <c r="A12" s="35"/>
       <c r="B12" s="17" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C12" s="55"/>
       <c r="D12" s="17" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E12" s="56"/>
       <c r="F12" s="17">
@@ -7375,11 +7564,11 @@
       </c>
       <c r="G12" s="56"/>
       <c r="H12" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I12" s="56"/>
       <c r="J12" s="17" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="23"/>
@@ -7390,11 +7579,11 @@
     <row r="13" spans="1:15">
       <c r="A13" s="35"/>
       <c r="B13" s="53" t="s">
-        <v>108</v>
-      </c>
-      <c r="C13" s="75"/>
+        <v>104</v>
+      </c>
+      <c r="C13" s="74"/>
       <c r="D13" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E13" s="56"/>
       <c r="F13" s="17">
@@ -7402,7 +7591,7 @@
       </c>
       <c r="G13" s="56"/>
       <c r="H13" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I13" s="56"/>
       <c r="J13" s="17"/>
@@ -7414,12 +7603,12 @@
     </row>
     <row r="14" spans="1:15" ht="54" customHeight="1">
       <c r="A14" s="35"/>
-      <c r="B14" s="76" t="s">
-        <v>109</v>
-      </c>
-      <c r="C14" s="75"/>
+      <c r="B14" s="75" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="74"/>
       <c r="D14" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E14" s="56"/>
       <c r="F14" s="17">
@@ -7427,26 +7616,26 @@
       </c>
       <c r="G14" s="56"/>
       <c r="H14" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I14" s="56"/>
-      <c r="J14" s="148" t="s">
-        <v>117</v>
-      </c>
-      <c r="K14" s="149"/>
-      <c r="L14" s="149"/>
-      <c r="M14" s="150"/>
+      <c r="J14" s="152" t="s">
+        <v>113</v>
+      </c>
+      <c r="K14" s="153"/>
+      <c r="L14" s="153"/>
+      <c r="M14" s="154"/>
       <c r="N14" s="42"/>
       <c r="O14" s="42"/>
     </row>
     <row r="15" spans="1:15" ht="36" customHeight="1">
       <c r="A15" s="35"/>
-      <c r="B15" s="76" t="s">
-        <v>110</v>
-      </c>
-      <c r="C15" s="75"/>
+      <c r="B15" s="75" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="74"/>
       <c r="D15" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E15" s="56"/>
       <c r="F15" s="17">
@@ -7454,29 +7643,39 @@
       </c>
       <c r="G15" s="56"/>
       <c r="H15" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I15" s="56"/>
-      <c r="J15" s="151" t="s">
-        <v>118</v>
-      </c>
-      <c r="K15" s="152"/>
-      <c r="L15" s="152"/>
-      <c r="M15" s="153"/>
+      <c r="J15" s="155" t="s">
+        <v>114</v>
+      </c>
+      <c r="K15" s="156"/>
+      <c r="L15" s="156"/>
+      <c r="M15" s="157"/>
       <c r="N15" s="42"/>
       <c r="O15" s="42"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="35"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="17"/>
+      <c r="B16" s="75" t="s">
+        <v>162</v>
+      </c>
+      <c r="C16" s="74"/>
+      <c r="D16" s="75" t="s">
+        <v>163</v>
+      </c>
+      <c r="E16" s="74"/>
+      <c r="F16" s="53" t="s">
+        <v>173</v>
+      </c>
+      <c r="G16" s="74"/>
+      <c r="H16" s="75" t="s">
+        <v>175</v>
+      </c>
+      <c r="I16" s="74"/>
+      <c r="J16" s="17" t="s">
+        <v>176</v>
+      </c>
       <c r="K16" s="23"/>
       <c r="L16" s="23"/>
       <c r="M16" s="56"/>
@@ -7485,69 +7684,107 @@
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="35"/>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="42"/>
-      <c r="K17" s="42"/>
-      <c r="L17" s="42"/>
-      <c r="M17" s="42"/>
+      <c r="B17" s="75" t="s">
+        <v>165</v>
+      </c>
+      <c r="C17" s="74"/>
+      <c r="D17" s="75" t="s">
+        <v>163</v>
+      </c>
+      <c r="E17" s="74"/>
+      <c r="F17" s="53" t="s">
+        <v>173</v>
+      </c>
+      <c r="G17" s="74"/>
+      <c r="H17" s="75" t="s">
+        <v>167</v>
+      </c>
+      <c r="I17" s="74"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="56"/>
       <c r="N17" s="42"/>
       <c r="O17" s="42"/>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" ht="36" customHeight="1">
       <c r="A18" s="35"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="42"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="42"/>
-      <c r="M18" s="42"/>
+      <c r="B18" s="75" t="s">
+        <v>164</v>
+      </c>
+      <c r="C18" s="74"/>
+      <c r="D18" s="75" t="s">
+        <v>166</v>
+      </c>
+      <c r="E18" s="74"/>
+      <c r="F18" s="53">
+        <v>1</v>
+      </c>
+      <c r="G18" s="74"/>
+      <c r="H18" s="75" t="s">
+        <v>168</v>
+      </c>
+      <c r="I18" s="74"/>
+      <c r="J18" s="152" t="s">
+        <v>169</v>
+      </c>
+      <c r="K18" s="153"/>
+      <c r="L18" s="153"/>
+      <c r="M18" s="154"/>
       <c r="N18" s="42"/>
       <c r="O18" s="42"/>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" ht="36" customHeight="1">
       <c r="A19" s="35"/>
-      <c r="B19" s="59"/>
-      <c r="C19" s="59"/>
-      <c r="D19" s="59"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="59"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="59"/>
-      <c r="J19" s="59"/>
-      <c r="K19" s="59"/>
-      <c r="L19" s="59"/>
-      <c r="M19" s="59"/>
-      <c r="N19" s="59"/>
-      <c r="O19" s="59"/>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="B19" s="75" t="s">
+        <v>170</v>
+      </c>
+      <c r="C19" s="74"/>
+      <c r="D19" s="75" t="s">
+        <v>172</v>
+      </c>
+      <c r="E19" s="74"/>
+      <c r="F19" s="53" t="s">
+        <v>173</v>
+      </c>
+      <c r="G19" s="74"/>
+      <c r="H19" s="75" t="s">
+        <v>174</v>
+      </c>
+      <c r="I19" s="74"/>
+      <c r="J19" s="149" t="s">
+        <v>177</v>
+      </c>
+      <c r="K19" s="150"/>
+      <c r="L19" s="150"/>
+      <c r="M19" s="151"/>
+      <c r="N19" s="158"/>
+      <c r="O19" s="42"/>
+    </row>
+    <row r="20" spans="1:15" ht="36" customHeight="1">
       <c r="A20" s="35"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="42"/>
-      <c r="K20" s="42"/>
-      <c r="L20" s="42"/>
-      <c r="M20" s="42"/>
+      <c r="B20" s="75" t="s">
+        <v>171</v>
+      </c>
+      <c r="C20" s="74"/>
+      <c r="D20" s="75" t="s">
+        <v>108</v>
+      </c>
+      <c r="E20" s="74"/>
+      <c r="F20" s="53" t="s">
+        <v>173</v>
+      </c>
+      <c r="G20" s="74"/>
+      <c r="H20" s="75" t="s">
+        <v>173</v>
+      </c>
+      <c r="I20" s="74"/>
+      <c r="J20" s="149" t="s">
+        <v>179</v>
+      </c>
+      <c r="K20" s="150"/>
+      <c r="L20" s="150"/>
+      <c r="M20" s="151"/>
       <c r="N20" s="42"/>
       <c r="O20" s="42"/>
     </row>
@@ -7585,107 +7822,107 @@
       <c r="N22" s="42"/>
       <c r="O22" s="42"/>
     </row>
-    <row r="23" spans="1:15" ht="26.5">
-      <c r="A23" s="44"/>
-      <c r="B23" s="44"/>
-      <c r="C23" s="44"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="44"/>
-      <c r="K23" s="44"/>
-      <c r="L23" s="44"/>
-      <c r="M23" s="44"/>
-      <c r="N23" s="44"/>
-      <c r="O23" s="44"/>
+    <row r="23" spans="1:15">
+      <c r="A23" s="35"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="59"/>
+      <c r="J23" s="59"/>
+      <c r="K23" s="59"/>
+      <c r="L23" s="59"/>
+      <c r="M23" s="59"/>
+      <c r="N23" s="59"/>
+      <c r="O23" s="59"/>
     </row>
     <row r="24" spans="1:15">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
+      <c r="A24" s="35"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="42"/>
+      <c r="K24" s="42"/>
+      <c r="L24" s="42"/>
+      <c r="M24" s="42"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="42"/>
     </row>
     <row r="25" spans="1:15">
-      <c r="A25" s="8"/>
-      <c r="B25" s="57"/>
-      <c r="C25" s="57"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="57"/>
-      <c r="K25" s="57"/>
-      <c r="L25" s="57"/>
-      <c r="M25" s="57"/>
-      <c r="N25" s="57"/>
-      <c r="O25" s="57"/>
+      <c r="A25" s="35"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="42"/>
+      <c r="L25" s="42"/>
+      <c r="M25" s="42"/>
+      <c r="N25" s="42"/>
+      <c r="O25" s="42"/>
     </row>
     <row r="26" spans="1:15">
-      <c r="A26" s="8"/>
-      <c r="B26" s="57"/>
-      <c r="C26" s="57"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="57"/>
-      <c r="J26" s="57"/>
-      <c r="K26" s="57"/>
-      <c r="L26" s="57"/>
-      <c r="M26" s="57"/>
-      <c r="N26" s="57"/>
-      <c r="O26" s="57"/>
-    </row>
-    <row r="27" spans="1:15">
-      <c r="A27" s="8"/>
-      <c r="B27" s="57"/>
-      <c r="C27" s="57"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="57"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="57"/>
-      <c r="H27" s="57"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="57"/>
-      <c r="K27" s="57"/>
-      <c r="L27" s="57"/>
-      <c r="M27" s="57"/>
-      <c r="N27" s="57"/>
-      <c r="O27" s="57"/>
+      <c r="A26" s="35"/>
+      <c r="B26" s="42"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="42"/>
+      <c r="L26" s="42"/>
+      <c r="M26" s="42"/>
+      <c r="N26" s="42"/>
+      <c r="O26" s="42"/>
+    </row>
+    <row r="27" spans="1:15" ht="26.5">
+      <c r="A27" s="44"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="44"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="44"/>
+      <c r="L27" s="44"/>
+      <c r="M27" s="44"/>
+      <c r="N27" s="44"/>
+      <c r="O27" s="44"/>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
-      <c r="B28" s="57"/>
-      <c r="C28" s="57"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="57"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="57"/>
-      <c r="K28" s="57"/>
-      <c r="L28" s="57"/>
-      <c r="M28" s="57"/>
-      <c r="N28" s="57"/>
-      <c r="O28" s="57"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
@@ -7706,71 +7943,71 @@
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="8"/>
-      <c r="O30" s="8"/>
+      <c r="B30" s="57"/>
+      <c r="C30" s="57"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="57"/>
+      <c r="M30" s="57"/>
+      <c r="N30" s="57"/>
+      <c r="O30" s="57"/>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
-      <c r="M31" s="8"/>
-      <c r="N31" s="8"/>
-      <c r="O31" s="8"/>
+      <c r="B31" s="57"/>
+      <c r="C31" s="57"/>
+      <c r="D31" s="57"/>
+      <c r="E31" s="57"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="57"/>
+      <c r="H31" s="57"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="57"/>
+      <c r="L31" s="57"/>
+      <c r="M31" s="57"/>
+      <c r="N31" s="57"/>
+      <c r="O31" s="57"/>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="8"/>
-      <c r="N32" s="8"/>
-      <c r="O32" s="8"/>
+      <c r="B32" s="57"/>
+      <c r="C32" s="57"/>
+      <c r="D32" s="57"/>
+      <c r="E32" s="57"/>
+      <c r="F32" s="57"/>
+      <c r="G32" s="57"/>
+      <c r="H32" s="57"/>
+      <c r="I32" s="57"/>
+      <c r="J32" s="57"/>
+      <c r="K32" s="57"/>
+      <c r="L32" s="57"/>
+      <c r="M32" s="57"/>
+      <c r="N32" s="57"/>
+      <c r="O32" s="57"/>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
-      <c r="M33" s="8"/>
-      <c r="N33" s="8"/>
-      <c r="O33" s="8"/>
+      <c r="B33" s="57"/>
+      <c r="C33" s="57"/>
+      <c r="D33" s="57"/>
+      <c r="E33" s="57"/>
+      <c r="F33" s="57"/>
+      <c r="G33" s="57"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="57"/>
+      <c r="K33" s="57"/>
+      <c r="L33" s="57"/>
+      <c r="M33" s="57"/>
+      <c r="N33" s="57"/>
+      <c r="O33" s="57"/>
     </row>
     <row r="34" spans="1:15">
       <c r="A34" s="8"/>
@@ -7789,8 +8026,79 @@
       <c r="N34" s="8"/>
       <c r="O34" s="8"/>
     </row>
+    <row r="35" spans="1:15">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="8"/>
+      <c r="O35" s="8"/>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
+      <c r="N36" s="8"/>
+      <c r="O36" s="8"/>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="8"/>
+      <c r="N37" s="8"/>
+      <c r="O37" s="8"/>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" s="8"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="8"/>
+      <c r="N38" s="8"/>
+      <c r="O38" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="11">
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="J20:M20"/>
     <mergeCell ref="J9:M9"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="J15:M15"/>
@@ -7811,28 +8119,28 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:16" ht="20">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="131" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="132"/>
-      <c r="E1" s="133" t="s">
-        <v>48</v>
-      </c>
-      <c r="F1" s="134"/>
-      <c r="G1" s="134"/>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="134"/>
-      <c r="K1" s="135"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="89" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="90"/>
+      <c r="E1" s="91" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="93"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -7842,17 +8150,17 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="20">
-      <c r="A2" s="91"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="131"/>
-      <c r="D2" s="132"/>
-      <c r="E2" s="133"/>
-      <c r="F2" s="134"/>
-      <c r="G2" s="134"/>
-      <c r="H2" s="134"/>
-      <c r="I2" s="134"/>
-      <c r="J2" s="134"/>
-      <c r="K2" s="135"/>
+      <c r="A2" s="87"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="93"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -7902,21 +8210,21 @@
         <v>4</v>
       </c>
       <c r="C5" s="60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D5" s="51"/>
       <c r="E5" s="65"/>
       <c r="F5" s="51"/>
       <c r="G5" s="61"/>
       <c r="H5" s="60" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I5" s="65"/>
       <c r="J5" s="51"/>
       <c r="K5" s="51"/>
       <c r="L5" s="66"/>
       <c r="M5" s="60" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N5" s="62"/>
       <c r="O5" s="56"/>
@@ -7927,26 +8235,26 @@
         <v>1</v>
       </c>
       <c r="C6" s="53" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D6" s="51"/>
       <c r="E6" s="23"/>
       <c r="F6" s="51"/>
       <c r="G6" s="56"/>
       <c r="H6" s="53" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I6" s="23"/>
       <c r="J6" s="51"/>
       <c r="K6" s="51"/>
       <c r="L6" s="66"/>
       <c r="M6" s="17" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N6" s="62"/>
       <c r="O6" s="55"/>
       <c r="P6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -7955,21 +8263,21 @@
         <v>2</v>
       </c>
       <c r="C7" s="53" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D7" s="51"/>
       <c r="E7" s="23"/>
       <c r="F7" s="51"/>
       <c r="G7" s="56"/>
       <c r="H7" s="53" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="51"/>
       <c r="K7" s="51"/>
       <c r="L7" s="66"/>
-      <c r="M7" s="77" t="s">
-        <v>125</v>
+      <c r="M7" s="76" t="s">
+        <v>121</v>
       </c>
       <c r="N7" s="54"/>
       <c r="O7" s="55"/>

--- a/要件定義書（採用管理システム）.xlsx
+++ b/要件定義書（採用管理システム）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\my_application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29BF7BBA-EB00-4953-8397-493A528573A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3711475-305E-4500-9B52-EAF73A4D6AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="7" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="183">
   <si>
     <t>要件定義</t>
   </si>
@@ -71,9 +71,6 @@
     <t>文書番号</t>
   </si>
   <si>
-    <t>株式会社 ○○○○</t>
-  </si>
-  <si>
     <t>目次</t>
   </si>
   <si>
@@ -102,9 +99,6 @@
   </si>
   <si>
     <t>業務要件</t>
-  </si>
-  <si>
-    <t>山田太郎</t>
   </si>
   <si>
     <t>1-1. システム化の背景</t>
@@ -1173,16 +1167,6 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>非機能要件</t>
-    <rPh sb="0" eb="3">
-      <t>ヒキノウ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ヨウケン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>渡辺のぞみ</t>
     <rPh sb="0" eb="2">
       <t>ワタナベ</t>
@@ -1743,6 +1727,50 @@
     </rPh>
     <rPh sb="24" eb="26">
       <t>タカハシ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>半角英数字、＠、．（ドット）、-（ハイフン）</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・画面遷移・表示3秒以内</t>
+    <rPh sb="1" eb="5">
+      <t>ガメンセンイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>ビョウイナイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・ログイン機能をつける</t>
+    <rPh sb="5" eb="7">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・システム稼働時間は8:00～21:00とする</t>
+  </si>
+  <si>
+    <t>渡辺のぞみ</t>
+    <rPh sb="0" eb="2">
+      <t>ワタナベ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>非機能要件（作成）</t>
+    <rPh sb="0" eb="5">
+      <t>ヒキノウヨウケン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>サクセイ</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -2257,7 +2285,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2504,198 +2532,204 @@
     <xf numFmtId="56" fontId="5" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -2705,6 +2739,18 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2714,15 +2760,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2731,12 +2768,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3146,44 +3177,44 @@
       <c r="P5" s="8"/>
     </row>
     <row r="6" spans="1:16" ht="39" customHeight="1">
-      <c r="A6" s="96"/>
-      <c r="B6" s="97"/>
-      <c r="C6" s="98"/>
-      <c r="D6" s="99" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="99"/>
-      <c r="F6" s="99"/>
-      <c r="G6" s="99"/>
-      <c r="H6" s="99"/>
-      <c r="I6" s="99"/>
-      <c r="J6" s="99"/>
-      <c r="K6" s="99"/>
-      <c r="L6" s="99"/>
-      <c r="M6" s="99"/>
-      <c r="N6" s="97"/>
-      <c r="O6" s="98"/>
-      <c r="P6" s="96"/>
+      <c r="A6" s="94"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="97" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="97"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="97"/>
+      <c r="H6" s="97"/>
+      <c r="I6" s="97"/>
+      <c r="J6" s="97"/>
+      <c r="K6" s="97"/>
+      <c r="L6" s="97"/>
+      <c r="M6" s="97"/>
+      <c r="N6" s="95"/>
+      <c r="O6" s="96"/>
+      <c r="P6" s="94"/>
     </row>
     <row r="7" spans="1:16" ht="39" customHeight="1">
-      <c r="A7" s="96"/>
-      <c r="B7" s="97"/>
-      <c r="C7" s="98"/>
-      <c r="D7" s="99" t="s">
+      <c r="A7" s="94"/>
+      <c r="B7" s="95"/>
+      <c r="C7" s="96"/>
+      <c r="D7" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="99"/>
-      <c r="F7" s="99"/>
-      <c r="G7" s="99"/>
-      <c r="H7" s="99"/>
-      <c r="I7" s="99"/>
-      <c r="J7" s="99"/>
-      <c r="K7" s="99"/>
-      <c r="L7" s="99"/>
-      <c r="M7" s="99"/>
-      <c r="N7" s="97"/>
-      <c r="O7" s="98"/>
-      <c r="P7" s="96"/>
+      <c r="E7" s="97"/>
+      <c r="F7" s="97"/>
+      <c r="G7" s="97"/>
+      <c r="H7" s="97"/>
+      <c r="I7" s="97"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="97"/>
+      <c r="L7" s="97"/>
+      <c r="M7" s="97"/>
+      <c r="N7" s="95"/>
+      <c r="O7" s="96"/>
+      <c r="P7" s="94"/>
     </row>
     <row r="8" spans="1:16" ht="18.5" thickBot="1">
       <c r="A8" s="8"/>
@@ -3245,16 +3276,16 @@
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
-      <c r="F11" s="100" t="s">
+      <c r="F11" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="101"/>
-      <c r="H11" s="102" t="s">
-        <v>59</v>
-      </c>
-      <c r="I11" s="103"/>
-      <c r="J11" s="103"/>
-      <c r="K11" s="103"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="100" t="s">
+        <v>57</v>
+      </c>
+      <c r="I11" s="101"/>
+      <c r="J11" s="101"/>
+      <c r="K11" s="101"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -3267,16 +3298,16 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
-      <c r="F12" s="100" t="s">
+      <c r="F12" s="98" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="101"/>
-      <c r="H12" s="104">
+      <c r="G12" s="99"/>
+      <c r="H12" s="102">
         <v>46265</v>
       </c>
-      <c r="I12" s="105"/>
-      <c r="J12" s="105"/>
-      <c r="K12" s="105"/>
+      <c r="I12" s="103"/>
+      <c r="J12" s="103"/>
+      <c r="K12" s="103"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
@@ -3289,16 +3320,16 @@
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
-      <c r="F13" s="100" t="s">
+      <c r="F13" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="101"/>
-      <c r="H13" s="104">
-        <v>46273</v>
-      </c>
-      <c r="I13" s="105"/>
-      <c r="J13" s="105"/>
-      <c r="K13" s="105"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="102">
+        <v>46294</v>
+      </c>
+      <c r="I13" s="103"/>
+      <c r="J13" s="103"/>
+      <c r="K13" s="103"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
@@ -3311,14 +3342,14 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
-      <c r="F14" s="100" t="s">
+      <c r="F14" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="101"/>
-      <c r="H14" s="102"/>
-      <c r="I14" s="103"/>
-      <c r="J14" s="103"/>
-      <c r="K14" s="103"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="100"/>
+      <c r="I14" s="101"/>
+      <c r="J14" s="101"/>
+      <c r="K14" s="101"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
@@ -3440,9 +3471,7 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
-      <c r="G21" s="21" t="s">
-        <v>12</v>
-      </c>
+      <c r="G21" s="21"/>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
       <c r="J21" s="8"/>
@@ -3486,53 +3515,53 @@
       <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="106"/>
+      <c r="B1" s="104"/>
       <c r="C1" s="86"/>
-      <c r="D1" s="108" t="s">
+      <c r="D1" s="106" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="110"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="108"/>
       <c r="P1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="114" t="s">
-        <v>123</v>
-      </c>
-      <c r="R1" s="115"/>
+      <c r="Q1" s="112" t="s">
+        <v>120</v>
+      </c>
+      <c r="R1" s="113"/>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="87"/>
-      <c r="B2" s="107"/>
+      <c r="B2" s="105"/>
       <c r="C2" s="88"/>
-      <c r="D2" s="111"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="112"/>
-      <c r="G2" s="112"/>
-      <c r="H2" s="112"/>
-      <c r="I2" s="112"/>
-      <c r="J2" s="112"/>
-      <c r="K2" s="112"/>
-      <c r="L2" s="112"/>
-      <c r="M2" s="112"/>
-      <c r="N2" s="112"/>
-      <c r="O2" s="113"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="110"/>
+      <c r="H2" s="110"/>
+      <c r="I2" s="110"/>
+      <c r="J2" s="110"/>
+      <c r="K2" s="110"/>
+      <c r="L2" s="110"/>
+      <c r="M2" s="110"/>
+      <c r="N2" s="110"/>
+      <c r="O2" s="111"/>
       <c r="P2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="116">
+      <c r="Q2" s="114">
         <v>46273</v>
       </c>
-      <c r="R2" s="117"/>
+      <c r="R2" s="115"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="2"/>
@@ -3558,453 +3587,459 @@
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="118" t="s">
+      <c r="B4" s="116" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="119"/>
-      <c r="D4" s="118" t="s">
+      <c r="C4" s="117"/>
+      <c r="D4" s="116" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="119"/>
-      <c r="F4" s="118" t="s">
+      <c r="E4" s="117"/>
+      <c r="F4" s="116" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="120"/>
-      <c r="H4" s="119"/>
-      <c r="I4" s="118" t="s">
+      <c r="G4" s="118"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="116" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="120"/>
-      <c r="K4" s="120"/>
-      <c r="L4" s="120"/>
-      <c r="M4" s="120"/>
-      <c r="N4" s="120"/>
-      <c r="O4" s="120"/>
-      <c r="P4" s="120"/>
-      <c r="Q4" s="120"/>
-      <c r="R4" s="119"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="118"/>
+      <c r="M4" s="118"/>
+      <c r="N4" s="118"/>
+      <c r="O4" s="118"/>
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="117"/>
     </row>
     <row r="5" spans="1:18" ht="36" customHeight="1">
       <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="121">
+      <c r="B5" s="119">
         <v>46260</v>
       </c>
-      <c r="C5" s="122"/>
-      <c r="D5" s="123" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="124"/>
-      <c r="F5" s="125" t="s">
-        <v>124</v>
-      </c>
-      <c r="G5" s="126"/>
-      <c r="H5" s="127"/>
-      <c r="I5" s="128"/>
-      <c r="J5" s="129"/>
-      <c r="K5" s="129"/>
-      <c r="L5" s="129"/>
-      <c r="M5" s="129"/>
-      <c r="N5" s="129"/>
-      <c r="O5" s="129"/>
-      <c r="P5" s="129"/>
-      <c r="Q5" s="129"/>
-      <c r="R5" s="130"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="121" t="s">
+        <v>120</v>
+      </c>
+      <c r="E5" s="122"/>
+      <c r="F5" s="123" t="s">
+        <v>121</v>
+      </c>
+      <c r="G5" s="124"/>
+      <c r="H5" s="125"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="127"/>
+      <c r="K5" s="127"/>
+      <c r="L5" s="127"/>
+      <c r="M5" s="127"/>
+      <c r="N5" s="127"/>
+      <c r="O5" s="127"/>
+      <c r="P5" s="127"/>
+      <c r="Q5" s="127"/>
+      <c r="R5" s="128"/>
     </row>
     <row r="6" spans="1:18" ht="36" customHeight="1">
       <c r="A6" s="6">
         <v>2</v>
       </c>
-      <c r="B6" s="131">
+      <c r="B6" s="129">
         <v>46266</v>
       </c>
-      <c r="C6" s="132"/>
-      <c r="D6" s="133" t="s">
-        <v>123</v>
-      </c>
-      <c r="E6" s="132"/>
-      <c r="F6" s="134" t="s">
-        <v>125</v>
-      </c>
-      <c r="G6" s="135"/>
-      <c r="H6" s="136"/>
-      <c r="I6" s="134" t="s">
-        <v>127</v>
-      </c>
-      <c r="J6" s="137"/>
-      <c r="K6" s="137"/>
-      <c r="L6" s="137"/>
-      <c r="M6" s="137"/>
-      <c r="N6" s="137"/>
-      <c r="O6" s="137"/>
-      <c r="P6" s="137"/>
-      <c r="Q6" s="137"/>
-      <c r="R6" s="138"/>
+      <c r="C6" s="130"/>
+      <c r="D6" s="131" t="s">
+        <v>120</v>
+      </c>
+      <c r="E6" s="130"/>
+      <c r="F6" s="132" t="s">
+        <v>122</v>
+      </c>
+      <c r="G6" s="133"/>
+      <c r="H6" s="134"/>
+      <c r="I6" s="132" t="s">
+        <v>124</v>
+      </c>
+      <c r="J6" s="135"/>
+      <c r="K6" s="135"/>
+      <c r="L6" s="135"/>
+      <c r="M6" s="135"/>
+      <c r="N6" s="135"/>
+      <c r="O6" s="135"/>
+      <c r="P6" s="135"/>
+      <c r="Q6" s="135"/>
+      <c r="R6" s="136"/>
     </row>
     <row r="7" spans="1:18" ht="36" customHeight="1">
       <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="131">
+      <c r="B7" s="129">
         <v>46268</v>
       </c>
-      <c r="C7" s="132"/>
-      <c r="D7" s="133" t="s">
+      <c r="C7" s="130"/>
+      <c r="D7" s="131" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" s="130"/>
+      <c r="F7" s="132" t="s">
         <v>123</v>
       </c>
-      <c r="E7" s="132"/>
-      <c r="F7" s="134" t="s">
-        <v>126</v>
-      </c>
-      <c r="G7" s="135"/>
-      <c r="H7" s="136"/>
-      <c r="I7" s="139"/>
-      <c r="J7" s="137"/>
-      <c r="K7" s="137"/>
-      <c r="L7" s="137"/>
-      <c r="M7" s="137"/>
-      <c r="N7" s="137"/>
-      <c r="O7" s="137"/>
-      <c r="P7" s="137"/>
-      <c r="Q7" s="137"/>
-      <c r="R7" s="138"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="134"/>
+      <c r="I7" s="137"/>
+      <c r="J7" s="135"/>
+      <c r="K7" s="135"/>
+      <c r="L7" s="135"/>
+      <c r="M7" s="135"/>
+      <c r="N7" s="135"/>
+      <c r="O7" s="135"/>
+      <c r="P7" s="135"/>
+      <c r="Q7" s="135"/>
+      <c r="R7" s="136"/>
     </row>
     <row r="8" spans="1:18" ht="36" customHeight="1">
       <c r="A8" s="6">
         <v>4</v>
       </c>
-      <c r="B8" s="131">
+      <c r="B8" s="129">
         <v>46273</v>
       </c>
-      <c r="C8" s="132"/>
-      <c r="D8" s="133" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" s="132"/>
-      <c r="F8" s="139" t="s">
-        <v>159</v>
-      </c>
-      <c r="G8" s="137"/>
-      <c r="H8" s="138"/>
-      <c r="I8" s="139"/>
-      <c r="J8" s="137"/>
-      <c r="K8" s="137"/>
-      <c r="L8" s="137"/>
-      <c r="M8" s="137"/>
-      <c r="N8" s="137"/>
-      <c r="O8" s="137"/>
-      <c r="P8" s="137"/>
-      <c r="Q8" s="137"/>
-      <c r="R8" s="138"/>
+      <c r="C8" s="130"/>
+      <c r="D8" s="131" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="130"/>
+      <c r="F8" s="137" t="s">
+        <v>156</v>
+      </c>
+      <c r="G8" s="135"/>
+      <c r="H8" s="136"/>
+      <c r="I8" s="137"/>
+      <c r="J8" s="135"/>
+      <c r="K8" s="135"/>
+      <c r="L8" s="135"/>
+      <c r="M8" s="135"/>
+      <c r="N8" s="135"/>
+      <c r="O8" s="135"/>
+      <c r="P8" s="135"/>
+      <c r="Q8" s="135"/>
+      <c r="R8" s="136"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="6">
         <v>5</v>
       </c>
-      <c r="B9" s="133"/>
-      <c r="C9" s="132"/>
-      <c r="D9" s="133"/>
-      <c r="E9" s="132"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="140"/>
-      <c r="H9" s="132"/>
-      <c r="I9" s="139"/>
-      <c r="J9" s="137"/>
-      <c r="K9" s="137"/>
-      <c r="L9" s="137"/>
-      <c r="M9" s="137"/>
-      <c r="N9" s="137"/>
-      <c r="O9" s="137"/>
-      <c r="P9" s="137"/>
-      <c r="Q9" s="137"/>
-      <c r="R9" s="138"/>
+      <c r="B9" s="129">
+        <v>46294</v>
+      </c>
+      <c r="C9" s="130"/>
+      <c r="D9" s="131" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="130"/>
+      <c r="F9" s="137" t="s">
+        <v>182</v>
+      </c>
+      <c r="G9" s="135"/>
+      <c r="H9" s="136"/>
+      <c r="I9" s="137"/>
+      <c r="J9" s="135"/>
+      <c r="K9" s="135"/>
+      <c r="L9" s="135"/>
+      <c r="M9" s="135"/>
+      <c r="N9" s="135"/>
+      <c r="O9" s="135"/>
+      <c r="P9" s="135"/>
+      <c r="Q9" s="135"/>
+      <c r="R9" s="136"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="6">
         <v>6</v>
       </c>
-      <c r="B10" s="133"/>
-      <c r="C10" s="132"/>
-      <c r="D10" s="133"/>
-      <c r="E10" s="132"/>
-      <c r="F10" s="133"/>
-      <c r="G10" s="140"/>
-      <c r="H10" s="132"/>
-      <c r="I10" s="139"/>
-      <c r="J10" s="137"/>
-      <c r="K10" s="137"/>
-      <c r="L10" s="137"/>
-      <c r="M10" s="137"/>
-      <c r="N10" s="137"/>
-      <c r="O10" s="137"/>
-      <c r="P10" s="137"/>
-      <c r="Q10" s="137"/>
-      <c r="R10" s="138"/>
+      <c r="B10" s="131"/>
+      <c r="C10" s="130"/>
+      <c r="D10" s="131"/>
+      <c r="E10" s="130"/>
+      <c r="F10" s="131"/>
+      <c r="G10" s="138"/>
+      <c r="H10" s="130"/>
+      <c r="I10" s="137"/>
+      <c r="J10" s="135"/>
+      <c r="K10" s="135"/>
+      <c r="L10" s="135"/>
+      <c r="M10" s="135"/>
+      <c r="N10" s="135"/>
+      <c r="O10" s="135"/>
+      <c r="P10" s="135"/>
+      <c r="Q10" s="135"/>
+      <c r="R10" s="136"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="6">
         <v>7</v>
       </c>
-      <c r="B11" s="133"/>
-      <c r="C11" s="132"/>
-      <c r="D11" s="133"/>
-      <c r="E11" s="132"/>
-      <c r="F11" s="133"/>
-      <c r="G11" s="140"/>
-      <c r="H11" s="132"/>
-      <c r="I11" s="139"/>
-      <c r="J11" s="137"/>
-      <c r="K11" s="137"/>
-      <c r="L11" s="137"/>
-      <c r="M11" s="137"/>
-      <c r="N11" s="137"/>
-      <c r="O11" s="137"/>
-      <c r="P11" s="137"/>
-      <c r="Q11" s="137"/>
-      <c r="R11" s="138"/>
+      <c r="B11" s="131"/>
+      <c r="C11" s="130"/>
+      <c r="D11" s="131"/>
+      <c r="E11" s="130"/>
+      <c r="F11" s="131"/>
+      <c r="G11" s="138"/>
+      <c r="H11" s="130"/>
+      <c r="I11" s="137"/>
+      <c r="J11" s="135"/>
+      <c r="K11" s="135"/>
+      <c r="L11" s="135"/>
+      <c r="M11" s="135"/>
+      <c r="N11" s="135"/>
+      <c r="O11" s="135"/>
+      <c r="P11" s="135"/>
+      <c r="Q11" s="135"/>
+      <c r="R11" s="136"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="6">
         <v>8</v>
       </c>
-      <c r="B12" s="133"/>
-      <c r="C12" s="132"/>
-      <c r="D12" s="133"/>
-      <c r="E12" s="132"/>
-      <c r="F12" s="133"/>
-      <c r="G12" s="140"/>
-      <c r="H12" s="132"/>
-      <c r="I12" s="139"/>
-      <c r="J12" s="137"/>
-      <c r="K12" s="137"/>
-      <c r="L12" s="137"/>
-      <c r="M12" s="137"/>
-      <c r="N12" s="137"/>
-      <c r="O12" s="137"/>
-      <c r="P12" s="137"/>
-      <c r="Q12" s="137"/>
-      <c r="R12" s="138"/>
+      <c r="B12" s="131"/>
+      <c r="C12" s="130"/>
+      <c r="D12" s="131"/>
+      <c r="E12" s="130"/>
+      <c r="F12" s="131"/>
+      <c r="G12" s="138"/>
+      <c r="H12" s="130"/>
+      <c r="I12" s="137"/>
+      <c r="J12" s="135"/>
+      <c r="K12" s="135"/>
+      <c r="L12" s="135"/>
+      <c r="M12" s="135"/>
+      <c r="N12" s="135"/>
+      <c r="O12" s="135"/>
+      <c r="P12" s="135"/>
+      <c r="Q12" s="135"/>
+      <c r="R12" s="136"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="6">
         <v>9</v>
       </c>
-      <c r="B13" s="133"/>
-      <c r="C13" s="132"/>
-      <c r="D13" s="133"/>
-      <c r="E13" s="132"/>
-      <c r="F13" s="133"/>
-      <c r="G13" s="140"/>
-      <c r="H13" s="132"/>
-      <c r="I13" s="139"/>
-      <c r="J13" s="137"/>
-      <c r="K13" s="137"/>
-      <c r="L13" s="137"/>
-      <c r="M13" s="137"/>
-      <c r="N13" s="137"/>
-      <c r="O13" s="137"/>
-      <c r="P13" s="137"/>
-      <c r="Q13" s="137"/>
-      <c r="R13" s="138"/>
+      <c r="B13" s="131"/>
+      <c r="C13" s="130"/>
+      <c r="D13" s="131"/>
+      <c r="E13" s="130"/>
+      <c r="F13" s="131"/>
+      <c r="G13" s="138"/>
+      <c r="H13" s="130"/>
+      <c r="I13" s="137"/>
+      <c r="J13" s="135"/>
+      <c r="K13" s="135"/>
+      <c r="L13" s="135"/>
+      <c r="M13" s="135"/>
+      <c r="N13" s="135"/>
+      <c r="O13" s="135"/>
+      <c r="P13" s="135"/>
+      <c r="Q13" s="135"/>
+      <c r="R13" s="136"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="6">
         <v>10</v>
       </c>
-      <c r="B14" s="133"/>
-      <c r="C14" s="132"/>
-      <c r="D14" s="133"/>
-      <c r="E14" s="132"/>
-      <c r="F14" s="133"/>
-      <c r="G14" s="140"/>
-      <c r="H14" s="132"/>
-      <c r="I14" s="139"/>
-      <c r="J14" s="137"/>
-      <c r="K14" s="137"/>
-      <c r="L14" s="137"/>
-      <c r="M14" s="137"/>
-      <c r="N14" s="137"/>
-      <c r="O14" s="137"/>
-      <c r="P14" s="137"/>
-      <c r="Q14" s="137"/>
-      <c r="R14" s="138"/>
+      <c r="B14" s="131"/>
+      <c r="C14" s="130"/>
+      <c r="D14" s="131"/>
+      <c r="E14" s="130"/>
+      <c r="F14" s="131"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="130"/>
+      <c r="I14" s="137"/>
+      <c r="J14" s="135"/>
+      <c r="K14" s="135"/>
+      <c r="L14" s="135"/>
+      <c r="M14" s="135"/>
+      <c r="N14" s="135"/>
+      <c r="O14" s="135"/>
+      <c r="P14" s="135"/>
+      <c r="Q14" s="135"/>
+      <c r="R14" s="136"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="6">
         <v>11</v>
       </c>
-      <c r="B15" s="133"/>
-      <c r="C15" s="132"/>
-      <c r="D15" s="133"/>
-      <c r="E15" s="132"/>
-      <c r="F15" s="133"/>
-      <c r="G15" s="140"/>
-      <c r="H15" s="132"/>
-      <c r="I15" s="139"/>
-      <c r="J15" s="137"/>
-      <c r="K15" s="137"/>
-      <c r="L15" s="137"/>
-      <c r="M15" s="137"/>
-      <c r="N15" s="137"/>
-      <c r="O15" s="137"/>
-      <c r="P15" s="137"/>
-      <c r="Q15" s="137"/>
-      <c r="R15" s="138"/>
+      <c r="B15" s="131"/>
+      <c r="C15" s="130"/>
+      <c r="D15" s="131"/>
+      <c r="E15" s="130"/>
+      <c r="F15" s="131"/>
+      <c r="G15" s="138"/>
+      <c r="H15" s="130"/>
+      <c r="I15" s="137"/>
+      <c r="J15" s="135"/>
+      <c r="K15" s="135"/>
+      <c r="L15" s="135"/>
+      <c r="M15" s="135"/>
+      <c r="N15" s="135"/>
+      <c r="O15" s="135"/>
+      <c r="P15" s="135"/>
+      <c r="Q15" s="135"/>
+      <c r="R15" s="136"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="6">
         <v>12</v>
       </c>
-      <c r="B16" s="133"/>
-      <c r="C16" s="132"/>
-      <c r="D16" s="133"/>
-      <c r="E16" s="132"/>
-      <c r="F16" s="133"/>
-      <c r="G16" s="140"/>
-      <c r="H16" s="132"/>
-      <c r="I16" s="139"/>
-      <c r="J16" s="137"/>
-      <c r="K16" s="137"/>
-      <c r="L16" s="137"/>
-      <c r="M16" s="137"/>
-      <c r="N16" s="137"/>
-      <c r="O16" s="137"/>
-      <c r="P16" s="137"/>
-      <c r="Q16" s="137"/>
-      <c r="R16" s="138"/>
+      <c r="B16" s="131"/>
+      <c r="C16" s="130"/>
+      <c r="D16" s="131"/>
+      <c r="E16" s="130"/>
+      <c r="F16" s="131"/>
+      <c r="G16" s="138"/>
+      <c r="H16" s="130"/>
+      <c r="I16" s="137"/>
+      <c r="J16" s="135"/>
+      <c r="K16" s="135"/>
+      <c r="L16" s="135"/>
+      <c r="M16" s="135"/>
+      <c r="N16" s="135"/>
+      <c r="O16" s="135"/>
+      <c r="P16" s="135"/>
+      <c r="Q16" s="135"/>
+      <c r="R16" s="136"/>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="6">
         <v>13</v>
       </c>
-      <c r="B17" s="133"/>
-      <c r="C17" s="132"/>
-      <c r="D17" s="133"/>
-      <c r="E17" s="132"/>
-      <c r="F17" s="133"/>
-      <c r="G17" s="140"/>
-      <c r="H17" s="132"/>
-      <c r="I17" s="139"/>
-      <c r="J17" s="137"/>
-      <c r="K17" s="137"/>
-      <c r="L17" s="137"/>
-      <c r="M17" s="137"/>
-      <c r="N17" s="137"/>
-      <c r="O17" s="137"/>
-      <c r="P17" s="137"/>
-      <c r="Q17" s="137"/>
-      <c r="R17" s="138"/>
+      <c r="B17" s="131"/>
+      <c r="C17" s="130"/>
+      <c r="D17" s="131"/>
+      <c r="E17" s="130"/>
+      <c r="F17" s="131"/>
+      <c r="G17" s="138"/>
+      <c r="H17" s="130"/>
+      <c r="I17" s="137"/>
+      <c r="J17" s="135"/>
+      <c r="K17" s="135"/>
+      <c r="L17" s="135"/>
+      <c r="M17" s="135"/>
+      <c r="N17" s="135"/>
+      <c r="O17" s="135"/>
+      <c r="P17" s="135"/>
+      <c r="Q17" s="135"/>
+      <c r="R17" s="136"/>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="6">
         <v>14</v>
       </c>
-      <c r="B18" s="133"/>
-      <c r="C18" s="132"/>
-      <c r="D18" s="133"/>
-      <c r="E18" s="132"/>
-      <c r="F18" s="133"/>
-      <c r="G18" s="140"/>
-      <c r="H18" s="132"/>
-      <c r="I18" s="139"/>
-      <c r="J18" s="137"/>
-      <c r="K18" s="137"/>
-      <c r="L18" s="137"/>
-      <c r="M18" s="137"/>
-      <c r="N18" s="137"/>
-      <c r="O18" s="137"/>
-      <c r="P18" s="137"/>
-      <c r="Q18" s="137"/>
-      <c r="R18" s="138"/>
+      <c r="B18" s="131"/>
+      <c r="C18" s="130"/>
+      <c r="D18" s="131"/>
+      <c r="E18" s="130"/>
+      <c r="F18" s="131"/>
+      <c r="G18" s="138"/>
+      <c r="H18" s="130"/>
+      <c r="I18" s="137"/>
+      <c r="J18" s="135"/>
+      <c r="K18" s="135"/>
+      <c r="L18" s="135"/>
+      <c r="M18" s="135"/>
+      <c r="N18" s="135"/>
+      <c r="O18" s="135"/>
+      <c r="P18" s="135"/>
+      <c r="Q18" s="135"/>
+      <c r="R18" s="136"/>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="6">
         <v>15</v>
       </c>
-      <c r="B19" s="133"/>
-      <c r="C19" s="132"/>
-      <c r="D19" s="133"/>
-      <c r="E19" s="132"/>
-      <c r="F19" s="133"/>
-      <c r="G19" s="140"/>
-      <c r="H19" s="132"/>
-      <c r="I19" s="139"/>
-      <c r="J19" s="137"/>
-      <c r="K19" s="137"/>
-      <c r="L19" s="137"/>
-      <c r="M19" s="137"/>
-      <c r="N19" s="137"/>
-      <c r="O19" s="137"/>
-      <c r="P19" s="137"/>
-      <c r="Q19" s="137"/>
-      <c r="R19" s="138"/>
+      <c r="B19" s="131"/>
+      <c r="C19" s="130"/>
+      <c r="D19" s="131"/>
+      <c r="E19" s="130"/>
+      <c r="F19" s="131"/>
+      <c r="G19" s="138"/>
+      <c r="H19" s="130"/>
+      <c r="I19" s="137"/>
+      <c r="J19" s="135"/>
+      <c r="K19" s="135"/>
+      <c r="L19" s="135"/>
+      <c r="M19" s="135"/>
+      <c r="N19" s="135"/>
+      <c r="O19" s="135"/>
+      <c r="P19" s="135"/>
+      <c r="Q19" s="135"/>
+      <c r="R19" s="136"/>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="6">
         <v>16</v>
       </c>
-      <c r="B20" s="133"/>
-      <c r="C20" s="132"/>
-      <c r="D20" s="133"/>
-      <c r="E20" s="132"/>
-      <c r="F20" s="133"/>
-      <c r="G20" s="140"/>
-      <c r="H20" s="132"/>
-      <c r="I20" s="139"/>
-      <c r="J20" s="137"/>
-      <c r="K20" s="137"/>
-      <c r="L20" s="137"/>
-      <c r="M20" s="137"/>
-      <c r="N20" s="137"/>
-      <c r="O20" s="137"/>
-      <c r="P20" s="137"/>
-      <c r="Q20" s="137"/>
-      <c r="R20" s="138"/>
+      <c r="B20" s="131"/>
+      <c r="C20" s="130"/>
+      <c r="D20" s="131"/>
+      <c r="E20" s="130"/>
+      <c r="F20" s="131"/>
+      <c r="G20" s="138"/>
+      <c r="H20" s="130"/>
+      <c r="I20" s="137"/>
+      <c r="J20" s="135"/>
+      <c r="K20" s="135"/>
+      <c r="L20" s="135"/>
+      <c r="M20" s="135"/>
+      <c r="N20" s="135"/>
+      <c r="O20" s="135"/>
+      <c r="P20" s="135"/>
+      <c r="Q20" s="135"/>
+      <c r="R20" s="136"/>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="6">
         <v>17</v>
       </c>
-      <c r="B21" s="133"/>
-      <c r="C21" s="132"/>
-      <c r="D21" s="133"/>
-      <c r="E21" s="132"/>
-      <c r="F21" s="133"/>
-      <c r="G21" s="140"/>
-      <c r="H21" s="132"/>
-      <c r="I21" s="139"/>
-      <c r="J21" s="137"/>
-      <c r="K21" s="137"/>
-      <c r="L21" s="137"/>
-      <c r="M21" s="137"/>
-      <c r="N21" s="137"/>
-      <c r="O21" s="137"/>
-      <c r="P21" s="137"/>
-      <c r="Q21" s="137"/>
-      <c r="R21" s="138"/>
+      <c r="B21" s="131"/>
+      <c r="C21" s="130"/>
+      <c r="D21" s="131"/>
+      <c r="E21" s="130"/>
+      <c r="F21" s="131"/>
+      <c r="G21" s="138"/>
+      <c r="H21" s="130"/>
+      <c r="I21" s="137"/>
+      <c r="J21" s="135"/>
+      <c r="K21" s="135"/>
+      <c r="L21" s="135"/>
+      <c r="M21" s="135"/>
+      <c r="N21" s="135"/>
+      <c r="O21" s="135"/>
+      <c r="P21" s="135"/>
+      <c r="Q21" s="135"/>
+      <c r="R21" s="136"/>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="6">
         <v>18</v>
       </c>
-      <c r="B22" s="133"/>
-      <c r="C22" s="132"/>
-      <c r="D22" s="133"/>
-      <c r="E22" s="132"/>
-      <c r="F22" s="133"/>
-      <c r="G22" s="140"/>
-      <c r="H22" s="132"/>
-      <c r="I22" s="139"/>
-      <c r="J22" s="137"/>
-      <c r="K22" s="137"/>
-      <c r="L22" s="137"/>
-      <c r="M22" s="137"/>
-      <c r="N22" s="137"/>
-      <c r="O22" s="137"/>
-      <c r="P22" s="137"/>
-      <c r="Q22" s="137"/>
-      <c r="R22" s="138"/>
+      <c r="B22" s="131"/>
+      <c r="C22" s="130"/>
+      <c r="D22" s="131"/>
+      <c r="E22" s="130"/>
+      <c r="F22" s="131"/>
+      <c r="G22" s="138"/>
+      <c r="H22" s="130"/>
+      <c r="I22" s="137"/>
+      <c r="J22" s="135"/>
+      <c r="K22" s="135"/>
+      <c r="L22" s="135"/>
+      <c r="M22" s="135"/>
+      <c r="N22" s="135"/>
+      <c r="O22" s="135"/>
+      <c r="P22" s="135"/>
+      <c r="Q22" s="135"/>
+      <c r="R22" s="136"/>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="5"/>
@@ -4245,22 +4280,22 @@
       </c>
       <c r="B1" s="86"/>
       <c r="C1" s="85" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
+        <v>12</v>
+      </c>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
+      <c r="K1" s="104"/>
       <c r="L1" s="86"/>
       <c r="M1" s="24" t="s">
         <v>2</v>
       </c>
       <c r="N1" s="22" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="O1" s="25" t="s">
         <v>3</v>
@@ -4273,21 +4308,21 @@
       <c r="A2" s="87"/>
       <c r="B2" s="88"/>
       <c r="C2" s="87"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="107"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="107"/>
-      <c r="I2" s="107"/>
-      <c r="J2" s="107"/>
-      <c r="K2" s="107"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="105"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="105"/>
+      <c r="J2" s="105"/>
+      <c r="K2" s="105"/>
       <c r="L2" s="88"/>
       <c r="M2" s="27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N2" s="28"/>
       <c r="O2" s="80" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P2" s="30"/>
     </row>
@@ -4311,28 +4346,28 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="139" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="141" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="142"/>
-      <c r="D4" s="142"/>
-      <c r="E4" s="142"/>
-      <c r="F4" s="142"/>
-      <c r="G4" s="143"/>
+      <c r="C4" s="140"/>
+      <c r="D4" s="140"/>
+      <c r="E4" s="140"/>
+      <c r="F4" s="140"/>
+      <c r="G4" s="141"/>
       <c r="H4" s="31"/>
       <c r="I4" s="79" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="139" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="141" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="142"/>
-      <c r="L4" s="142"/>
-      <c r="M4" s="142"/>
-      <c r="N4" s="142"/>
-      <c r="O4" s="143"/>
+      <c r="K4" s="140"/>
+      <c r="L4" s="140"/>
+      <c r="M4" s="140"/>
+      <c r="N4" s="140"/>
+      <c r="O4" s="141"/>
       <c r="P4" s="35"/>
     </row>
     <row r="5" spans="1:16">
@@ -4355,10 +4390,10 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
@@ -4367,10 +4402,10 @@
       <c r="G6" s="31"/>
       <c r="H6" s="7"/>
       <c r="I6" s="36" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="J6" s="31" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="K6" s="31"/>
       <c r="L6" s="31"/>
@@ -4381,10 +4416,10 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="77" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
@@ -4393,10 +4428,10 @@
       <c r="G7" s="31"/>
       <c r="H7" s="7"/>
       <c r="I7" s="77" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="J7" s="31" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="K7" s="31"/>
       <c r="L7" s="31"/>
@@ -4407,10 +4442,10 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="77" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C8" s="35"/>
       <c r="D8" s="35"/>
@@ -4419,10 +4454,10 @@
       <c r="G8" s="35"/>
       <c r="H8" s="7"/>
       <c r="I8" s="77" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J8" s="35" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K8" s="35"/>
       <c r="L8" s="35"/>
@@ -4433,10 +4468,10 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="77" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C9" s="31"/>
       <c r="D9" s="31"/>
@@ -4455,10 +4490,10 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="77" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C10" s="31"/>
       <c r="D10" s="31"/>
@@ -4467,7 +4502,7 @@
       <c r="G10" s="31"/>
       <c r="H10" s="7"/>
       <c r="I10" s="36" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="J10" s="31"/>
       <c r="K10" s="31"/>
@@ -4482,7 +4517,7 @@
         <v>1.5</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C11" s="31"/>
       <c r="D11" s="31"/>
@@ -4491,10 +4526,10 @@
       <c r="G11" s="31"/>
       <c r="H11" s="7"/>
       <c r="I11" s="78" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="J11" s="31" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="K11" s="31"/>
       <c r="L11" s="31"/>
@@ -4523,10 +4558,10 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="36" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C13" s="31"/>
       <c r="D13" s="31"/>
@@ -4535,7 +4570,7 @@
       <c r="G13" s="31"/>
       <c r="H13" s="7"/>
       <c r="I13" s="7" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J13" s="31"/>
       <c r="K13" s="31"/>
@@ -4547,10 +4582,10 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="78" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C14" s="31"/>
       <c r="D14" s="31"/>
@@ -4559,10 +4594,10 @@
       <c r="G14" s="31"/>
       <c r="H14" s="31"/>
       <c r="I14" s="78" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J14" s="31" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="K14" s="31"/>
       <c r="L14" s="31"/>
@@ -4591,10 +4626,10 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="36" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C16" s="31"/>
       <c r="D16" s="31"/>
@@ -4613,10 +4648,10 @@
     </row>
     <row r="17" spans="1:16" ht="26.5">
       <c r="A17" s="78" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C17" s="31"/>
       <c r="D17" s="31"/>
@@ -4635,10 +4670,10 @@
     </row>
     <row r="18" spans="1:16" ht="26.5">
       <c r="A18" s="78" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C18" s="35"/>
       <c r="D18" s="35"/>
@@ -4753,11 +4788,11 @@
       </c>
       <c r="B1" s="86"/>
       <c r="C1" s="89" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D1" s="90"/>
       <c r="E1" s="91" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F1" s="92"/>
       <c r="G1" s="92"/>
@@ -4769,7 +4804,7 @@
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -4791,13 +4826,13 @@
       <c r="J2" s="92"/>
       <c r="K2" s="93"/>
       <c r="L2" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="N2" s="29" t="s">
         <v>14</v>
-      </c>
-      <c r="M2" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="N2" s="29" t="s">
-        <v>15</v>
       </c>
       <c r="O2" s="73">
         <v>46266</v>
@@ -4823,7 +4858,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="35" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -4841,44 +4876,44 @@
     </row>
     <row r="5" spans="1:15" ht="18" customHeight="1">
       <c r="A5" s="8"/>
-      <c r="B5" s="145" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="145"/>
-      <c r="D5" s="145"/>
-      <c r="E5" s="145"/>
-      <c r="F5" s="145"/>
-      <c r="G5" s="145"/>
-      <c r="H5" s="145"/>
-      <c r="I5" s="145"/>
-      <c r="J5" s="145"/>
-      <c r="K5" s="145"/>
-      <c r="L5" s="145"/>
-      <c r="M5" s="145"/>
-      <c r="N5" s="145"/>
+      <c r="B5" s="143" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="143"/>
+      <c r="D5" s="143"/>
+      <c r="E5" s="143"/>
+      <c r="F5" s="143"/>
+      <c r="G5" s="143"/>
+      <c r="H5" s="143"/>
+      <c r="I5" s="143"/>
+      <c r="J5" s="143"/>
+      <c r="K5" s="143"/>
+      <c r="L5" s="143"/>
+      <c r="M5" s="143"/>
+      <c r="N5" s="143"/>
       <c r="O5" s="8"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="35"/>
-      <c r="B6" s="145"/>
-      <c r="C6" s="145"/>
-      <c r="D6" s="145"/>
-      <c r="E6" s="145"/>
-      <c r="F6" s="145"/>
-      <c r="G6" s="145"/>
-      <c r="H6" s="145"/>
-      <c r="I6" s="145"/>
-      <c r="J6" s="145"/>
-      <c r="K6" s="145"/>
-      <c r="L6" s="145"/>
-      <c r="M6" s="145"/>
-      <c r="N6" s="145"/>
+      <c r="B6" s="143"/>
+      <c r="C6" s="143"/>
+      <c r="D6" s="143"/>
+      <c r="E6" s="143"/>
+      <c r="F6" s="143"/>
+      <c r="G6" s="143"/>
+      <c r="H6" s="143"/>
+      <c r="I6" s="143"/>
+      <c r="J6" s="143"/>
+      <c r="K6" s="143"/>
+      <c r="L6" s="143"/>
+      <c r="M6" s="143"/>
+      <c r="N6" s="143"/>
       <c r="O6" s="35"/>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="35"/>
       <c r="B7" s="35" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C7" s="35"/>
       <c r="D7" s="35"/>
@@ -4914,7 +4949,7 @@
     <row r="9" spans="1:15">
       <c r="A9" s="35"/>
       <c r="B9" s="35" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -4933,7 +4968,7 @@
     <row r="10" spans="1:15">
       <c r="A10" s="35"/>
       <c r="B10" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -4969,7 +5004,7 @@
     <row r="12" spans="1:15">
       <c r="A12" s="35"/>
       <c r="B12" s="35" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C12" s="35"/>
       <c r="D12" s="35"/>
@@ -4987,115 +5022,115 @@
     </row>
     <row r="13" spans="1:15" ht="18" customHeight="1">
       <c r="A13" s="35"/>
-      <c r="B13" s="144" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="144"/>
-      <c r="D13" s="144"/>
-      <c r="E13" s="144"/>
-      <c r="F13" s="144"/>
-      <c r="G13" s="144"/>
-      <c r="H13" s="144"/>
-      <c r="I13" s="144"/>
-      <c r="J13" s="144"/>
-      <c r="K13" s="144"/>
-      <c r="L13" s="144"/>
-      <c r="M13" s="144"/>
-      <c r="N13" s="144"/>
-      <c r="O13" s="144"/>
+      <c r="B13" s="142" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="142"/>
+      <c r="D13" s="142"/>
+      <c r="E13" s="142"/>
+      <c r="F13" s="142"/>
+      <c r="G13" s="142"/>
+      <c r="H13" s="142"/>
+      <c r="I13" s="142"/>
+      <c r="J13" s="142"/>
+      <c r="K13" s="142"/>
+      <c r="L13" s="142"/>
+      <c r="M13" s="142"/>
+      <c r="N13" s="142"/>
+      <c r="O13" s="142"/>
     </row>
     <row r="14" spans="1:15" ht="18" customHeight="1">
       <c r="A14" s="35"/>
-      <c r="B14" s="144" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" s="144"/>
-      <c r="D14" s="144"/>
-      <c r="E14" s="144"/>
-      <c r="F14" s="144"/>
-      <c r="G14" s="144"/>
-      <c r="H14" s="144"/>
-      <c r="I14" s="144"/>
-      <c r="J14" s="144"/>
-      <c r="K14" s="144"/>
-      <c r="L14" s="144"/>
-      <c r="M14" s="144"/>
-      <c r="N14" s="144"/>
-      <c r="O14" s="144"/>
+      <c r="B14" s="142" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="142"/>
+      <c r="D14" s="142"/>
+      <c r="E14" s="142"/>
+      <c r="F14" s="142"/>
+      <c r="G14" s="142"/>
+      <c r="H14" s="142"/>
+      <c r="I14" s="142"/>
+      <c r="J14" s="142"/>
+      <c r="K14" s="142"/>
+      <c r="L14" s="142"/>
+      <c r="M14" s="142"/>
+      <c r="N14" s="142"/>
+      <c r="O14" s="142"/>
     </row>
     <row r="15" spans="1:15" ht="18" customHeight="1">
       <c r="A15" s="35"/>
-      <c r="B15" s="144" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" s="144"/>
-      <c r="D15" s="144"/>
-      <c r="E15" s="144"/>
-      <c r="F15" s="144"/>
-      <c r="G15" s="144"/>
-      <c r="H15" s="144"/>
-      <c r="I15" s="144"/>
-      <c r="J15" s="144"/>
-      <c r="K15" s="144"/>
-      <c r="L15" s="144"/>
-      <c r="M15" s="144"/>
-      <c r="N15" s="144"/>
-      <c r="O15" s="144"/>
+      <c r="B15" s="142" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="142"/>
+      <c r="D15" s="142"/>
+      <c r="E15" s="142"/>
+      <c r="F15" s="142"/>
+      <c r="G15" s="142"/>
+      <c r="H15" s="142"/>
+      <c r="I15" s="142"/>
+      <c r="J15" s="142"/>
+      <c r="K15" s="142"/>
+      <c r="L15" s="142"/>
+      <c r="M15" s="142"/>
+      <c r="N15" s="142"/>
+      <c r="O15" s="142"/>
     </row>
     <row r="16" spans="1:15" ht="18" customHeight="1">
       <c r="A16" s="35"/>
-      <c r="B16" s="144" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" s="144"/>
-      <c r="D16" s="144"/>
-      <c r="E16" s="144"/>
-      <c r="F16" s="144"/>
-      <c r="G16" s="144"/>
-      <c r="H16" s="144"/>
-      <c r="I16" s="144"/>
-      <c r="J16" s="144"/>
-      <c r="K16" s="144"/>
-      <c r="L16" s="144"/>
-      <c r="M16" s="144"/>
-      <c r="N16" s="144"/>
-      <c r="O16" s="144"/>
+      <c r="B16" s="142" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="142"/>
+      <c r="D16" s="142"/>
+      <c r="E16" s="142"/>
+      <c r="F16" s="142"/>
+      <c r="G16" s="142"/>
+      <c r="H16" s="142"/>
+      <c r="I16" s="142"/>
+      <c r="J16" s="142"/>
+      <c r="K16" s="142"/>
+      <c r="L16" s="142"/>
+      <c r="M16" s="142"/>
+      <c r="N16" s="142"/>
+      <c r="O16" s="142"/>
     </row>
     <row r="17" spans="1:15" ht="18" customHeight="1">
       <c r="A17" s="35"/>
-      <c r="B17" s="144" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" s="144"/>
-      <c r="D17" s="144"/>
-      <c r="E17" s="144"/>
-      <c r="F17" s="144"/>
-      <c r="G17" s="144"/>
-      <c r="H17" s="144"/>
-      <c r="I17" s="144"/>
-      <c r="J17" s="144"/>
-      <c r="K17" s="144"/>
-      <c r="L17" s="144"/>
-      <c r="M17" s="144"/>
-      <c r="N17" s="144"/>
-      <c r="O17" s="144"/>
+      <c r="B17" s="142" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="142"/>
+      <c r="D17" s="142"/>
+      <c r="E17" s="142"/>
+      <c r="F17" s="142"/>
+      <c r="G17" s="142"/>
+      <c r="H17" s="142"/>
+      <c r="I17" s="142"/>
+      <c r="J17" s="142"/>
+      <c r="K17" s="142"/>
+      <c r="L17" s="142"/>
+      <c r="M17" s="142"/>
+      <c r="N17" s="142"/>
+      <c r="O17" s="142"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="35"/>
-      <c r="B18" s="144"/>
-      <c r="C18" s="144"/>
-      <c r="D18" s="144"/>
-      <c r="E18" s="144"/>
-      <c r="F18" s="144"/>
-      <c r="G18" s="144"/>
-      <c r="H18" s="144"/>
-      <c r="I18" s="144"/>
-      <c r="J18" s="144"/>
-      <c r="K18" s="144"/>
-      <c r="L18" s="144"/>
-      <c r="M18" s="144"/>
-      <c r="N18" s="144"/>
-      <c r="O18" s="144"/>
+      <c r="B18" s="142"/>
+      <c r="C18" s="142"/>
+      <c r="D18" s="142"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="142"/>
+      <c r="G18" s="142"/>
+      <c r="H18" s="142"/>
+      <c r="I18" s="142"/>
+      <c r="J18" s="142"/>
+      <c r="K18" s="142"/>
+      <c r="L18" s="142"/>
+      <c r="M18" s="142"/>
+      <c r="N18" s="142"/>
+      <c r="O18" s="142"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="35"/>
@@ -5117,7 +5152,7 @@
     <row r="20" spans="1:15">
       <c r="A20" s="35"/>
       <c r="B20" s="42" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C20" s="43"/>
       <c r="D20" s="43"/>
@@ -5136,7 +5171,7 @@
     <row r="21" spans="1:15">
       <c r="A21" s="35"/>
       <c r="B21" s="42" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C21" s="43"/>
       <c r="D21" s="43"/>
@@ -5189,7 +5224,7 @@
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
@@ -5208,7 +5243,7 @@
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="45" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C25" s="46"/>
       <c r="D25" s="46"/>
@@ -5227,7 +5262,7 @@
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="45" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C26" s="46"/>
       <c r="D26" s="46"/>
@@ -5246,7 +5281,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="45" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C27" s="46"/>
       <c r="D27" s="46"/>
@@ -5281,7 +5316,7 @@
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
       <c r="B29" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
@@ -5300,7 +5335,7 @@
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
       <c r="B30" s="47" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -5319,7 +5354,7 @@
     <row r="31" spans="1:15">
       <c r="A31" s="8"/>
       <c r="B31" s="47" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -5338,7 +5373,7 @@
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="47" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -5405,11 +5440,11 @@
       </c>
       <c r="B1" s="86"/>
       <c r="C1" s="89" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D1" s="90"/>
       <c r="E1" s="91" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F1" s="92"/>
       <c r="G1" s="92"/>
@@ -5421,7 +5456,7 @@
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -5443,13 +5478,13 @@
       <c r="J2" s="92"/>
       <c r="K2" s="93"/>
       <c r="L2" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="N2" s="29" t="s">
         <v>14</v>
-      </c>
-      <c r="M2" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="N2" s="29" t="s">
-        <v>15</v>
       </c>
       <c r="O2" s="73">
         <v>46266</v>
@@ -5475,7 +5510,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="35" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -5510,12 +5545,12 @@
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1">
       <c r="A6" s="35"/>
-      <c r="B6" s="94" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="95"/>
-      <c r="D6" s="82" t="s">
-        <v>161</v>
+      <c r="B6" s="146" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="147"/>
+      <c r="D6" s="83" t="s">
+        <v>158</v>
       </c>
       <c r="E6" s="50"/>
       <c r="F6" s="50"/>
@@ -5531,12 +5566,12 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="35"/>
-      <c r="B7" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="84"/>
+      <c r="B7" s="144" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="145"/>
       <c r="D7" s="53" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E7" s="54"/>
       <c r="F7" s="54"/>
@@ -5552,12 +5587,12 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="35"/>
-      <c r="B8" s="83" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="84"/>
+      <c r="B8" s="144" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="145"/>
       <c r="D8" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
@@ -6026,11 +6061,11 @@
       </c>
       <c r="B1" s="86"/>
       <c r="C1" s="89" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D1" s="90"/>
       <c r="E1" s="71" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F1" s="71"/>
       <c r="G1" s="71"/>
@@ -6041,15 +6076,15 @@
         <v>2</v>
       </c>
       <c r="L1" s="26" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="148">
+      <c r="N1" s="150">
         <v>46260</v>
       </c>
-      <c r="O1" s="148"/>
+      <c r="O1" s="150"/>
     </row>
     <row r="2" spans="1:15" ht="20">
       <c r="A2" s="87"/>
@@ -6063,18 +6098,18 @@
       <c r="I2" s="92"/>
       <c r="J2" s="93"/>
       <c r="K2" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="M2" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="M2" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2" s="159">
+      <c r="N2" s="151">
         <v>46281</v>
       </c>
-      <c r="O2" s="159"/>
+      <c r="O2" s="151"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="40"/>
@@ -6096,7 +6131,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="35" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -6132,12 +6167,12 @@
     <row r="6" spans="1:15" ht="18" customHeight="1">
       <c r="A6" s="35"/>
       <c r="B6" s="49" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C6" s="50"/>
       <c r="D6" s="50"/>
       <c r="E6" s="49" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F6" s="50"/>
       <c r="G6" s="50"/>
@@ -6145,7 +6180,7 @@
       <c r="I6" s="51"/>
       <c r="J6" s="66"/>
       <c r="K6" s="49" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L6" s="55"/>
       <c r="M6" s="70"/>
@@ -6155,12 +6190,12 @@
     <row r="7" spans="1:15">
       <c r="A7" s="35"/>
       <c r="B7" s="53" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C7" s="54"/>
       <c r="D7" s="54"/>
       <c r="E7" s="68" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="54"/>
@@ -6168,7 +6203,7 @@
       <c r="I7" s="54"/>
       <c r="J7" s="55"/>
       <c r="K7" s="69" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L7" s="55"/>
       <c r="M7" s="31"/>
@@ -6178,12 +6213,12 @@
     <row r="8" spans="1:15">
       <c r="A8" s="35"/>
       <c r="B8" s="53" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C8" s="54"/>
       <c r="D8" s="54"/>
       <c r="E8" s="68" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F8" s="23"/>
       <c r="G8" s="54"/>
@@ -6191,7 +6226,7 @@
       <c r="I8" s="54"/>
       <c r="J8" s="55"/>
       <c r="K8" s="69" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L8" s="55"/>
       <c r="M8" s="31"/>
@@ -6201,12 +6236,12 @@
     <row r="9" spans="1:15">
       <c r="A9" s="35"/>
       <c r="B9" s="53" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C9" s="54"/>
       <c r="D9" s="54"/>
       <c r="E9" s="68" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="54"/>
@@ -6214,7 +6249,7 @@
       <c r="I9" s="54"/>
       <c r="J9" s="55"/>
       <c r="K9" s="69" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L9" s="55"/>
       <c r="M9" s="31"/>
@@ -6224,22 +6259,22 @@
     <row r="10" spans="1:15">
       <c r="A10" s="35"/>
       <c r="B10" s="17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
       <c r="E10" s="68" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F10" s="23"/>
       <c r="G10" s="54"/>
       <c r="H10" s="54"/>
       <c r="I10" s="54"/>
       <c r="J10" s="55"/>
-      <c r="K10" s="146" t="s">
-        <v>92</v>
-      </c>
-      <c r="L10" s="147"/>
+      <c r="K10" s="148" t="s">
+        <v>90</v>
+      </c>
+      <c r="L10" s="149"/>
       <c r="M10" s="31"/>
       <c r="N10" s="35"/>
       <c r="O10" s="7"/>
@@ -6264,7 +6299,7 @@
     <row r="12" spans="1:15">
       <c r="A12" s="35"/>
       <c r="B12" s="35" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C12" s="35"/>
       <c r="D12" s="35"/>
@@ -6272,7 +6307,7 @@
     <row r="13" spans="1:15">
       <c r="A13" s="35"/>
       <c r="B13" s="42" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C13" s="42"/>
       <c r="D13" s="42"/>
@@ -6291,7 +6326,7 @@
     <row r="14" spans="1:15">
       <c r="A14" s="35"/>
       <c r="B14" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C14" s="57"/>
       <c r="D14" s="57"/>
@@ -6310,7 +6345,7 @@
     <row r="15" spans="1:15">
       <c r="A15" s="35"/>
       <c r="B15" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C15" s="57"/>
       <c r="D15" s="57"/>
@@ -6346,7 +6381,7 @@
     <row r="17" spans="1:15">
       <c r="A17" s="35"/>
       <c r="B17" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C17" s="57"/>
       <c r="D17" s="57"/>
@@ -6365,7 +6400,7 @@
     <row r="18" spans="1:15">
       <c r="A18" s="35"/>
       <c r="B18" s="57" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C18" s="42"/>
       <c r="D18" s="42"/>
@@ -6401,7 +6436,7 @@
     <row r="20" spans="1:15">
       <c r="A20" s="35"/>
       <c r="B20" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C20" s="42"/>
       <c r="D20" s="42"/>
@@ -6420,7 +6455,7 @@
     <row r="21" spans="1:15" ht="18" customHeight="1">
       <c r="A21" s="44"/>
       <c r="B21" s="57" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C21" s="44"/>
       <c r="D21" s="44"/>
@@ -6439,7 +6474,7 @@
     <row r="22" spans="1:15" ht="18" customHeight="1">
       <c r="A22" s="8"/>
       <c r="B22" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
@@ -6475,7 +6510,7 @@
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="42" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C24" s="46"/>
       <c r="D24" s="46"/>
@@ -6494,7 +6529,7 @@
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="57" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C25" s="46"/>
       <c r="D25" s="46"/>
@@ -6646,8 +6681,11 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D678CDCE-2C5A-4AFB-B9CB-39BA46C32C81}">
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="15" max="15" width="9.25" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
       <c r="A1" s="85" t="s">
@@ -6655,11 +6693,11 @@
       </c>
       <c r="B1" s="86"/>
       <c r="C1" s="89" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D1" s="90"/>
       <c r="E1" s="91" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F1" s="92"/>
       <c r="G1" s="92"/>
@@ -6671,13 +6709,13 @@
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>23</v>
+        <v>181</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
       <c r="O1" s="39">
-        <v>46001</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
@@ -6693,11 +6731,11 @@
       <c r="J2" s="92"/>
       <c r="K2" s="93"/>
       <c r="L2" s="25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M2" s="58"/>
       <c r="N2" s="25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O2" s="26"/>
     </row>
@@ -6721,7 +6759,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="35" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -6739,7 +6777,9 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
-      <c r="B5" s="31"/>
+      <c r="B5" s="31" t="s">
+        <v>178</v>
+      </c>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
       <c r="E5" s="31"/>
@@ -6774,7 +6814,7 @@
     <row r="7" spans="1:15">
       <c r="A7" s="35"/>
       <c r="B7" s="35" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C7" s="35"/>
       <c r="D7" s="35"/>
@@ -6792,7 +6832,9 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="35"/>
-      <c r="B8" s="35"/>
+      <c r="B8" s="35" t="s">
+        <v>179</v>
+      </c>
       <c r="C8" s="35"/>
       <c r="D8" s="35"/>
       <c r="E8" s="35"/>
@@ -6809,7 +6851,7 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="35"/>
-      <c r="B9" s="35"/>
+      <c r="B9" s="7"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -6826,7 +6868,9 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="35"/>
-      <c r="B10" s="7"/>
+      <c r="B10" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -6844,42 +6888,42 @@
     <row r="11" spans="1:15">
       <c r="A11" s="35"/>
       <c r="B11" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
+        <v>180</v>
+      </c>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="35"/>
       <c r="O11" s="35"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="35"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="35"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="35"/>
-      <c r="N12" s="35"/>
-      <c r="O12" s="35"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="42"/>
+      <c r="O12" s="42"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="35"/>
-      <c r="B13" s="35"/>
+      <c r="B13" s="42"/>
       <c r="C13" s="42"/>
       <c r="D13" s="42"/>
       <c r="E13" s="42"/>
@@ -6964,37 +7008,37 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="35"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="42"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="42"/>
-      <c r="M18" s="42"/>
-      <c r="N18" s="42"/>
-      <c r="O18" s="42"/>
+      <c r="B18" s="59"/>
+      <c r="C18" s="59"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="59"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="59"/>
+      <c r="J18" s="59"/>
+      <c r="K18" s="59"/>
+      <c r="L18" s="59"/>
+      <c r="M18" s="59"/>
+      <c r="N18" s="59"/>
+      <c r="O18" s="59"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="35"/>
-      <c r="B19" s="59"/>
-      <c r="C19" s="59"/>
-      <c r="D19" s="59"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="59"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="59"/>
-      <c r="J19" s="59"/>
-      <c r="K19" s="59"/>
-      <c r="L19" s="59"/>
-      <c r="M19" s="59"/>
-      <c r="N19" s="59"/>
-      <c r="O19" s="59"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="42"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="42"/>
+      <c r="O19" s="42"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="35"/>
@@ -7030,56 +7074,56 @@
       <c r="N21" s="42"/>
       <c r="O21" s="42"/>
     </row>
-    <row r="22" spans="1:15">
-      <c r="A22" s="35"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="42"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="42"/>
-      <c r="J22" s="42"/>
-      <c r="K22" s="42"/>
-      <c r="L22" s="42"/>
-      <c r="M22" s="42"/>
-      <c r="N22" s="42"/>
-      <c r="O22" s="42"/>
-    </row>
-    <row r="23" spans="1:15" ht="26.5">
-      <c r="A23" s="44"/>
-      <c r="B23" s="44"/>
-      <c r="C23" s="44"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="44"/>
-      <c r="K23" s="44"/>
-      <c r="L23" s="44"/>
-      <c r="M23" s="44"/>
-      <c r="N23" s="44"/>
-      <c r="O23" s="44"/>
+    <row r="22" spans="1:15" ht="26.5">
+      <c r="A22" s="44"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="44"/>
+      <c r="K22" s="44"/>
+      <c r="L22" s="44"/>
+      <c r="M22" s="44"/>
+      <c r="N22" s="44"/>
+      <c r="O22" s="44"/>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="57"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="57"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="57"/>
+      <c r="H24" s="57"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="57"/>
+      <c r="K24" s="57"/>
+      <c r="L24" s="57"/>
+      <c r="M24" s="57"/>
+      <c r="N24" s="57"/>
+      <c r="O24" s="57"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
@@ -7151,20 +7195,20 @@
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
-      <c r="B29" s="57"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="57"/>
-      <c r="J29" s="57"/>
-      <c r="K29" s="57"/>
-      <c r="L29" s="57"/>
-      <c r="M29" s="57"/>
-      <c r="N29" s="57"/>
-      <c r="O29" s="57"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
@@ -7233,23 +7277,6 @@
       <c r="M33" s="8"/>
       <c r="N33" s="8"/>
       <c r="O33" s="8"/>
-    </row>
-    <row r="34" spans="1:15">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="8"/>
-      <c r="N34" s="8"/>
-      <c r="O34" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -7278,11 +7305,11 @@
       </c>
       <c r="B1" s="86"/>
       <c r="C1" s="89" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D1" s="90"/>
       <c r="E1" s="91" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F1" s="92"/>
       <c r="G1" s="92"/>
@@ -7294,7 +7321,7 @@
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -7316,13 +7343,13 @@
       <c r="J2" s="92"/>
       <c r="K2" s="93"/>
       <c r="L2" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="N2" s="25" t="s">
         <v>14</v>
-      </c>
-      <c r="M2" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="N2" s="25" t="s">
-        <v>15</v>
       </c>
       <c r="O2" s="39">
         <v>46281</v>
@@ -7365,23 +7392,23 @@
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
       <c r="B5" s="60" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C5" s="61"/>
       <c r="D5" s="60" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E5" s="61"/>
       <c r="F5" s="60" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G5" s="61"/>
       <c r="H5" s="60" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I5" s="61"/>
       <c r="J5" s="60" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K5" s="54"/>
       <c r="L5" s="62"/>
@@ -7392,11 +7419,11 @@
     <row r="6" spans="1:15">
       <c r="A6" s="35"/>
       <c r="B6" s="53" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C6" s="56"/>
       <c r="D6" s="53" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E6" s="56"/>
       <c r="F6" s="53">
@@ -7404,11 +7431,11 @@
       </c>
       <c r="G6" s="56"/>
       <c r="H6" s="53" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I6" s="56"/>
       <c r="J6" s="53" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K6" s="54"/>
       <c r="L6" s="62"/>
@@ -7419,11 +7446,11 @@
     <row r="7" spans="1:15">
       <c r="A7" s="35"/>
       <c r="B7" s="53" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C7" s="56"/>
       <c r="D7" s="53" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E7" s="56"/>
       <c r="F7" s="53">
@@ -7431,11 +7458,11 @@
       </c>
       <c r="G7" s="56"/>
       <c r="H7" s="53" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I7" s="56"/>
       <c r="J7" s="53" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="54"/>
@@ -7446,11 +7473,11 @@
     <row r="8" spans="1:15">
       <c r="A8" s="35"/>
       <c r="B8" s="53" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C8" s="56"/>
       <c r="D8" s="53" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E8" s="56"/>
       <c r="F8" s="53">
@@ -7458,11 +7485,11 @@
       </c>
       <c r="G8" s="56"/>
       <c r="H8" s="53" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I8" s="56"/>
       <c r="J8" s="53" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K8" s="23"/>
       <c r="L8" s="54"/>
@@ -7473,38 +7500,38 @@
     <row r="9" spans="1:15" ht="36" customHeight="1">
       <c r="A9" s="35"/>
       <c r="B9" s="53" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C9" s="56"/>
       <c r="D9" s="17" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E9" s="56"/>
       <c r="F9" s="17" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G9" s="56"/>
       <c r="H9" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I9" s="56"/>
-      <c r="J9" s="149" t="s">
-        <v>111</v>
-      </c>
-      <c r="K9" s="150"/>
-      <c r="L9" s="150"/>
-      <c r="M9" s="151"/>
+      <c r="J9" s="155" t="s">
+        <v>109</v>
+      </c>
+      <c r="K9" s="156"/>
+      <c r="L9" s="156"/>
+      <c r="M9" s="157"/>
       <c r="N9" s="8"/>
       <c r="O9" s="35"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="35"/>
       <c r="B10" s="68" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C10" s="56"/>
       <c r="D10" s="17" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E10" s="56"/>
       <c r="F10" s="17">
@@ -7512,10 +7539,12 @@
       </c>
       <c r="G10" s="56"/>
       <c r="H10" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I10" s="23"/>
-      <c r="J10" s="17"/>
+      <c r="J10" s="82" t="s">
+        <v>177</v>
+      </c>
       <c r="K10" s="23"/>
       <c r="L10" s="23"/>
       <c r="M10" s="56"/>
@@ -7525,11 +7554,11 @@
     <row r="11" spans="1:15">
       <c r="A11" s="35"/>
       <c r="B11" s="17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C11" s="56"/>
       <c r="D11" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E11" s="56"/>
       <c r="F11" s="17">
@@ -7537,11 +7566,11 @@
       </c>
       <c r="G11" s="56"/>
       <c r="H11" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I11" s="56"/>
       <c r="J11" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="K11" s="23"/>
       <c r="L11" s="23"/>
@@ -7552,11 +7581,11 @@
     <row r="12" spans="1:15">
       <c r="A12" s="35"/>
       <c r="B12" s="17" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C12" s="55"/>
       <c r="D12" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E12" s="56"/>
       <c r="F12" s="17">
@@ -7564,11 +7593,11 @@
       </c>
       <c r="G12" s="56"/>
       <c r="H12" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I12" s="56"/>
       <c r="J12" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="23"/>
@@ -7579,11 +7608,11 @@
     <row r="13" spans="1:15">
       <c r="A13" s="35"/>
       <c r="B13" s="53" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C13" s="74"/>
       <c r="D13" s="17" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E13" s="56"/>
       <c r="F13" s="17">
@@ -7591,7 +7620,7 @@
       </c>
       <c r="G13" s="56"/>
       <c r="H13" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I13" s="56"/>
       <c r="J13" s="17"/>
@@ -7604,11 +7633,11 @@
     <row r="14" spans="1:15" ht="54" customHeight="1">
       <c r="A14" s="35"/>
       <c r="B14" s="75" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C14" s="74"/>
       <c r="D14" s="17" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E14" s="56"/>
       <c r="F14" s="17">
@@ -7616,11 +7645,11 @@
       </c>
       <c r="G14" s="56"/>
       <c r="H14" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I14" s="56"/>
       <c r="J14" s="152" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K14" s="153"/>
       <c r="L14" s="153"/>
@@ -7631,11 +7660,11 @@
     <row r="15" spans="1:15" ht="36" customHeight="1">
       <c r="A15" s="35"/>
       <c r="B15" s="75" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C15" s="74"/>
       <c r="D15" s="17" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E15" s="56"/>
       <c r="F15" s="17">
@@ -7643,38 +7672,38 @@
       </c>
       <c r="G15" s="56"/>
       <c r="H15" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I15" s="56"/>
-      <c r="J15" s="155" t="s">
-        <v>114</v>
-      </c>
-      <c r="K15" s="156"/>
-      <c r="L15" s="156"/>
-      <c r="M15" s="157"/>
+      <c r="J15" s="158" t="s">
+        <v>112</v>
+      </c>
+      <c r="K15" s="159"/>
+      <c r="L15" s="159"/>
+      <c r="M15" s="160"/>
       <c r="N15" s="42"/>
       <c r="O15" s="42"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="35"/>
       <c r="B16" s="75" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C16" s="74"/>
       <c r="D16" s="75" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E16" s="74"/>
       <c r="F16" s="53" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G16" s="74"/>
       <c r="H16" s="75" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I16" s="74"/>
       <c r="J16" s="17" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="K16" s="23"/>
       <c r="L16" s="23"/>
@@ -7685,19 +7714,19 @@
     <row r="17" spans="1:15">
       <c r="A17" s="35"/>
       <c r="B17" s="75" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C17" s="74"/>
       <c r="D17" s="75" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E17" s="74"/>
       <c r="F17" s="53" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G17" s="74"/>
       <c r="H17" s="75" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I17" s="74"/>
       <c r="J17" s="17"/>
@@ -7710,11 +7739,11 @@
     <row r="18" spans="1:15" ht="36" customHeight="1">
       <c r="A18" s="35"/>
       <c r="B18" s="75" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C18" s="74"/>
       <c r="D18" s="75" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E18" s="74"/>
       <c r="F18" s="53">
@@ -7722,11 +7751,11 @@
       </c>
       <c r="G18" s="74"/>
       <c r="H18" s="75" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I18" s="74"/>
       <c r="J18" s="152" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="K18" s="153"/>
       <c r="L18" s="153"/>
@@ -7737,54 +7766,54 @@
     <row r="19" spans="1:15" ht="36" customHeight="1">
       <c r="A19" s="35"/>
       <c r="B19" s="75" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C19" s="74"/>
       <c r="D19" s="75" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E19" s="74"/>
       <c r="F19" s="53" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G19" s="74"/>
       <c r="H19" s="75" t="s">
+        <v>171</v>
+      </c>
+      <c r="I19" s="74"/>
+      <c r="J19" s="155" t="s">
         <v>174</v>
       </c>
-      <c r="I19" s="74"/>
-      <c r="J19" s="149" t="s">
-        <v>177</v>
-      </c>
-      <c r="K19" s="150"/>
-      <c r="L19" s="150"/>
-      <c r="M19" s="151"/>
-      <c r="N19" s="158"/>
+      <c r="K19" s="156"/>
+      <c r="L19" s="156"/>
+      <c r="M19" s="157"/>
+      <c r="N19" s="84"/>
       <c r="O19" s="42"/>
     </row>
     <row r="20" spans="1:15" ht="36" customHeight="1">
       <c r="A20" s="35"/>
       <c r="B20" s="75" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C20" s="74"/>
       <c r="D20" s="75" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E20" s="74"/>
       <c r="F20" s="53" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G20" s="74"/>
       <c r="H20" s="75" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I20" s="74"/>
-      <c r="J20" s="149" t="s">
-        <v>179</v>
-      </c>
-      <c r="K20" s="150"/>
-      <c r="L20" s="150"/>
-      <c r="M20" s="151"/>
+      <c r="J20" s="155" t="s">
+        <v>176</v>
+      </c>
+      <c r="K20" s="156"/>
+      <c r="L20" s="156"/>
+      <c r="M20" s="157"/>
       <c r="N20" s="42"/>
       <c r="O20" s="42"/>
     </row>
@@ -8115,20 +8144,20 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B52A5B-90BF-4339-BD21-5A13EC799265}">
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:16" ht="20">
+    <row r="1" spans="1:15" ht="20">
       <c r="A1" s="85" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="86"/>
       <c r="C1" s="89" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D1" s="90"/>
       <c r="E1" s="91" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F1" s="92"/>
       <c r="G1" s="92"/>
@@ -8140,7 +8169,7 @@
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -8149,7 +8178,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="20">
+    <row r="2" spans="1:15" ht="20">
       <c r="A2" s="87"/>
       <c r="B2" s="88"/>
       <c r="C2" s="89"/>
@@ -8162,15 +8191,15 @@
       <c r="J2" s="92"/>
       <c r="K2" s="93"/>
       <c r="L2" s="25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M2" s="58"/>
       <c r="N2" s="25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O2" s="26"/>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:15">
       <c r="A3" s="40"/>
       <c r="B3" s="40"/>
       <c r="C3" s="40"/>
@@ -8187,7 +8216,7 @@
       <c r="N3" s="40"/>
       <c r="O3" s="35"/>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="35"/>
       <c r="C4" s="8"/>
@@ -8204,85 +8233,82 @@
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:15">
       <c r="A5" s="8"/>
       <c r="B5" s="64" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="60" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D5" s="51"/>
       <c r="E5" s="65"/>
       <c r="F5" s="51"/>
       <c r="G5" s="61"/>
       <c r="H5" s="60" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I5" s="65"/>
       <c r="J5" s="51"/>
       <c r="K5" s="51"/>
       <c r="L5" s="66"/>
       <c r="M5" s="60" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N5" s="62"/>
       <c r="O5" s="56"/>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:15">
       <c r="A6" s="35"/>
       <c r="B6" s="67">
         <v>1</v>
       </c>
       <c r="C6" s="53" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D6" s="51"/>
       <c r="E6" s="23"/>
       <c r="F6" s="51"/>
       <c r="G6" s="56"/>
       <c r="H6" s="53" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I6" s="23"/>
       <c r="J6" s="51"/>
       <c r="K6" s="51"/>
       <c r="L6" s="66"/>
       <c r="M6" s="17" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="N6" s="62"/>
       <c r="O6" s="55"/>
-      <c r="P6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="35"/>
       <c r="B7" s="67">
         <v>2</v>
       </c>
       <c r="C7" s="53" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D7" s="51"/>
       <c r="E7" s="23"/>
       <c r="F7" s="51"/>
       <c r="G7" s="56"/>
       <c r="H7" s="53" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="51"/>
       <c r="K7" s="51"/>
       <c r="L7" s="66"/>
       <c r="M7" s="76" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N7" s="54"/>
       <c r="O7" s="55"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:15">
       <c r="A8" s="35"/>
       <c r="B8" s="67"/>
       <c r="C8" s="53"/>
@@ -8299,7 +8325,7 @@
       <c r="N8" s="54"/>
       <c r="O8" s="55"/>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:15">
       <c r="A9" s="35"/>
       <c r="B9" s="67"/>
       <c r="C9" s="17"/>
@@ -8316,7 +8342,7 @@
       <c r="N9" s="23"/>
       <c r="O9" s="55"/>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:15">
       <c r="A10" s="35"/>
       <c r="B10" s="7"/>
       <c r="C10" s="8"/>
@@ -8333,7 +8359,7 @@
       <c r="N10" s="8"/>
       <c r="O10" s="35"/>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:15">
       <c r="A11" s="35"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -8350,7 +8376,7 @@
       <c r="N11" s="8"/>
       <c r="O11" s="35"/>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:15">
       <c r="A12" s="35"/>
       <c r="B12" s="8"/>
       <c r="C12" s="35"/>
@@ -8367,7 +8393,7 @@
       <c r="N12" s="35"/>
       <c r="O12" s="35"/>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:15">
       <c r="A13" s="35"/>
       <c r="B13" s="35"/>
       <c r="C13" s="42"/>
@@ -8384,7 +8410,7 @@
       <c r="N13" s="42"/>
       <c r="O13" s="42"/>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:15">
       <c r="A14" s="35"/>
       <c r="B14" s="42"/>
       <c r="C14" s="42"/>
@@ -8401,7 +8427,7 @@
       <c r="N14" s="42"/>
       <c r="O14" s="42"/>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:15">
       <c r="A15" s="35"/>
       <c r="B15" s="42"/>
       <c r="C15" s="42"/>
@@ -8418,7 +8444,7 @@
       <c r="N15" s="42"/>
       <c r="O15" s="42"/>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:15">
       <c r="A16" s="35"/>
       <c r="B16" s="42"/>
       <c r="C16" s="42"/>

--- a/要件定義書（採用管理システム）.xlsx
+++ b/要件定義書（採用管理システム）.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\my_application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3711475-305E-4500-9B52-EAF73A4D6AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B68A01AA-ADCA-40F4-A3F5-004BB69F59C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="5" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -806,52 +806,6 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>・応募者情報を検索→表示（氏名・カナ・性別・メールアドレス・電話番号・面接予定日・選考状況・担当者・合否）</t>
-    <rPh sb="1" eb="4">
-      <t>オウボシャ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ケンサク</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>シメイ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>セイベツ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>デンワ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>バンゴウ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>メンセツ</t>
-    </rPh>
-    <rPh sb="37" eb="40">
-      <t>ヨテイビ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>センコウ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="46" eb="49">
-      <t>タントウシャ</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>ゴウヒ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>・更新ボタンより変更・登録が可能</t>
     <rPh sb="1" eb="3">
       <t>コウシン</t>
@@ -1771,6 +1725,46 @@
     </rPh>
     <rPh sb="6" eb="8">
       <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・応募者情報を検索→表示（氏名・カナ・性別・メールアドレス・面接予定日・選考状況・担当者・合否）</t>
+    <rPh sb="1" eb="4">
+      <t>オウボシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>セイベツ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>メンセツ</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>ヨテイビ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>センコウ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="41" eb="44">
+      <t>タントウシャ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ゴウヒ</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -2541,18 +2535,165 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2567,153 +2708,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3177,44 +3171,44 @@
       <c r="P5" s="8"/>
     </row>
     <row r="6" spans="1:16" ht="39" customHeight="1">
-      <c r="A6" s="94"/>
-      <c r="B6" s="95"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="97" t="s">
+      <c r="A6" s="92"/>
+      <c r="B6" s="93"/>
+      <c r="C6" s="91"/>
+      <c r="D6" s="94" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="97"/>
-      <c r="F6" s="97"/>
-      <c r="G6" s="97"/>
-      <c r="H6" s="97"/>
-      <c r="I6" s="97"/>
-      <c r="J6" s="97"/>
-      <c r="K6" s="97"/>
-      <c r="L6" s="97"/>
-      <c r="M6" s="97"/>
-      <c r="N6" s="95"/>
-      <c r="O6" s="96"/>
-      <c r="P6" s="94"/>
+      <c r="E6" s="94"/>
+      <c r="F6" s="94"/>
+      <c r="G6" s="94"/>
+      <c r="H6" s="94"/>
+      <c r="I6" s="94"/>
+      <c r="J6" s="94"/>
+      <c r="K6" s="94"/>
+      <c r="L6" s="94"/>
+      <c r="M6" s="94"/>
+      <c r="N6" s="93"/>
+      <c r="O6" s="91"/>
+      <c r="P6" s="92"/>
     </row>
     <row r="7" spans="1:16" ht="39" customHeight="1">
-      <c r="A7" s="94"/>
-      <c r="B7" s="95"/>
-      <c r="C7" s="96"/>
-      <c r="D7" s="97" t="s">
+      <c r="A7" s="92"/>
+      <c r="B7" s="93"/>
+      <c r="C7" s="91"/>
+      <c r="D7" s="94" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="97"/>
-      <c r="F7" s="97"/>
-      <c r="G7" s="97"/>
-      <c r="H7" s="97"/>
-      <c r="I7" s="97"/>
-      <c r="J7" s="97"/>
-      <c r="K7" s="97"/>
-      <c r="L7" s="97"/>
-      <c r="M7" s="97"/>
-      <c r="N7" s="95"/>
-      <c r="O7" s="96"/>
-      <c r="P7" s="94"/>
+      <c r="E7" s="94"/>
+      <c r="F7" s="94"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="94"/>
+      <c r="J7" s="94"/>
+      <c r="K7" s="94"/>
+      <c r="L7" s="94"/>
+      <c r="M7" s="94"/>
+      <c r="N7" s="93"/>
+      <c r="O7" s="91"/>
+      <c r="P7" s="92"/>
     </row>
     <row r="8" spans="1:16" ht="18.5" thickBot="1">
       <c r="A8" s="8"/>
@@ -3276,16 +3270,16 @@
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
-      <c r="F11" s="98" t="s">
+      <c r="F11" s="85" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="99"/>
-      <c r="H11" s="100" t="s">
+      <c r="G11" s="86"/>
+      <c r="H11" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="I11" s="101"/>
-      <c r="J11" s="101"/>
-      <c r="K11" s="101"/>
+      <c r="I11" s="90"/>
+      <c r="J11" s="90"/>
+      <c r="K11" s="90"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -3298,16 +3292,16 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
-      <c r="F12" s="98" t="s">
+      <c r="F12" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="99"/>
-      <c r="H12" s="102">
+      <c r="G12" s="86"/>
+      <c r="H12" s="87">
         <v>46265</v>
       </c>
-      <c r="I12" s="103"/>
-      <c r="J12" s="103"/>
-      <c r="K12" s="103"/>
+      <c r="I12" s="88"/>
+      <c r="J12" s="88"/>
+      <c r="K12" s="88"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
@@ -3320,16 +3314,16 @@
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
-      <c r="F13" s="98" t="s">
+      <c r="F13" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="99"/>
-      <c r="H13" s="102">
+      <c r="G13" s="86"/>
+      <c r="H13" s="87">
         <v>46294</v>
       </c>
-      <c r="I13" s="103"/>
-      <c r="J13" s="103"/>
-      <c r="K13" s="103"/>
+      <c r="I13" s="88"/>
+      <c r="J13" s="88"/>
+      <c r="K13" s="88"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
@@ -3342,14 +3336,14 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
-      <c r="F14" s="98" t="s">
+      <c r="F14" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="99"/>
-      <c r="H14" s="100"/>
-      <c r="I14" s="101"/>
-      <c r="J14" s="101"/>
-      <c r="K14" s="101"/>
+      <c r="G14" s="86"/>
+      <c r="H14" s="89"/>
+      <c r="I14" s="90"/>
+      <c r="J14" s="90"/>
+      <c r="K14" s="90"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
@@ -3484,22 +3478,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:K13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:K14"/>
-    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:M6"/>
+    <mergeCell ref="D7:M7"/>
     <mergeCell ref="P6:P7"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="H11:K11"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="H12:K12"/>
     <mergeCell ref="N6:N7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:M6"/>
-    <mergeCell ref="D7:M7"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="O6:O7"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3512,56 +3506,56 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="115" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="104"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="106" t="s">
+      <c r="B1" s="116"/>
+      <c r="C1" s="117"/>
+      <c r="D1" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="108"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="123"/>
       <c r="P1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="112" t="s">
-        <v>120</v>
-      </c>
-      <c r="R1" s="113"/>
+      <c r="Q1" s="127" t="s">
+        <v>119</v>
+      </c>
+      <c r="R1" s="128"/>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="87"/>
-      <c r="B2" s="105"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="110"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="110"/>
-      <c r="I2" s="110"/>
-      <c r="J2" s="110"/>
-      <c r="K2" s="110"/>
-      <c r="L2" s="110"/>
-      <c r="M2" s="110"/>
-      <c r="N2" s="110"/>
-      <c r="O2" s="111"/>
+      <c r="A2" s="118"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="125"/>
+      <c r="O2" s="126"/>
       <c r="P2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="114">
+      <c r="Q2" s="129">
         <v>46273</v>
       </c>
-      <c r="R2" s="115"/>
+      <c r="R2" s="130"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="2"/>
@@ -3587,459 +3581,459 @@
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="116" t="s">
+      <c r="B4" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="117"/>
-      <c r="D4" s="116" t="s">
+      <c r="C4" s="132"/>
+      <c r="D4" s="131" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="117"/>
-      <c r="F4" s="116" t="s">
+      <c r="E4" s="132"/>
+      <c r="F4" s="131" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="118"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="116" t="s">
+      <c r="G4" s="133"/>
+      <c r="H4" s="132"/>
+      <c r="I4" s="131" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118"/>
-      <c r="M4" s="118"/>
-      <c r="N4" s="118"/>
-      <c r="O4" s="118"/>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="117"/>
+      <c r="J4" s="133"/>
+      <c r="K4" s="133"/>
+      <c r="L4" s="133"/>
+      <c r="M4" s="133"/>
+      <c r="N4" s="133"/>
+      <c r="O4" s="133"/>
+      <c r="P4" s="133"/>
+      <c r="Q4" s="133"/>
+      <c r="R4" s="132"/>
     </row>
     <row r="5" spans="1:18" ht="36" customHeight="1">
       <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="119">
+      <c r="B5" s="105">
         <v>46260</v>
       </c>
-      <c r="C5" s="120"/>
-      <c r="D5" s="121" t="s">
+      <c r="C5" s="106"/>
+      <c r="D5" s="107" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" s="108"/>
+      <c r="F5" s="109" t="s">
         <v>120</v>
       </c>
-      <c r="E5" s="122"/>
-      <c r="F5" s="123" t="s">
-        <v>121</v>
-      </c>
-      <c r="G5" s="124"/>
-      <c r="H5" s="125"/>
-      <c r="I5" s="126"/>
-      <c r="J5" s="127"/>
-      <c r="K5" s="127"/>
-      <c r="L5" s="127"/>
-      <c r="M5" s="127"/>
-      <c r="N5" s="127"/>
-      <c r="O5" s="127"/>
-      <c r="P5" s="127"/>
-      <c r="Q5" s="127"/>
-      <c r="R5" s="128"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="111"/>
+      <c r="I5" s="112"/>
+      <c r="J5" s="113"/>
+      <c r="K5" s="113"/>
+      <c r="L5" s="113"/>
+      <c r="M5" s="113"/>
+      <c r="N5" s="113"/>
+      <c r="O5" s="113"/>
+      <c r="P5" s="113"/>
+      <c r="Q5" s="113"/>
+      <c r="R5" s="114"/>
     </row>
     <row r="6" spans="1:18" ht="36" customHeight="1">
       <c r="A6" s="6">
         <v>2</v>
       </c>
-      <c r="B6" s="129">
+      <c r="B6" s="101">
         <v>46266</v>
       </c>
-      <c r="C6" s="130"/>
-      <c r="D6" s="131" t="s">
-        <v>120</v>
-      </c>
-      <c r="E6" s="130"/>
-      <c r="F6" s="132" t="s">
-        <v>122</v>
-      </c>
-      <c r="G6" s="133"/>
-      <c r="H6" s="134"/>
-      <c r="I6" s="132" t="s">
-        <v>124</v>
-      </c>
-      <c r="J6" s="135"/>
-      <c r="K6" s="135"/>
-      <c r="L6" s="135"/>
-      <c r="M6" s="135"/>
-      <c r="N6" s="135"/>
-      <c r="O6" s="135"/>
-      <c r="P6" s="135"/>
-      <c r="Q6" s="135"/>
-      <c r="R6" s="136"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="95" t="s">
+        <v>119</v>
+      </c>
+      <c r="E6" s="96"/>
+      <c r="F6" s="102" t="s">
+        <v>121</v>
+      </c>
+      <c r="G6" s="103"/>
+      <c r="H6" s="104"/>
+      <c r="I6" s="102" t="s">
+        <v>123</v>
+      </c>
+      <c r="J6" s="99"/>
+      <c r="K6" s="99"/>
+      <c r="L6" s="99"/>
+      <c r="M6" s="99"/>
+      <c r="N6" s="99"/>
+      <c r="O6" s="99"/>
+      <c r="P6" s="99"/>
+      <c r="Q6" s="99"/>
+      <c r="R6" s="100"/>
     </row>
     <row r="7" spans="1:18" ht="36" customHeight="1">
       <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="129">
+      <c r="B7" s="101">
         <v>46268</v>
       </c>
-      <c r="C7" s="130"/>
-      <c r="D7" s="131" t="s">
-        <v>120</v>
-      </c>
-      <c r="E7" s="130"/>
-      <c r="F7" s="132" t="s">
-        <v>123</v>
-      </c>
-      <c r="G7" s="133"/>
-      <c r="H7" s="134"/>
-      <c r="I7" s="137"/>
-      <c r="J7" s="135"/>
-      <c r="K7" s="135"/>
-      <c r="L7" s="135"/>
-      <c r="M7" s="135"/>
-      <c r="N7" s="135"/>
-      <c r="O7" s="135"/>
-      <c r="P7" s="135"/>
-      <c r="Q7" s="135"/>
-      <c r="R7" s="136"/>
+      <c r="C7" s="96"/>
+      <c r="D7" s="95" t="s">
+        <v>119</v>
+      </c>
+      <c r="E7" s="96"/>
+      <c r="F7" s="102" t="s">
+        <v>122</v>
+      </c>
+      <c r="G7" s="103"/>
+      <c r="H7" s="104"/>
+      <c r="I7" s="98"/>
+      <c r="J7" s="99"/>
+      <c r="K7" s="99"/>
+      <c r="L7" s="99"/>
+      <c r="M7" s="99"/>
+      <c r="N7" s="99"/>
+      <c r="O7" s="99"/>
+      <c r="P7" s="99"/>
+      <c r="Q7" s="99"/>
+      <c r="R7" s="100"/>
     </row>
     <row r="8" spans="1:18" ht="36" customHeight="1">
       <c r="A8" s="6">
         <v>4</v>
       </c>
-      <c r="B8" s="129">
+      <c r="B8" s="101">
         <v>46273</v>
       </c>
-      <c r="C8" s="130"/>
-      <c r="D8" s="131" t="s">
+      <c r="C8" s="96"/>
+      <c r="D8" s="95" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="130"/>
-      <c r="F8" s="137" t="s">
-        <v>156</v>
-      </c>
-      <c r="G8" s="135"/>
-      <c r="H8" s="136"/>
-      <c r="I8" s="137"/>
-      <c r="J8" s="135"/>
-      <c r="K8" s="135"/>
-      <c r="L8" s="135"/>
-      <c r="M8" s="135"/>
-      <c r="N8" s="135"/>
-      <c r="O8" s="135"/>
-      <c r="P8" s="135"/>
-      <c r="Q8" s="135"/>
-      <c r="R8" s="136"/>
+      <c r="E8" s="96"/>
+      <c r="F8" s="98" t="s">
+        <v>155</v>
+      </c>
+      <c r="G8" s="99"/>
+      <c r="H8" s="100"/>
+      <c r="I8" s="98"/>
+      <c r="J8" s="99"/>
+      <c r="K8" s="99"/>
+      <c r="L8" s="99"/>
+      <c r="M8" s="99"/>
+      <c r="N8" s="99"/>
+      <c r="O8" s="99"/>
+      <c r="P8" s="99"/>
+      <c r="Q8" s="99"/>
+      <c r="R8" s="100"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="6">
         <v>5</v>
       </c>
-      <c r="B9" s="129">
+      <c r="B9" s="101">
         <v>46294</v>
       </c>
-      <c r="C9" s="130"/>
-      <c r="D9" s="131" t="s">
+      <c r="C9" s="96"/>
+      <c r="D9" s="95" t="s">
         <v>65</v>
       </c>
-      <c r="E9" s="130"/>
-      <c r="F9" s="137" t="s">
-        <v>182</v>
-      </c>
-      <c r="G9" s="135"/>
-      <c r="H9" s="136"/>
-      <c r="I9" s="137"/>
-      <c r="J9" s="135"/>
-      <c r="K9" s="135"/>
-      <c r="L9" s="135"/>
-      <c r="M9" s="135"/>
-      <c r="N9" s="135"/>
-      <c r="O9" s="135"/>
-      <c r="P9" s="135"/>
-      <c r="Q9" s="135"/>
-      <c r="R9" s="136"/>
+      <c r="E9" s="96"/>
+      <c r="F9" s="98" t="s">
+        <v>181</v>
+      </c>
+      <c r="G9" s="99"/>
+      <c r="H9" s="100"/>
+      <c r="I9" s="98"/>
+      <c r="J9" s="99"/>
+      <c r="K9" s="99"/>
+      <c r="L9" s="99"/>
+      <c r="M9" s="99"/>
+      <c r="N9" s="99"/>
+      <c r="O9" s="99"/>
+      <c r="P9" s="99"/>
+      <c r="Q9" s="99"/>
+      <c r="R9" s="100"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="6">
         <v>6</v>
       </c>
-      <c r="B10" s="131"/>
-      <c r="C10" s="130"/>
-      <c r="D10" s="131"/>
-      <c r="E10" s="130"/>
-      <c r="F10" s="131"/>
-      <c r="G10" s="138"/>
-      <c r="H10" s="130"/>
-      <c r="I10" s="137"/>
-      <c r="J10" s="135"/>
-      <c r="K10" s="135"/>
-      <c r="L10" s="135"/>
-      <c r="M10" s="135"/>
-      <c r="N10" s="135"/>
-      <c r="O10" s="135"/>
-      <c r="P10" s="135"/>
-      <c r="Q10" s="135"/>
-      <c r="R10" s="136"/>
+      <c r="B10" s="95"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="95"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="95"/>
+      <c r="G10" s="97"/>
+      <c r="H10" s="96"/>
+      <c r="I10" s="98"/>
+      <c r="J10" s="99"/>
+      <c r="K10" s="99"/>
+      <c r="L10" s="99"/>
+      <c r="M10" s="99"/>
+      <c r="N10" s="99"/>
+      <c r="O10" s="99"/>
+      <c r="P10" s="99"/>
+      <c r="Q10" s="99"/>
+      <c r="R10" s="100"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="6">
         <v>7</v>
       </c>
-      <c r="B11" s="131"/>
-      <c r="C11" s="130"/>
-      <c r="D11" s="131"/>
-      <c r="E11" s="130"/>
-      <c r="F11" s="131"/>
-      <c r="G11" s="138"/>
-      <c r="H11" s="130"/>
-      <c r="I11" s="137"/>
-      <c r="J11" s="135"/>
-      <c r="K11" s="135"/>
-      <c r="L11" s="135"/>
-      <c r="M11" s="135"/>
-      <c r="N11" s="135"/>
-      <c r="O11" s="135"/>
-      <c r="P11" s="135"/>
-      <c r="Q11" s="135"/>
-      <c r="R11" s="136"/>
+      <c r="B11" s="95"/>
+      <c r="C11" s="96"/>
+      <c r="D11" s="95"/>
+      <c r="E11" s="96"/>
+      <c r="F11" s="95"/>
+      <c r="G11" s="97"/>
+      <c r="H11" s="96"/>
+      <c r="I11" s="98"/>
+      <c r="J11" s="99"/>
+      <c r="K11" s="99"/>
+      <c r="L11" s="99"/>
+      <c r="M11" s="99"/>
+      <c r="N11" s="99"/>
+      <c r="O11" s="99"/>
+      <c r="P11" s="99"/>
+      <c r="Q11" s="99"/>
+      <c r="R11" s="100"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="6">
         <v>8</v>
       </c>
-      <c r="B12" s="131"/>
-      <c r="C12" s="130"/>
-      <c r="D12" s="131"/>
-      <c r="E12" s="130"/>
-      <c r="F12" s="131"/>
-      <c r="G12" s="138"/>
-      <c r="H12" s="130"/>
-      <c r="I12" s="137"/>
-      <c r="J12" s="135"/>
-      <c r="K12" s="135"/>
-      <c r="L12" s="135"/>
-      <c r="M12" s="135"/>
-      <c r="N12" s="135"/>
-      <c r="O12" s="135"/>
-      <c r="P12" s="135"/>
-      <c r="Q12" s="135"/>
-      <c r="R12" s="136"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="96"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="96"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="97"/>
+      <c r="H12" s="96"/>
+      <c r="I12" s="98"/>
+      <c r="J12" s="99"/>
+      <c r="K12" s="99"/>
+      <c r="L12" s="99"/>
+      <c r="M12" s="99"/>
+      <c r="N12" s="99"/>
+      <c r="O12" s="99"/>
+      <c r="P12" s="99"/>
+      <c r="Q12" s="99"/>
+      <c r="R12" s="100"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="6">
         <v>9</v>
       </c>
-      <c r="B13" s="131"/>
-      <c r="C13" s="130"/>
-      <c r="D13" s="131"/>
-      <c r="E13" s="130"/>
-      <c r="F13" s="131"/>
-      <c r="G13" s="138"/>
-      <c r="H13" s="130"/>
-      <c r="I13" s="137"/>
-      <c r="J13" s="135"/>
-      <c r="K13" s="135"/>
-      <c r="L13" s="135"/>
-      <c r="M13" s="135"/>
-      <c r="N13" s="135"/>
-      <c r="O13" s="135"/>
-      <c r="P13" s="135"/>
-      <c r="Q13" s="135"/>
-      <c r="R13" s="136"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="96"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="96"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="97"/>
+      <c r="H13" s="96"/>
+      <c r="I13" s="98"/>
+      <c r="J13" s="99"/>
+      <c r="K13" s="99"/>
+      <c r="L13" s="99"/>
+      <c r="M13" s="99"/>
+      <c r="N13" s="99"/>
+      <c r="O13" s="99"/>
+      <c r="P13" s="99"/>
+      <c r="Q13" s="99"/>
+      <c r="R13" s="100"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="6">
         <v>10</v>
       </c>
-      <c r="B14" s="131"/>
-      <c r="C14" s="130"/>
-      <c r="D14" s="131"/>
-      <c r="E14" s="130"/>
-      <c r="F14" s="131"/>
-      <c r="G14" s="138"/>
-      <c r="H14" s="130"/>
-      <c r="I14" s="137"/>
-      <c r="J14" s="135"/>
-      <c r="K14" s="135"/>
-      <c r="L14" s="135"/>
-      <c r="M14" s="135"/>
-      <c r="N14" s="135"/>
-      <c r="O14" s="135"/>
-      <c r="P14" s="135"/>
-      <c r="Q14" s="135"/>
-      <c r="R14" s="136"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="96"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="96"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="97"/>
+      <c r="H14" s="96"/>
+      <c r="I14" s="98"/>
+      <c r="J14" s="99"/>
+      <c r="K14" s="99"/>
+      <c r="L14" s="99"/>
+      <c r="M14" s="99"/>
+      <c r="N14" s="99"/>
+      <c r="O14" s="99"/>
+      <c r="P14" s="99"/>
+      <c r="Q14" s="99"/>
+      <c r="R14" s="100"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="6">
         <v>11</v>
       </c>
-      <c r="B15" s="131"/>
-      <c r="C15" s="130"/>
-      <c r="D15" s="131"/>
-      <c r="E15" s="130"/>
-      <c r="F15" s="131"/>
-      <c r="G15" s="138"/>
-      <c r="H15" s="130"/>
-      <c r="I15" s="137"/>
-      <c r="J15" s="135"/>
-      <c r="K15" s="135"/>
-      <c r="L15" s="135"/>
-      <c r="M15" s="135"/>
-      <c r="N15" s="135"/>
-      <c r="O15" s="135"/>
-      <c r="P15" s="135"/>
-      <c r="Q15" s="135"/>
-      <c r="R15" s="136"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="96"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="96"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="97"/>
+      <c r="H15" s="96"/>
+      <c r="I15" s="98"/>
+      <c r="J15" s="99"/>
+      <c r="K15" s="99"/>
+      <c r="L15" s="99"/>
+      <c r="M15" s="99"/>
+      <c r="N15" s="99"/>
+      <c r="O15" s="99"/>
+      <c r="P15" s="99"/>
+      <c r="Q15" s="99"/>
+      <c r="R15" s="100"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="6">
         <v>12</v>
       </c>
-      <c r="B16" s="131"/>
-      <c r="C16" s="130"/>
-      <c r="D16" s="131"/>
-      <c r="E16" s="130"/>
-      <c r="F16" s="131"/>
-      <c r="G16" s="138"/>
-      <c r="H16" s="130"/>
-      <c r="I16" s="137"/>
-      <c r="J16" s="135"/>
-      <c r="K16" s="135"/>
-      <c r="L16" s="135"/>
-      <c r="M16" s="135"/>
-      <c r="N16" s="135"/>
-      <c r="O16" s="135"/>
-      <c r="P16" s="135"/>
-      <c r="Q16" s="135"/>
-      <c r="R16" s="136"/>
+      <c r="B16" s="95"/>
+      <c r="C16" s="96"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="96"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="97"/>
+      <c r="H16" s="96"/>
+      <c r="I16" s="98"/>
+      <c r="J16" s="99"/>
+      <c r="K16" s="99"/>
+      <c r="L16" s="99"/>
+      <c r="M16" s="99"/>
+      <c r="N16" s="99"/>
+      <c r="O16" s="99"/>
+      <c r="P16" s="99"/>
+      <c r="Q16" s="99"/>
+      <c r="R16" s="100"/>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="6">
         <v>13</v>
       </c>
-      <c r="B17" s="131"/>
-      <c r="C17" s="130"/>
-      <c r="D17" s="131"/>
-      <c r="E17" s="130"/>
-      <c r="F17" s="131"/>
-      <c r="G17" s="138"/>
-      <c r="H17" s="130"/>
-      <c r="I17" s="137"/>
-      <c r="J17" s="135"/>
-      <c r="K17" s="135"/>
-      <c r="L17" s="135"/>
-      <c r="M17" s="135"/>
-      <c r="N17" s="135"/>
-      <c r="O17" s="135"/>
-      <c r="P17" s="135"/>
-      <c r="Q17" s="135"/>
-      <c r="R17" s="136"/>
+      <c r="B17" s="95"/>
+      <c r="C17" s="96"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="96"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="97"/>
+      <c r="H17" s="96"/>
+      <c r="I17" s="98"/>
+      <c r="J17" s="99"/>
+      <c r="K17" s="99"/>
+      <c r="L17" s="99"/>
+      <c r="M17" s="99"/>
+      <c r="N17" s="99"/>
+      <c r="O17" s="99"/>
+      <c r="P17" s="99"/>
+      <c r="Q17" s="99"/>
+      <c r="R17" s="100"/>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="6">
         <v>14</v>
       </c>
-      <c r="B18" s="131"/>
-      <c r="C18" s="130"/>
-      <c r="D18" s="131"/>
-      <c r="E18" s="130"/>
-      <c r="F18" s="131"/>
-      <c r="G18" s="138"/>
-      <c r="H18" s="130"/>
-      <c r="I18" s="137"/>
-      <c r="J18" s="135"/>
-      <c r="K18" s="135"/>
-      <c r="L18" s="135"/>
-      <c r="M18" s="135"/>
-      <c r="N18" s="135"/>
-      <c r="O18" s="135"/>
-      <c r="P18" s="135"/>
-      <c r="Q18" s="135"/>
-      <c r="R18" s="136"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="96"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="96"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="97"/>
+      <c r="H18" s="96"/>
+      <c r="I18" s="98"/>
+      <c r="J18" s="99"/>
+      <c r="K18" s="99"/>
+      <c r="L18" s="99"/>
+      <c r="M18" s="99"/>
+      <c r="N18" s="99"/>
+      <c r="O18" s="99"/>
+      <c r="P18" s="99"/>
+      <c r="Q18" s="99"/>
+      <c r="R18" s="100"/>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="6">
         <v>15</v>
       </c>
-      <c r="B19" s="131"/>
-      <c r="C19" s="130"/>
-      <c r="D19" s="131"/>
-      <c r="E19" s="130"/>
-      <c r="F19" s="131"/>
-      <c r="G19" s="138"/>
-      <c r="H19" s="130"/>
-      <c r="I19" s="137"/>
-      <c r="J19" s="135"/>
-      <c r="K19" s="135"/>
-      <c r="L19" s="135"/>
-      <c r="M19" s="135"/>
-      <c r="N19" s="135"/>
-      <c r="O19" s="135"/>
-      <c r="P19" s="135"/>
-      <c r="Q19" s="135"/>
-      <c r="R19" s="136"/>
+      <c r="B19" s="95"/>
+      <c r="C19" s="96"/>
+      <c r="D19" s="95"/>
+      <c r="E19" s="96"/>
+      <c r="F19" s="95"/>
+      <c r="G19" s="97"/>
+      <c r="H19" s="96"/>
+      <c r="I19" s="98"/>
+      <c r="J19" s="99"/>
+      <c r="K19" s="99"/>
+      <c r="L19" s="99"/>
+      <c r="M19" s="99"/>
+      <c r="N19" s="99"/>
+      <c r="O19" s="99"/>
+      <c r="P19" s="99"/>
+      <c r="Q19" s="99"/>
+      <c r="R19" s="100"/>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="6">
         <v>16</v>
       </c>
-      <c r="B20" s="131"/>
-      <c r="C20" s="130"/>
-      <c r="D20" s="131"/>
-      <c r="E20" s="130"/>
-      <c r="F20" s="131"/>
-      <c r="G20" s="138"/>
-      <c r="H20" s="130"/>
-      <c r="I20" s="137"/>
-      <c r="J20" s="135"/>
-      <c r="K20" s="135"/>
-      <c r="L20" s="135"/>
-      <c r="M20" s="135"/>
-      <c r="N20" s="135"/>
-      <c r="O20" s="135"/>
-      <c r="P20" s="135"/>
-      <c r="Q20" s="135"/>
-      <c r="R20" s="136"/>
+      <c r="B20" s="95"/>
+      <c r="C20" s="96"/>
+      <c r="D20" s="95"/>
+      <c r="E20" s="96"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="97"/>
+      <c r="H20" s="96"/>
+      <c r="I20" s="98"/>
+      <c r="J20" s="99"/>
+      <c r="K20" s="99"/>
+      <c r="L20" s="99"/>
+      <c r="M20" s="99"/>
+      <c r="N20" s="99"/>
+      <c r="O20" s="99"/>
+      <c r="P20" s="99"/>
+      <c r="Q20" s="99"/>
+      <c r="R20" s="100"/>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="6">
         <v>17</v>
       </c>
-      <c r="B21" s="131"/>
-      <c r="C21" s="130"/>
-      <c r="D21" s="131"/>
-      <c r="E21" s="130"/>
-      <c r="F21" s="131"/>
-      <c r="G21" s="138"/>
-      <c r="H21" s="130"/>
-      <c r="I21" s="137"/>
-      <c r="J21" s="135"/>
-      <c r="K21" s="135"/>
-      <c r="L21" s="135"/>
-      <c r="M21" s="135"/>
-      <c r="N21" s="135"/>
-      <c r="O21" s="135"/>
-      <c r="P21" s="135"/>
-      <c r="Q21" s="135"/>
-      <c r="R21" s="136"/>
+      <c r="B21" s="95"/>
+      <c r="C21" s="96"/>
+      <c r="D21" s="95"/>
+      <c r="E21" s="96"/>
+      <c r="F21" s="95"/>
+      <c r="G21" s="97"/>
+      <c r="H21" s="96"/>
+      <c r="I21" s="98"/>
+      <c r="J21" s="99"/>
+      <c r="K21" s="99"/>
+      <c r="L21" s="99"/>
+      <c r="M21" s="99"/>
+      <c r="N21" s="99"/>
+      <c r="O21" s="99"/>
+      <c r="P21" s="99"/>
+      <c r="Q21" s="99"/>
+      <c r="R21" s="100"/>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="6">
         <v>18</v>
       </c>
-      <c r="B22" s="131"/>
-      <c r="C22" s="130"/>
-      <c r="D22" s="131"/>
-      <c r="E22" s="130"/>
-      <c r="F22" s="131"/>
-      <c r="G22" s="138"/>
-      <c r="H22" s="130"/>
-      <c r="I22" s="137"/>
-      <c r="J22" s="135"/>
-      <c r="K22" s="135"/>
-      <c r="L22" s="135"/>
-      <c r="M22" s="135"/>
-      <c r="N22" s="135"/>
-      <c r="O22" s="135"/>
-      <c r="P22" s="135"/>
-      <c r="Q22" s="135"/>
-      <c r="R22" s="136"/>
+      <c r="B22" s="95"/>
+      <c r="C22" s="96"/>
+      <c r="D22" s="95"/>
+      <c r="E22" s="96"/>
+      <c r="F22" s="95"/>
+      <c r="G22" s="97"/>
+      <c r="H22" s="96"/>
+      <c r="I22" s="98"/>
+      <c r="J22" s="99"/>
+      <c r="K22" s="99"/>
+      <c r="L22" s="99"/>
+      <c r="M22" s="99"/>
+      <c r="N22" s="99"/>
+      <c r="O22" s="99"/>
+      <c r="P22" s="99"/>
+      <c r="Q22" s="99"/>
+      <c r="R22" s="100"/>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="5"/>
@@ -4183,6 +4177,78 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:O2"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="I4:R4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="I5:R5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="I6:R6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="I7:R7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="I8:R8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="I9:R9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="I10:R10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="I11:R11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="I12:R12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="I13:R13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:R14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:R15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:R16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:R17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:R18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:R19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:R20"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="F21:H21"/>
@@ -4191,78 +4257,6 @@
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="F22:H22"/>
     <mergeCell ref="I22:R22"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:R19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="I20:R20"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:R17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:R18"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:R15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:R16"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="I13:R13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:R14"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="I11:R11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="I12:R12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="I9:R9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="I10:R10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="I7:R7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="I8:R8"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="I5:R5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="I6:R6"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="D1:O2"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="I4:R4"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4275,27 +4269,27 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="85" t="s">
+      <c r="B1" s="117"/>
+      <c r="C1" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="104"/>
-      <c r="E1" s="104"/>
-      <c r="F1" s="104"/>
-      <c r="G1" s="104"/>
-      <c r="H1" s="104"/>
-      <c r="I1" s="104"/>
-      <c r="J1" s="104"/>
-      <c r="K1" s="104"/>
-      <c r="L1" s="86"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="117"/>
       <c r="M1" s="24" t="s">
         <v>2</v>
       </c>
       <c r="N1" s="22" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O1" s="25" t="s">
         <v>3</v>
@@ -4305,18 +4299,18 @@
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="87"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="88"/>
+      <c r="A2" s="118"/>
+      <c r="B2" s="120"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="119"/>
+      <c r="L2" s="120"/>
       <c r="M2" s="27" t="s">
         <v>13</v>
       </c>
@@ -4348,26 +4342,26 @@
       <c r="A4" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="139" t="s">
+      <c r="B4" s="134" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="140"/>
-      <c r="D4" s="140"/>
-      <c r="E4" s="140"/>
-      <c r="F4" s="140"/>
-      <c r="G4" s="141"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="135"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="135"/>
+      <c r="G4" s="136"/>
       <c r="H4" s="31"/>
       <c r="I4" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="139" t="s">
+      <c r="J4" s="134" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="140"/>
-      <c r="L4" s="140"/>
-      <c r="M4" s="140"/>
-      <c r="N4" s="140"/>
-      <c r="O4" s="141"/>
+      <c r="K4" s="135"/>
+      <c r="L4" s="135"/>
+      <c r="M4" s="135"/>
+      <c r="N4" s="135"/>
+      <c r="O4" s="136"/>
       <c r="P4" s="35"/>
     </row>
     <row r="5" spans="1:16">
@@ -4393,7 +4387,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
@@ -4402,10 +4396,10 @@
       <c r="G6" s="31"/>
       <c r="H6" s="7"/>
       <c r="I6" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="J6" s="31" t="s">
         <v>143</v>
-      </c>
-      <c r="J6" s="31" t="s">
-        <v>144</v>
       </c>
       <c r="K6" s="31"/>
       <c r="L6" s="31"/>
@@ -4416,10 +4410,10 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="77" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
@@ -4428,10 +4422,10 @@
       <c r="G7" s="31"/>
       <c r="H7" s="7"/>
       <c r="I7" s="77" t="s">
+        <v>144</v>
+      </c>
+      <c r="J7" s="31" t="s">
         <v>145</v>
-      </c>
-      <c r="J7" s="31" t="s">
-        <v>146</v>
       </c>
       <c r="K7" s="31"/>
       <c r="L7" s="31"/>
@@ -4442,10 +4436,10 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="77" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" s="35"/>
       <c r="D8" s="35"/>
@@ -4454,10 +4448,10 @@
       <c r="G8" s="35"/>
       <c r="H8" s="7"/>
       <c r="I8" s="77" t="s">
+        <v>146</v>
+      </c>
+      <c r="J8" s="35" t="s">
         <v>147</v>
-      </c>
-      <c r="J8" s="35" t="s">
-        <v>148</v>
       </c>
       <c r="K8" s="35"/>
       <c r="L8" s="35"/>
@@ -4468,10 +4462,10 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="77" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C9" s="31"/>
       <c r="D9" s="31"/>
@@ -4490,10 +4484,10 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="77" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C10" s="31"/>
       <c r="D10" s="31"/>
@@ -4502,7 +4496,7 @@
       <c r="G10" s="31"/>
       <c r="H10" s="7"/>
       <c r="I10" s="36" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J10" s="31"/>
       <c r="K10" s="31"/>
@@ -4517,7 +4511,7 @@
         <v>1.5</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C11" s="31"/>
       <c r="D11" s="31"/>
@@ -4526,10 +4520,10 @@
       <c r="G11" s="31"/>
       <c r="H11" s="7"/>
       <c r="I11" s="78" t="s">
+        <v>149</v>
+      </c>
+      <c r="J11" s="31" t="s">
         <v>150</v>
-      </c>
-      <c r="J11" s="31" t="s">
-        <v>151</v>
       </c>
       <c r="K11" s="31"/>
       <c r="L11" s="31"/>
@@ -4561,7 +4555,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C13" s="31"/>
       <c r="D13" s="31"/>
@@ -4570,7 +4564,7 @@
       <c r="G13" s="31"/>
       <c r="H13" s="7"/>
       <c r="I13" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J13" s="31"/>
       <c r="K13" s="31"/>
@@ -4582,10 +4576,10 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="78" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C14" s="31"/>
       <c r="D14" s="31"/>
@@ -4594,10 +4588,10 @@
       <c r="G14" s="31"/>
       <c r="H14" s="31"/>
       <c r="I14" s="78" t="s">
+        <v>152</v>
+      </c>
+      <c r="J14" s="31" t="s">
         <v>153</v>
-      </c>
-      <c r="J14" s="31" t="s">
-        <v>154</v>
       </c>
       <c r="K14" s="31"/>
       <c r="L14" s="31"/>
@@ -4629,7 +4623,7 @@
         <v>20</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C16" s="31"/>
       <c r="D16" s="31"/>
@@ -4648,10 +4642,10 @@
     </row>
     <row r="17" spans="1:16" ht="26.5">
       <c r="A17" s="78" t="s">
+        <v>138</v>
+      </c>
+      <c r="B17" s="31" t="s">
         <v>139</v>
-      </c>
-      <c r="B17" s="31" t="s">
-        <v>140</v>
       </c>
       <c r="C17" s="31"/>
       <c r="D17" s="31"/>
@@ -4670,10 +4664,10 @@
     </row>
     <row r="18" spans="1:16" ht="26.5">
       <c r="A18" s="78" t="s">
+        <v>140</v>
+      </c>
+      <c r="B18" s="35" t="s">
         <v>141</v>
-      </c>
-      <c r="B18" s="35" t="s">
-        <v>142</v>
       </c>
       <c r="C18" s="35"/>
       <c r="D18" s="35"/>
@@ -4783,23 +4777,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="89" t="s">
+      <c r="B1" s="117"/>
+      <c r="C1" s="138" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="90"/>
-      <c r="E1" s="91" t="s">
+      <c r="D1" s="139"/>
+      <c r="E1" s="140" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="93"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="142"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -4814,17 +4808,17 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="93"/>
+      <c r="A2" s="118"/>
+      <c r="B2" s="120"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="139"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="142"/>
       <c r="L2" s="29" t="s">
         <v>13</v>
       </c>
@@ -5022,115 +5016,115 @@
     </row>
     <row r="13" spans="1:15" ht="18" customHeight="1">
       <c r="A13" s="35"/>
-      <c r="B13" s="142" t="s">
+      <c r="B13" s="137" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="142"/>
-      <c r="D13" s="142"/>
-      <c r="E13" s="142"/>
-      <c r="F13" s="142"/>
-      <c r="G13" s="142"/>
-      <c r="H13" s="142"/>
-      <c r="I13" s="142"/>
-      <c r="J13" s="142"/>
-      <c r="K13" s="142"/>
-      <c r="L13" s="142"/>
-      <c r="M13" s="142"/>
-      <c r="N13" s="142"/>
-      <c r="O13" s="142"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="137"/>
+      <c r="E13" s="137"/>
+      <c r="F13" s="137"/>
+      <c r="G13" s="137"/>
+      <c r="H13" s="137"/>
+      <c r="I13" s="137"/>
+      <c r="J13" s="137"/>
+      <c r="K13" s="137"/>
+      <c r="L13" s="137"/>
+      <c r="M13" s="137"/>
+      <c r="N13" s="137"/>
+      <c r="O13" s="137"/>
     </row>
     <row r="14" spans="1:15" ht="18" customHeight="1">
       <c r="A14" s="35"/>
-      <c r="B14" s="142" t="s">
+      <c r="B14" s="137" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="142"/>
-      <c r="D14" s="142"/>
-      <c r="E14" s="142"/>
-      <c r="F14" s="142"/>
-      <c r="G14" s="142"/>
-      <c r="H14" s="142"/>
-      <c r="I14" s="142"/>
-      <c r="J14" s="142"/>
-      <c r="K14" s="142"/>
-      <c r="L14" s="142"/>
-      <c r="M14" s="142"/>
-      <c r="N14" s="142"/>
-      <c r="O14" s="142"/>
+      <c r="C14" s="137"/>
+      <c r="D14" s="137"/>
+      <c r="E14" s="137"/>
+      <c r="F14" s="137"/>
+      <c r="G14" s="137"/>
+      <c r="H14" s="137"/>
+      <c r="I14" s="137"/>
+      <c r="J14" s="137"/>
+      <c r="K14" s="137"/>
+      <c r="L14" s="137"/>
+      <c r="M14" s="137"/>
+      <c r="N14" s="137"/>
+      <c r="O14" s="137"/>
     </row>
     <row r="15" spans="1:15" ht="18" customHeight="1">
       <c r="A15" s="35"/>
-      <c r="B15" s="142" t="s">
+      <c r="B15" s="137" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="142"/>
-      <c r="D15" s="142"/>
-      <c r="E15" s="142"/>
-      <c r="F15" s="142"/>
-      <c r="G15" s="142"/>
-      <c r="H15" s="142"/>
-      <c r="I15" s="142"/>
-      <c r="J15" s="142"/>
-      <c r="K15" s="142"/>
-      <c r="L15" s="142"/>
-      <c r="M15" s="142"/>
-      <c r="N15" s="142"/>
-      <c r="O15" s="142"/>
+      <c r="C15" s="137"/>
+      <c r="D15" s="137"/>
+      <c r="E15" s="137"/>
+      <c r="F15" s="137"/>
+      <c r="G15" s="137"/>
+      <c r="H15" s="137"/>
+      <c r="I15" s="137"/>
+      <c r="J15" s="137"/>
+      <c r="K15" s="137"/>
+      <c r="L15" s="137"/>
+      <c r="M15" s="137"/>
+      <c r="N15" s="137"/>
+      <c r="O15" s="137"/>
     </row>
     <row r="16" spans="1:15" ht="18" customHeight="1">
       <c r="A16" s="35"/>
-      <c r="B16" s="142" t="s">
+      <c r="B16" s="137" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="142"/>
-      <c r="D16" s="142"/>
-      <c r="E16" s="142"/>
-      <c r="F16" s="142"/>
-      <c r="G16" s="142"/>
-      <c r="H16" s="142"/>
-      <c r="I16" s="142"/>
-      <c r="J16" s="142"/>
-      <c r="K16" s="142"/>
-      <c r="L16" s="142"/>
-      <c r="M16" s="142"/>
-      <c r="N16" s="142"/>
-      <c r="O16" s="142"/>
+      <c r="C16" s="137"/>
+      <c r="D16" s="137"/>
+      <c r="E16" s="137"/>
+      <c r="F16" s="137"/>
+      <c r="G16" s="137"/>
+      <c r="H16" s="137"/>
+      <c r="I16" s="137"/>
+      <c r="J16" s="137"/>
+      <c r="K16" s="137"/>
+      <c r="L16" s="137"/>
+      <c r="M16" s="137"/>
+      <c r="N16" s="137"/>
+      <c r="O16" s="137"/>
     </row>
     <row r="17" spans="1:15" ht="18" customHeight="1">
       <c r="A17" s="35"/>
-      <c r="B17" s="142" t="s">
+      <c r="B17" s="137" t="s">
         <v>63</v>
       </c>
-      <c r="C17" s="142"/>
-      <c r="D17" s="142"/>
-      <c r="E17" s="142"/>
-      <c r="F17" s="142"/>
-      <c r="G17" s="142"/>
-      <c r="H17" s="142"/>
-      <c r="I17" s="142"/>
-      <c r="J17" s="142"/>
-      <c r="K17" s="142"/>
-      <c r="L17" s="142"/>
-      <c r="M17" s="142"/>
-      <c r="N17" s="142"/>
-      <c r="O17" s="142"/>
+      <c r="C17" s="137"/>
+      <c r="D17" s="137"/>
+      <c r="E17" s="137"/>
+      <c r="F17" s="137"/>
+      <c r="G17" s="137"/>
+      <c r="H17" s="137"/>
+      <c r="I17" s="137"/>
+      <c r="J17" s="137"/>
+      <c r="K17" s="137"/>
+      <c r="L17" s="137"/>
+      <c r="M17" s="137"/>
+      <c r="N17" s="137"/>
+      <c r="O17" s="137"/>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="35"/>
-      <c r="B18" s="142"/>
-      <c r="C18" s="142"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="142"/>
-      <c r="G18" s="142"/>
-      <c r="H18" s="142"/>
-      <c r="I18" s="142"/>
-      <c r="J18" s="142"/>
-      <c r="K18" s="142"/>
-      <c r="L18" s="142"/>
-      <c r="M18" s="142"/>
-      <c r="N18" s="142"/>
-      <c r="O18" s="142"/>
+      <c r="B18" s="137"/>
+      <c r="C18" s="137"/>
+      <c r="D18" s="137"/>
+      <c r="E18" s="137"/>
+      <c r="F18" s="137"/>
+      <c r="G18" s="137"/>
+      <c r="H18" s="137"/>
+      <c r="I18" s="137"/>
+      <c r="J18" s="137"/>
+      <c r="K18" s="137"/>
+      <c r="L18" s="137"/>
+      <c r="M18" s="137"/>
+      <c r="N18" s="137"/>
+      <c r="O18" s="137"/>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="35"/>
@@ -5335,7 +5329,7 @@
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
       <c r="B30" s="47" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -5435,23 +5429,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="89" t="s">
+      <c r="B1" s="117"/>
+      <c r="C1" s="138" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="90"/>
-      <c r="E1" s="91" t="s">
+      <c r="D1" s="139"/>
+      <c r="E1" s="140" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="93"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="142"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -5466,17 +5460,17 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="93"/>
+      <c r="A2" s="118"/>
+      <c r="B2" s="120"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="139"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="142"/>
       <c r="L2" s="29" t="s">
         <v>13</v>
       </c>
@@ -5550,7 +5544,7 @@
       </c>
       <c r="C6" s="147"/>
       <c r="D6" s="83" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E6" s="50"/>
       <c r="F6" s="50"/>
@@ -5592,7 +5586,7 @@
       </c>
       <c r="C8" s="145"/>
       <c r="D8" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
@@ -6056,14 +6050,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="89" t="s">
+      <c r="B1" s="117"/>
+      <c r="C1" s="138" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="90"/>
+      <c r="D1" s="139"/>
       <c r="E1" s="71" t="s">
         <v>73</v>
       </c>
@@ -6087,16 +6081,16 @@
       <c r="O1" s="150"/>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="93"/>
+      <c r="A2" s="118"/>
+      <c r="B2" s="120"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="139"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="142"/>
       <c r="K2" s="29" t="s">
         <v>13</v>
       </c>
@@ -6107,7 +6101,7 @@
         <v>14</v>
       </c>
       <c r="N2" s="151">
-        <v>46281</v>
+        <v>46302</v>
       </c>
       <c r="O2" s="151"/>
     </row>
@@ -6272,7 +6266,7 @@
       <c r="I10" s="54"/>
       <c r="J10" s="55"/>
       <c r="K10" s="148" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L10" s="149"/>
       <c r="M10" s="31"/>
@@ -6381,7 +6375,7 @@
     <row r="17" spans="1:15">
       <c r="A17" s="35"/>
       <c r="B17" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C17" s="57"/>
       <c r="D17" s="57"/>
@@ -6400,7 +6394,7 @@
     <row r="18" spans="1:15">
       <c r="A18" s="35"/>
       <c r="B18" s="57" t="s">
-        <v>88</v>
+        <v>182</v>
       </c>
       <c r="C18" s="42"/>
       <c r="D18" s="42"/>
@@ -6455,7 +6449,7 @@
     <row r="21" spans="1:15" ht="18" customHeight="1">
       <c r="A21" s="44"/>
       <c r="B21" s="57" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C21" s="44"/>
       <c r="D21" s="44"/>
@@ -6474,7 +6468,7 @@
     <row r="22" spans="1:15" ht="18" customHeight="1">
       <c r="A22" s="8"/>
       <c r="B22" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
@@ -6510,7 +6504,7 @@
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C24" s="46"/>
       <c r="D24" s="46"/>
@@ -6529,7 +6523,7 @@
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="57" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C25" s="46"/>
       <c r="D25" s="46"/>
@@ -6688,28 +6682,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="89" t="s">
+      <c r="B1" s="117"/>
+      <c r="C1" s="138" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="90"/>
-      <c r="E1" s="91" t="s">
+      <c r="D1" s="139"/>
+      <c r="E1" s="140" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="93"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="142"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -6719,17 +6713,17 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="93"/>
+      <c r="A2" s="118"/>
+      <c r="B2" s="120"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="139"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="142"/>
       <c r="L2" s="25" t="s">
         <v>13</v>
       </c>
@@ -6778,7 +6772,7 @@
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
       <c r="B5" s="31" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
@@ -6833,7 +6827,7 @@
     <row r="8" spans="1:15">
       <c r="A8" s="35"/>
       <c r="B8" s="35" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C8" s="35"/>
       <c r="D8" s="35"/>
@@ -6888,7 +6882,7 @@
     <row r="11" spans="1:15">
       <c r="A11" s="35"/>
       <c r="B11" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C11" s="35"/>
       <c r="D11" s="35"/>
@@ -7300,28 +7294,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="89" t="s">
+      <c r="B1" s="117"/>
+      <c r="C1" s="138" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="90"/>
-      <c r="E1" s="91" t="s">
+      <c r="D1" s="139"/>
+      <c r="E1" s="140" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="93"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="142"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -7331,17 +7325,17 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="93"/>
+      <c r="A2" s="118"/>
+      <c r="B2" s="120"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="139"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="142"/>
       <c r="L2" s="25" t="s">
         <v>13</v>
       </c>
@@ -7419,11 +7413,11 @@
     <row r="6" spans="1:15">
       <c r="A6" s="35"/>
       <c r="B6" s="53" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C6" s="56"/>
       <c r="D6" s="53" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E6" s="56"/>
       <c r="F6" s="53">
@@ -7435,7 +7429,7 @@
       </c>
       <c r="I6" s="56"/>
       <c r="J6" s="53" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K6" s="54"/>
       <c r="L6" s="62"/>
@@ -7446,7 +7440,7 @@
     <row r="7" spans="1:15">
       <c r="A7" s="35"/>
       <c r="B7" s="53" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C7" s="56"/>
       <c r="D7" s="53" t="s">
@@ -7462,7 +7456,7 @@
       </c>
       <c r="I7" s="56"/>
       <c r="J7" s="53" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="54"/>
@@ -7473,11 +7467,11 @@
     <row r="8" spans="1:15">
       <c r="A8" s="35"/>
       <c r="B8" s="53" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C8" s="56"/>
       <c r="D8" s="53" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E8" s="56"/>
       <c r="F8" s="53">
@@ -7489,7 +7483,7 @@
       </c>
       <c r="I8" s="56"/>
       <c r="J8" s="53" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K8" s="23"/>
       <c r="L8" s="54"/>
@@ -7500,15 +7494,15 @@
     <row r="9" spans="1:15" ht="36" customHeight="1">
       <c r="A9" s="35"/>
       <c r="B9" s="53" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C9" s="56"/>
       <c r="D9" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E9" s="56"/>
       <c r="F9" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G9" s="56"/>
       <c r="H9" s="17" t="s">
@@ -7516,7 +7510,7 @@
       </c>
       <c r="I9" s="56"/>
       <c r="J9" s="155" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K9" s="156"/>
       <c r="L9" s="156"/>
@@ -7527,11 +7521,11 @@
     <row r="10" spans="1:15">
       <c r="A10" s="35"/>
       <c r="B10" s="68" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C10" s="56"/>
       <c r="D10" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E10" s="56"/>
       <c r="F10" s="17">
@@ -7543,7 +7537,7 @@
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="82" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K10" s="23"/>
       <c r="L10" s="23"/>
@@ -7554,11 +7548,11 @@
     <row r="11" spans="1:15">
       <c r="A11" s="35"/>
       <c r="B11" s="17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C11" s="56"/>
       <c r="D11" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E11" s="56"/>
       <c r="F11" s="17">
@@ -7570,7 +7564,7 @@
       </c>
       <c r="I11" s="56"/>
       <c r="J11" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K11" s="23"/>
       <c r="L11" s="23"/>
@@ -7581,11 +7575,11 @@
     <row r="12" spans="1:15">
       <c r="A12" s="35"/>
       <c r="B12" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C12" s="55"/>
       <c r="D12" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E12" s="56"/>
       <c r="F12" s="17">
@@ -7597,7 +7591,7 @@
       </c>
       <c r="I12" s="56"/>
       <c r="J12" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="23"/>
@@ -7608,11 +7602,11 @@
     <row r="13" spans="1:15">
       <c r="A13" s="35"/>
       <c r="B13" s="53" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C13" s="74"/>
       <c r="D13" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E13" s="56"/>
       <c r="F13" s="17">
@@ -7633,11 +7627,11 @@
     <row r="14" spans="1:15" ht="54" customHeight="1">
       <c r="A14" s="35"/>
       <c r="B14" s="75" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C14" s="74"/>
       <c r="D14" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E14" s="56"/>
       <c r="F14" s="17">
@@ -7649,7 +7643,7 @@
       </c>
       <c r="I14" s="56"/>
       <c r="J14" s="152" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K14" s="153"/>
       <c r="L14" s="153"/>
@@ -7660,11 +7654,11 @@
     <row r="15" spans="1:15" ht="36" customHeight="1">
       <c r="A15" s="35"/>
       <c r="B15" s="75" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C15" s="74"/>
       <c r="D15" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E15" s="56"/>
       <c r="F15" s="17">
@@ -7676,7 +7670,7 @@
       </c>
       <c r="I15" s="56"/>
       <c r="J15" s="158" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K15" s="159"/>
       <c r="L15" s="159"/>
@@ -7687,23 +7681,23 @@
     <row r="16" spans="1:15">
       <c r="A16" s="35"/>
       <c r="B16" s="75" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C16" s="74"/>
       <c r="D16" s="75" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E16" s="74"/>
       <c r="F16" s="53" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G16" s="74"/>
       <c r="H16" s="75" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I16" s="74"/>
       <c r="J16" s="17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K16" s="23"/>
       <c r="L16" s="23"/>
@@ -7714,19 +7708,19 @@
     <row r="17" spans="1:15">
       <c r="A17" s="35"/>
       <c r="B17" s="75" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C17" s="74"/>
       <c r="D17" s="75" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E17" s="74"/>
       <c r="F17" s="53" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G17" s="74"/>
       <c r="H17" s="75" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I17" s="74"/>
       <c r="J17" s="17"/>
@@ -7739,11 +7733,11 @@
     <row r="18" spans="1:15" ht="36" customHeight="1">
       <c r="A18" s="35"/>
       <c r="B18" s="75" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C18" s="74"/>
       <c r="D18" s="75" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E18" s="74"/>
       <c r="F18" s="53">
@@ -7751,11 +7745,11 @@
       </c>
       <c r="G18" s="74"/>
       <c r="H18" s="75" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I18" s="74"/>
       <c r="J18" s="152" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K18" s="153"/>
       <c r="L18" s="153"/>
@@ -7766,23 +7760,23 @@
     <row r="19" spans="1:15" ht="36" customHeight="1">
       <c r="A19" s="35"/>
       <c r="B19" s="75" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C19" s="74"/>
       <c r="D19" s="75" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E19" s="74"/>
       <c r="F19" s="53" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G19" s="74"/>
       <c r="H19" s="75" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I19" s="74"/>
       <c r="J19" s="155" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K19" s="156"/>
       <c r="L19" s="156"/>
@@ -7793,23 +7787,23 @@
     <row r="20" spans="1:15" ht="36" customHeight="1">
       <c r="A20" s="35"/>
       <c r="B20" s="75" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C20" s="74"/>
       <c r="D20" s="75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E20" s="74"/>
       <c r="F20" s="53" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G20" s="74"/>
       <c r="H20" s="75" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I20" s="74"/>
       <c r="J20" s="155" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K20" s="156"/>
       <c r="L20" s="156"/>
@@ -8125,17 +8119,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:K1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:K2"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="J19:M19"/>
     <mergeCell ref="J20:M20"/>
     <mergeCell ref="J9:M9"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="J15:M15"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:K1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:K2"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8148,28 +8142,28 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="89" t="s">
+      <c r="B1" s="117"/>
+      <c r="C1" s="138" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="90"/>
-      <c r="E1" s="91" t="s">
+      <c r="D1" s="139"/>
+      <c r="E1" s="140" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="93"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="142"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -8179,17 +8173,17 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="87"/>
-      <c r="B2" s="88"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="93"/>
+      <c r="A2" s="118"/>
+      <c r="B2" s="120"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="139"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="142"/>
       <c r="L2" s="25" t="s">
         <v>13</v>
       </c>
@@ -8264,21 +8258,21 @@
         <v>1</v>
       </c>
       <c r="C6" s="53" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D6" s="51"/>
       <c r="E6" s="23"/>
       <c r="F6" s="51"/>
       <c r="G6" s="56"/>
       <c r="H6" s="53" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I6" s="23"/>
       <c r="J6" s="51"/>
       <c r="K6" s="51"/>
       <c r="L6" s="66"/>
       <c r="M6" s="17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N6" s="62"/>
       <c r="O6" s="55"/>
@@ -8289,21 +8283,21 @@
         <v>2</v>
       </c>
       <c r="C7" s="53" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D7" s="51"/>
       <c r="E7" s="23"/>
       <c r="F7" s="51"/>
       <c r="G7" s="56"/>
       <c r="H7" s="53" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I7" s="23"/>
       <c r="J7" s="51"/>
       <c r="K7" s="51"/>
       <c r="L7" s="66"/>
       <c r="M7" s="76" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N7" s="54"/>
       <c r="O7" s="55"/>
